--- a/Live ТБ/Live ТБ.xlsx
+++ b/Live ТБ/Live ТБ.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R6bc19f0d05e04378"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R2cfe9904a1654b86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="R2a31b002570348ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="Rf6c95df203d0488c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R556ee96ca0e44904"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="Re4c30f588df34a46"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -515,7 +515,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -526,7 +526,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -537,7 +537,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -820,7 +820,7 @@
       </x:c>
       <x:c r="B7" s="57" t="n">
         <x:f>COUNTA('Реестр'!$A$6:$A$505)</x:f>
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="55"/>
       <x:c r="D7" s="58" t="str">
@@ -897,7 +897,7 @@
       </x:c>
       <x:c r="B12" s="57" t="n">
         <x:f>COUNTIF('Реестр'!$W$6:$W$505,"Открыт")</x:f>
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C12" s="55"/>
       <x:c r="D12" s="61"/>
@@ -941,7 +941,7 @@
       </x:c>
       <x:c r="B15" s="64" t="n">
         <x:f>IF(B7=0,"",AVERAGEIF('Реестр'!$A$6:$A$505,"&gt;0",'Реестр'!$J$6:$J$505))</x:f>
-        <x:v>1.825</x:v>
+        <x:v>1.864285714285714</x:v>
       </x:c>
       <x:c r="C15" s="55"/>
       <x:c r="D15" s="55"/>
@@ -955,7 +955,7 @@
         <x:v>Дата последнего выбора</x:v>
       </x:c>
       <x:c r="B16" s="70" t="str">
-        <x:v>13.10.2026 16:39</x:v>
+        <x:v>13.10.2026 18:08</x:v>
       </x:c>
       <x:c r="C16" s="55"/>
       <x:c r="D16" s="55"/>
@@ -1307,154 +1307,359 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="80"/>
-      <x:c r="B8" s="80"/>
-      <x:c r="C8" s="83"/>
-      <x:c r="D8" s="80"/>
-      <x:c r="E8" s="80"/>
-      <x:c r="F8" s="86"/>
-      <x:c r="G8" s="80"/>
-      <x:c r="H8" s="95"/>
-      <x:c r="I8" s="95"/>
-      <x:c r="J8" s="96"/>
-      <x:c r="K8" s="97"/>
-      <x:c r="L8" s="98"/>
-      <x:c r="M8" s="98"/>
-      <x:c r="N8" s="98"/>
-      <x:c r="O8" s="98"/>
-      <x:c r="P8" s="98"/>
-      <x:c r="Q8" s="80"/>
-      <x:c r="R8" s="80"/>
-      <x:c r="S8" s="80"/>
+      <x:c r="A8" s="80" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="80" t="str">
+        <x:v>13234372</x:v>
+      </x:c>
+      <x:c r="C8" s="83" t="str">
+        <x:v>13.10.2026 18:08</x:v>
+      </x:c>
+      <x:c r="D8" s="80" t="str">
+        <x:v>Алжир - Второй дивизион</x:v>
+      </x:c>
+      <x:c r="E8" s="80" t="str">
+        <x:v>ГК Маскара - ИРБ Сиди Мхамед Бенали</x:v>
+      </x:c>
+      <x:c r="F8" s="86" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G8" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H8" s="95" t="str">
+        <x:v>Сильное одностороннее давление хозяев при равном счёте</x:v>
+      </x:c>
+      <x:c r="I8" s="95" t="str">
+        <x:v>ТБ 1,0 всего матча</x:v>
+      </x:c>
+      <x:c r="J8" s="96" t="n">
+        <x:v>1.825</x:v>
+      </x:c>
+      <x:c r="K8" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L8" s="98" t="str">
+        <x:v>Владение 72:28; удары в створ 5:1; мимо 7:1; угловые 5:1; опасные атаки 59:19</x:v>
+      </x:c>
+      <x:c r="M8" s="98" t="str">
+        <x:v>Нет отдельного снимка за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N8" s="98" t="str">
+        <x:v>ГК Маскара постоянно давит и остаётся live-фаворитом; один гол даёт возврат, два - полный плюс</x:v>
+      </x:c>
+      <x:c r="O8" s="98" t="str">
+        <x:v>Низовая лига; xG недоступен; при одном голе будет только возврат</x:v>
+      </x:c>
+      <x:c r="P8" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q8" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R8" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S8" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T8" s="80"/>
       <x:c r="U8" s="80"/>
       <x:c r="V8" s="89" t="str">
-        <x:f>IF(U8="Выигрыш",J8-1,IF(U8="Поражение",-1,IF(U8="Возврат",0,IF(U8="Полувыигрыш",(J8-1)/2,IF(U8="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U8="","",IF(U8="Плюс",J8-1,IF(U8="Минус",-1,IF(U8="Возврат",0,IF(U8="Полуплюс",(J8-1)/2,IF(U8="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W8" s="80" t="str">
         <x:f>IF(A8="","",IF(U8="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X8" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X8" s="98" t="str">
+        <x:v>Основной кандидат текущего запуска</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="80"/>
-      <x:c r="B9" s="80"/>
-      <x:c r="C9" s="83"/>
-      <x:c r="D9" s="80"/>
-      <x:c r="E9" s="80"/>
-      <x:c r="F9" s="86"/>
-      <x:c r="G9" s="80"/>
-      <x:c r="H9" s="95"/>
-      <x:c r="I9" s="95"/>
-      <x:c r="J9" s="96"/>
-      <x:c r="K9" s="97"/>
-      <x:c r="L9" s="98"/>
-      <x:c r="M9" s="98"/>
-      <x:c r="N9" s="98"/>
-      <x:c r="O9" s="98"/>
-      <x:c r="P9" s="98"/>
-      <x:c r="Q9" s="80"/>
-      <x:c r="R9" s="80"/>
-      <x:c r="S9" s="80"/>
+      <x:c r="A9" s="80" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="80" t="str">
+        <x:v>13285570</x:v>
+      </x:c>
+      <x:c r="C9" s="83" t="str">
+        <x:v>13.10.2026 18:08</x:v>
+      </x:c>
+      <x:c r="D9" s="80" t="str">
+        <x:v>Азия - Лига чемпионов АФК 2</x:v>
+      </x:c>
+      <x:c r="E9" s="80" t="str">
+        <x:v>Ист Бенгал - Аль-Шорта</x:v>
+      </x:c>
+      <x:c r="F9" s="86" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G9" s="80" t="str">
+        <x:v>2:3</x:v>
+      </x:c>
+      <x:c r="H9" s="95" t="str">
+        <x:v>Открытый матч с взаимными моментами и сохраняющейся атакой</x:v>
+      </x:c>
+      <x:c r="I9" s="95" t="str">
+        <x:v>ТБ 6,25 всего матча</x:v>
+      </x:c>
+      <x:c r="J9" s="96" t="n">
+        <x:v>2.05</x:v>
+      </x:c>
+      <x:c r="K9" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L9" s="98" t="str">
+        <x:v>xG 2,32:1,45; удары в створ 7:3; угловые 3:6; опасные атаки 29:44; владение 39:61</x:v>
+      </x:c>
+      <x:c r="M9" s="98" t="str">
+        <x:v>Нет отдельного снимка за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N9" s="98" t="str">
+        <x:v>Суммарный xG 3,77 и 10 ударов в створ подтверждают открытый сценарий; проигрывающие хозяева вынуждены атаковать</x:v>
+      </x:c>
+      <x:c r="O9" s="98" t="str">
+        <x:v>Для полного плюса нужны ещё два гола; один дополнительный гол даёт полуминус</x:v>
+      </x:c>
+      <x:c r="P9" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q9" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R9" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S9" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T9" s="80"/>
       <x:c r="U9" s="80"/>
       <x:c r="V9" s="89" t="str">
-        <x:f>IF(U9="Выигрыш",J9-1,IF(U9="Поражение",-1,IF(U9="Возврат",0,IF(U9="Полувыигрыш",(J9-1)/2,IF(U9="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U9="","",IF(U9="Плюс",J9-1,IF(U9="Минус",-1,IF(U9="Возврат",0,IF(U9="Полуплюс",(J9-1)/2,IF(U9="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W9" s="80" t="str">
         <x:f>IF(A9="","",IF(U9="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X9" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X9" s="98" t="str">
+        <x:v>Агрессивный кандидат по открытому сценарию</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="80"/>
-      <x:c r="B10" s="80"/>
-      <x:c r="C10" s="83"/>
-      <x:c r="D10" s="80"/>
-      <x:c r="E10" s="80"/>
-      <x:c r="F10" s="86"/>
-      <x:c r="G10" s="80"/>
-      <x:c r="H10" s="95"/>
-      <x:c r="I10" s="95"/>
-      <x:c r="J10" s="96"/>
-      <x:c r="K10" s="97"/>
-      <x:c r="L10" s="98"/>
-      <x:c r="M10" s="98"/>
-      <x:c r="N10" s="98"/>
-      <x:c r="O10" s="98"/>
-      <x:c r="P10" s="98"/>
-      <x:c r="Q10" s="80"/>
-      <x:c r="R10" s="80"/>
-      <x:c r="S10" s="80"/>
+      <x:c r="A10" s="80" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" s="80" t="str">
+        <x:v>13234373</x:v>
+      </x:c>
+      <x:c r="C10" s="83" t="str">
+        <x:v>13.10.2026 18:08</x:v>
+      </x:c>
+      <x:c r="D10" s="80" t="str">
+        <x:v>Алжир - Второй дивизион</x:v>
+      </x:c>
+      <x:c r="E10" s="80" t="str">
+        <x:v>ЕСМ Колеа - ЕС Мостаганем</x:v>
+      </x:c>
+      <x:c r="F10" s="86" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G10" s="80" t="str">
+        <x:v>1:1</x:v>
+      </x:c>
+      <x:c r="H10" s="95" t="str">
+        <x:v>Равный счёт после активного первого тайма</x:v>
+      </x:c>
+      <x:c r="I10" s="95" t="str">
+        <x:v>ТБ 3,0 всего матча</x:v>
+      </x:c>
+      <x:c r="J10" s="96" t="n">
+        <x:v>1.975</x:v>
+      </x:c>
+      <x:c r="K10" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L10" s="98" t="str">
+        <x:v>Удары в створ 3:1; мимо 4:5; угловые 2:2; опасные атаки 28:17</x:v>
+      </x:c>
+      <x:c r="M10" s="98" t="str">
+        <x:v>Нет отдельного снимка за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N10" s="98" t="str">
+        <x:v>Две команды уже забили; 13 ударов суммарно; один гол даёт возврат, два - полный плюс</x:v>
+      </x:c>
+      <x:c r="O10" s="98" t="str">
+        <x:v>Только 4 удара в створ; xG недоступен; Алжир часто замедляется после перерыва</x:v>
+      </x:c>
+      <x:c r="P10" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q10" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R10" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S10" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T10" s="80"/>
       <x:c r="U10" s="80"/>
       <x:c r="V10" s="89" t="str">
-        <x:f>IF(U10="Выигрыш",J10-1,IF(U10="Поражение",-1,IF(U10="Возврат",0,IF(U10="Полувыигрыш",(J10-1)/2,IF(U10="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U10="","",IF(U10="Плюс",J10-1,IF(U10="Минус",-1,IF(U10="Возврат",0,IF(U10="Полуплюс",(J10-1)/2,IF(U10="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W10" s="80" t="str">
         <x:f>IF(A10="","",IF(U10="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X10" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X10" s="98" t="str">
+        <x:v>Линия с возвратом при одном дополнительном голе</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="80"/>
-      <x:c r="B11" s="80"/>
-      <x:c r="C11" s="83"/>
-      <x:c r="D11" s="80"/>
-      <x:c r="E11" s="80"/>
-      <x:c r="F11" s="86"/>
-      <x:c r="G11" s="80"/>
-      <x:c r="H11" s="95"/>
-      <x:c r="I11" s="95"/>
-      <x:c r="J11" s="96"/>
-      <x:c r="K11" s="97"/>
-      <x:c r="L11" s="98"/>
-      <x:c r="M11" s="98"/>
-      <x:c r="N11" s="98"/>
-      <x:c r="O11" s="98"/>
-      <x:c r="P11" s="98"/>
-      <x:c r="Q11" s="80"/>
-      <x:c r="R11" s="80"/>
-      <x:c r="S11" s="80"/>
+      <x:c r="A11" s="80" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B11" s="80" t="str">
+        <x:v>12202850</x:v>
+      </x:c>
+      <x:c r="C11" s="83" t="str">
+        <x:v>13.10.2026 18:08</x:v>
+      </x:c>
+      <x:c r="D11" s="80" t="str">
+        <x:v>Турция - Первая лига</x:v>
+      </x:c>
+      <x:c r="E11" s="80" t="str">
+        <x:v>Сарыер - Бодрум ФК</x:v>
+      </x:c>
+      <x:c r="F11" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G11" s="80" t="str">
+        <x:v>0:3</x:v>
+      </x:c>
+      <x:c r="H11" s="95" t="str">
+        <x:v>Хозяева вынуждены раскрываться, гости опасны в переходах</x:v>
+      </x:c>
+      <x:c r="I11" s="95" t="str">
+        <x:v>ТБ 4,5 всего матча</x:v>
+      </x:c>
+      <x:c r="J11" s="96" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="K11" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L11" s="98" t="str">
+        <x:v>Владение 62:38; xG 0,14:0,72; удары в створ 2:7; мимо 3:4; угловые 3:3; опасные атаки 25:25</x:v>
+      </x:c>
+      <x:c r="M11" s="98" t="str">
+        <x:v>Нет отдельного снимка за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N11" s="98" t="str">
+        <x:v>Девять ударов в створ; 0:3 заставляет хозяев рисковать, а Бодрум сохраняет контратакующий сценарий</x:v>
+      </x:c>
+      <x:c r="O11" s="98" t="str">
+        <x:v>Три гола сильно выше xG; лидер может сознательно снизить темп; нужны ещё два гола</x:v>
+      </x:c>
+      <x:c r="P11" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q11" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R11" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S11" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T11" s="80"/>
       <x:c r="U11" s="80"/>
       <x:c r="V11" s="89" t="str">
-        <x:f>IF(U11="Выигрыш",J11-1,IF(U11="Поражение",-1,IF(U11="Возврат",0,IF(U11="Полувыигрыш",(J11-1)/2,IF(U11="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U11="","",IF(U11="Плюс",J11-1,IF(U11="Минус",-1,IF(U11="Возврат",0,IF(U11="Полуплюс",(J11-1)/2,IF(U11="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W11" s="80" t="str">
         <x:f>IF(A11="","",IF(U11="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X11" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X11" s="98" t="str">
+        <x:v>Высокая дисперсия из-за реализации выше xG</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="80"/>
-      <x:c r="B12" s="80"/>
-      <x:c r="C12" s="83"/>
-      <x:c r="D12" s="80"/>
-      <x:c r="E12" s="80"/>
-      <x:c r="F12" s="86"/>
-      <x:c r="G12" s="80"/>
-      <x:c r="H12" s="95"/>
-      <x:c r="I12" s="95"/>
-      <x:c r="J12" s="96"/>
-      <x:c r="K12" s="97"/>
-      <x:c r="L12" s="98"/>
-      <x:c r="M12" s="98"/>
-      <x:c r="N12" s="98"/>
-      <x:c r="O12" s="98"/>
-      <x:c r="P12" s="98"/>
-      <x:c r="Q12" s="80"/>
-      <x:c r="R12" s="80"/>
-      <x:c r="S12" s="80"/>
+      <x:c r="A12" s="80" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="80" t="str">
+        <x:v>13234392</x:v>
+      </x:c>
+      <x:c r="C12" s="83" t="str">
+        <x:v>13.10.2026 18:08</x:v>
+      </x:c>
+      <x:c r="D12" s="80" t="str">
+        <x:v>Алжир - Второй дивизион</x:v>
+      </x:c>
+      <x:c r="E12" s="80" t="str">
+        <x:v>УС Шауия - Параду</x:v>
+      </x:c>
+      <x:c r="F12" s="86" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G12" s="80" t="str">
+        <x:v>1:0</x:v>
+      </x:c>
+      <x:c r="H12" s="95" t="str">
+        <x:v>Высокое территориальное давление при минимальном счёте</x:v>
+      </x:c>
+      <x:c r="I12" s="95" t="str">
+        <x:v>ТБ 1,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J12" s="96" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="K12" s="97" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L12" s="98" t="str">
+        <x:v>Удары в створ 1:1; мимо 5:1; угловые 6:4; опасные атаки 60:34</x:v>
+      </x:c>
+      <x:c r="M12" s="98" t="str">
+        <x:v>Нет отдельного снимка за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N12" s="98" t="str">
+        <x:v>Десять угловых и 94 опасные атаки; ещё один гол уже даёт половину плюса</x:v>
+      </x:c>
+      <x:c r="O12" s="98" t="str">
+        <x:v>Всего 2 удара в створ; хозяева ведут и могут перейти к контролю</x:v>
+      </x:c>
+      <x:c r="P12" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q12" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R12" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S12" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T12" s="80"/>
       <x:c r="U12" s="80"/>
       <x:c r="V12" s="89" t="str">
-        <x:f>IF(U12="Выигрыш",J12-1,IF(U12="Поражение",-1,IF(U12="Возврат",0,IF(U12="Полувыигрыш",(J12-1)/2,IF(U12="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U12="","",IF(U12="Плюс",J12-1,IF(U12="Минус",-1,IF(U12="Возврат",0,IF(U12="Полуплюс",(J12-1)/2,IF(U12="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W12" s="80" t="str">
         <x:f>IF(A12="","",IF(U12="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X12" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X12" s="98" t="str">
+        <x:v>Защитная азиатская линия: второй гол даёт полуплюс</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="80"/>

--- a/Live ТБ/Live ТБ.xlsx
+++ b/Live ТБ/Live ТБ.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="Rf6c95df203d0488c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R556ee96ca0e44904"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="Re4c30f588df34a46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R3b16fbb84a7a44a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R8d7d23fb87c24003"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="Rfce400a58ee24e13"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -820,7 +820,7 @@
       </x:c>
       <x:c r="B7" s="57" t="n">
         <x:f>COUNTA('Реестр'!$A$6:$A$505)</x:f>
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="55"/>
       <x:c r="D7" s="58" t="str">
@@ -897,7 +897,7 @@
       </x:c>
       <x:c r="B12" s="57" t="n">
         <x:f>COUNTIF('Реестр'!$W$6:$W$505,"Открыт")</x:f>
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="55"/>
       <x:c r="D12" s="61"/>
@@ -941,7 +941,7 @@
       </x:c>
       <x:c r="B15" s="64" t="n">
         <x:f>IF(B7=0,"",AVERAGEIF('Реестр'!$A$6:$A$505,"&gt;0",'Реестр'!$J$6:$J$505))</x:f>
-        <x:v>1.864285714285714</x:v>
+        <x:v>1.8796874999999997</x:v>
       </x:c>
       <x:c r="C15" s="55"/>
       <x:c r="D15" s="55"/>
@@ -955,7 +955,7 @@
         <x:v>Дата последнего выбора</x:v>
       </x:c>
       <x:c r="B16" s="70" t="str">
-        <x:v>13.10.2026 18:08</x:v>
+        <x:v>13.10.2026 18:43</x:v>
       </x:c>
       <x:c r="C16" s="55"/>
       <x:c r="D16" s="55"/>
@@ -1662,274 +1662,643 @@
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="80"/>
-      <x:c r="B13" s="80"/>
-      <x:c r="C13" s="83"/>
-      <x:c r="D13" s="80"/>
-      <x:c r="E13" s="80"/>
-      <x:c r="F13" s="86"/>
-      <x:c r="G13" s="80"/>
-      <x:c r="H13" s="95"/>
-      <x:c r="I13" s="95"/>
-      <x:c r="J13" s="96"/>
-      <x:c r="K13" s="97"/>
-      <x:c r="L13" s="98"/>
-      <x:c r="M13" s="98"/>
-      <x:c r="N13" s="98"/>
-      <x:c r="O13" s="98"/>
-      <x:c r="P13" s="98"/>
-      <x:c r="Q13" s="80"/>
-      <x:c r="R13" s="80"/>
-      <x:c r="S13" s="80"/>
+      <x:c r="A13" s="80" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" s="80" t="str">
+        <x:v>12325195</x:v>
+      </x:c>
+      <x:c r="C13" s="83" t="str">
+        <x:v>13.10.2026 18:37</x:v>
+      </x:c>
+      <x:c r="D13" s="80" t="str">
+        <x:v>Саудовская Аравия - Первый дивизион</x:v>
+      </x:c>
+      <x:c r="E13" s="80" t="str">
+        <x:v>Аль-Букайрия - Аль-Зульфи</x:v>
+      </x:c>
+      <x:c r="F13" s="86" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G13" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H13" s="95" t="str">
+        <x:v>Удаление у хозяев и устойчивое давление фаворита</x:v>
+      </x:c>
+      <x:c r="I13" s="95" t="str">
+        <x:v>ТБ 2,25 всего матча</x:v>
+      </x:c>
+      <x:c r="J13" s="96" t="n">
+        <x:v>2.025</x:v>
+      </x:c>
+      <x:c r="K13" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L13" s="98" t="str">
+        <x:v>Владение 50:50; удары в створ 1:3; мимо 0:4; угловые 0:6; опасные атаки 4:18; удаления 1:0</x:v>
+      </x:c>
+      <x:c r="M13" s="98" t="str">
+        <x:v>За 14 минут: удаление у хозяев; удары в створ +1:+2; удары мимо 0:+4; угловые 0:+4; опасные атаки +1:+11</x:v>
+      </x:c>
+      <x:c r="N13" s="98" t="str">
+        <x:v>Аль-Зульфи был фаворитом за 1,44; соперник в меньшинстве; давление и стандарты на стороне гостей</x:v>
+      </x:c>
+      <x:c r="O13" s="98" t="str">
+        <x:v>Счёт 0:0; для полного плюса нужны три гола; большинство может сделать игру односторонней</x:v>
+      </x:c>
+      <x:c r="P13" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q13" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R13" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S13" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T13" s="80"/>
       <x:c r="U13" s="80"/>
       <x:c r="V13" s="89" t="str">
-        <x:f>IF(U13="Выигрыш",J13-1,IF(U13="Поражение",-1,IF(U13="Возврат",0,IF(U13="Полувыигрыш",(J13-1)/2,IF(U13="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U13="","",IF(U13="Плюс",J13-1,IF(U13="Минус",-1,IF(U13="Возврат",0,IF(U13="Полуплюс",(J13-1)/2,IF(U13="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W13" s="80" t="str">
         <x:f>IF(A13="","",IF(U13="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X13" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X13" s="98" t="str">
+        <x:v>Главный кандидат: фаворит в большинстве и резко нарастил давление</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="80"/>
-      <x:c r="B14" s="80"/>
-      <x:c r="C14" s="83"/>
-      <x:c r="D14" s="80"/>
-      <x:c r="E14" s="80"/>
-      <x:c r="F14" s="86"/>
-      <x:c r="G14" s="80"/>
-      <x:c r="H14" s="95"/>
-      <x:c r="I14" s="95"/>
-      <x:c r="J14" s="96"/>
-      <x:c r="K14" s="97"/>
-      <x:c r="L14" s="98"/>
-      <x:c r="M14" s="98"/>
-      <x:c r="N14" s="98"/>
-      <x:c r="O14" s="98"/>
-      <x:c r="P14" s="98"/>
-      <x:c r="Q14" s="80"/>
-      <x:c r="R14" s="80"/>
-      <x:c r="S14" s="80"/>
+      <x:c r="A14" s="80" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="80" t="str">
+        <x:v>13285445</x:v>
+      </x:c>
+      <x:c r="C14" s="83" t="str">
+        <x:v>13.10.2026 18:37</x:v>
+      </x:c>
+      <x:c r="D14" s="80" t="str">
+        <x:v>Чили - Терсера</x:v>
+      </x:c>
+      <x:c r="E14" s="80" t="str">
+        <x:v>Атлетико Ориенте - Комуналь Кабреро</x:v>
+      </x:c>
+      <x:c r="F14" s="86" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G14" s="80" t="str">
+        <x:v>1:2</x:v>
+      </x:c>
+      <x:c r="H14" s="95" t="str">
+        <x:v>Открытая игра продолжается после третьего гола</x:v>
+      </x:c>
+      <x:c r="I14" s="95" t="str">
+        <x:v>ТБ 5,25 всего матча</x:v>
+      </x:c>
+      <x:c r="J14" s="96" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="K14" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L14" s="98" t="str">
+        <x:v>Владение 69:31; удары в створ 2:7; мимо 4:3; угловые 2:2; опасные атаки 11:16</x:v>
+      </x:c>
+      <x:c r="M14" s="98" t="str">
+        <x:v>За 13 минут: гол гостей; удары в створ 0:+4; удары мимо +3:+1; угловые 0:+1; опасные атаки +5:+8</x:v>
+      </x:c>
+      <x:c r="N14" s="98" t="str">
+        <x:v>Девять ударов в створ; четыре свежих попадания гостей; третий гол не остановил атаки</x:v>
+      </x:c>
+      <x:c r="O14" s="98" t="str">
+        <x:v>Нужны ещё три гола; нижняя лига и нет xG; высокая ранняя реализация</x:v>
+      </x:c>
+      <x:c r="P14" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q14" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R14" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S14" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T14" s="80"/>
       <x:c r="U14" s="80"/>
       <x:c r="V14" s="89" t="str">
-        <x:f>IF(U14="Выигрыш",J14-1,IF(U14="Поражение",-1,IF(U14="Возврат",0,IF(U14="Полувыигрыш",(J14-1)/2,IF(U14="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U14="","",IF(U14="Плюс",J14-1,IF(U14="Минус",-1,IF(U14="Возврат",0,IF(U14="Полуплюс",(J14-1)/2,IF(U14="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W14" s="80" t="str">
         <x:f>IF(A14="","",IF(U14="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X14" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X14" s="98" t="str">
+        <x:v>Сильная атакующая динамика, но очень высокая линия</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="80"/>
-      <x:c r="B15" s="80"/>
-      <x:c r="C15" s="83"/>
-      <x:c r="D15" s="80"/>
-      <x:c r="E15" s="80"/>
-      <x:c r="F15" s="86"/>
-      <x:c r="G15" s="80"/>
-      <x:c r="H15" s="95"/>
-      <x:c r="I15" s="95"/>
-      <x:c r="J15" s="96"/>
-      <x:c r="K15" s="97"/>
-      <x:c r="L15" s="98"/>
-      <x:c r="M15" s="98"/>
-      <x:c r="N15" s="98"/>
-      <x:c r="O15" s="98"/>
-      <x:c r="P15" s="98"/>
-      <x:c r="Q15" s="80"/>
-      <x:c r="R15" s="80"/>
-      <x:c r="S15" s="80"/>
+      <x:c r="A15" s="80" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B15" s="80" t="str">
+        <x:v>12062993</x:v>
+      </x:c>
+      <x:c r="C15" s="83" t="str">
+        <x:v>13.10.2026 18:37</x:v>
+      </x:c>
+      <x:c r="D15" s="80" t="str">
+        <x:v>Женщины - Квалификация ЧМ</x:v>
+      </x:c>
+      <x:c r="E15" s="80" t="str">
+        <x:v>Словения - Турция</x:v>
+      </x:c>
+      <x:c r="F15" s="86" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G15" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H15" s="95" t="str">
+        <x:v>Фаворит давит на соперника, оставшегося в меньшинстве</x:v>
+      </x:c>
+      <x:c r="I15" s="95" t="str">
+        <x:v>ТБ 2,0 всего матча</x:v>
+      </x:c>
+      <x:c r="J15" s="96" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="K15" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L15" s="98" t="str">
+        <x:v>Владение 50:50; атаки 61:40; удары в створ 1:1; мимо 3:2; угловые 3:0; опасные атаки 47:24; удаления 0:1</x:v>
+      </x:c>
+      <x:c r="M15" s="98" t="str">
+        <x:v>Нет предыдущего снимка этой категории</x:v>
+      </x:c>
+      <x:c r="N15" s="98" t="str">
+        <x:v>Словения была фаворитом за 1,29; у Турции удаление; территориальное преимущество и угловые хозяев</x:v>
+      </x:c>
+      <x:c r="O15" s="98" t="str">
+        <x:v>Всего два удара в створ; при двух голах будет только возврат; красная карточка может закрыть Турцию</x:v>
+      </x:c>
+      <x:c r="P15" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q15" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R15" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S15" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T15" s="80"/>
       <x:c r="U15" s="80"/>
       <x:c r="V15" s="89" t="str">
-        <x:f>IF(U15="Выигрыш",J15-1,IF(U15="Поражение",-1,IF(U15="Возврат",0,IF(U15="Полувыигрыш",(J15-1)/2,IF(U15="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U15="","",IF(U15="Плюс",J15-1,IF(U15="Минус",-1,IF(U15="Возврат",0,IF(U15="Полуплюс",(J15-1)/2,IF(U15="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W15" s="80" t="str">
         <x:f>IF(A15="","",IF(U15="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X15" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X15" s="98" t="str">
+        <x:v>Кандидат по удалению и территориальному превосходству фаворита</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="80"/>
-      <x:c r="B16" s="80"/>
-      <x:c r="C16" s="83"/>
-      <x:c r="D16" s="80"/>
-      <x:c r="E16" s="80"/>
-      <x:c r="F16" s="86"/>
-      <x:c r="G16" s="80"/>
-      <x:c r="H16" s="95"/>
-      <x:c r="I16" s="95"/>
-      <x:c r="J16" s="96"/>
-      <x:c r="K16" s="97"/>
-      <x:c r="L16" s="98"/>
-      <x:c r="M16" s="98"/>
-      <x:c r="N16" s="98"/>
-      <x:c r="O16" s="98"/>
-      <x:c r="P16" s="98"/>
-      <x:c r="Q16" s="80"/>
-      <x:c r="R16" s="80"/>
-      <x:c r="S16" s="80"/>
+      <x:c r="A16" s="80" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" s="80" t="str">
+        <x:v>12126208</x:v>
+      </x:c>
+      <x:c r="C16" s="83" t="str">
+        <x:v>13.10.2026 18:37</x:v>
+      </x:c>
+      <x:c r="D16" s="80" t="str">
+        <x:v>Болгария - Вторая лига</x:v>
+      </x:c>
+      <x:c r="E16" s="80" t="str">
+        <x:v>Монтана - Лудогорец II</x:v>
+      </x:c>
+      <x:c r="F16" s="86" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G16" s="80" t="str">
+        <x:v>2:1</x:v>
+      </x:c>
+      <x:c r="H16" s="95" t="str">
+        <x:v>Результативная игра сохраняет импульс после гола хозяев</x:v>
+      </x:c>
+      <x:c r="I16" s="95" t="str">
+        <x:v>ТБ 4,5 всего матча</x:v>
+      </x:c>
+      <x:c r="J16" s="96" t="n">
+        <x:v>1.775</x:v>
+      </x:c>
+      <x:c r="K16" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L16" s="98" t="str">
+        <x:v>Владение 53:47; удары в створ 4:2; мимо 1:0; опасные атаки 17:12</x:v>
+      </x:c>
+      <x:c r="M16" s="98" t="str">
+        <x:v>За 14 минут: гол хозяев; удары в створ +3:+1; удары мимо +1:0; опасные атаки +10:+7</x:v>
+      </x:c>
+      <x:c r="N16" s="98" t="str">
+        <x:v>Свежий гол и четыре новых удара в створ; до конца остаётся больше тайма; гостям нужно отыгрываться</x:v>
+      </x:c>
+      <x:c r="O16" s="98" t="str">
+        <x:v>Три гола реализованы из шести ударов в створ; нет угловых; давление пока не экстремальное</x:v>
+      </x:c>
+      <x:c r="P16" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q16" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R16" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S16" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T16" s="80"/>
       <x:c r="U16" s="80"/>
       <x:c r="V16" s="89" t="str">
-        <x:f>IF(U16="Выигрыш",J16-1,IF(U16="Поражение",-1,IF(U16="Возврат",0,IF(U16="Полувыигрыш",(J16-1)/2,IF(U16="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U16="","",IF(U16="Плюс",J16-1,IF(U16="Минус",-1,IF(U16="Возврат",0,IF(U16="Полуплюс",(J16-1)/2,IF(U16="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W16" s="80" t="str">
         <x:f>IF(A16="","",IF(U16="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X16" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X16" s="98" t="str">
+        <x:v>Продолжение открытого матча после свежего гола</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="80"/>
-      <x:c r="B17" s="80"/>
-      <x:c r="C17" s="83"/>
-      <x:c r="D17" s="80"/>
-      <x:c r="E17" s="80"/>
-      <x:c r="F17" s="86"/>
-      <x:c r="G17" s="80"/>
-      <x:c r="H17" s="95"/>
-      <x:c r="I17" s="95"/>
-      <x:c r="J17" s="96"/>
-      <x:c r="K17" s="97"/>
-      <x:c r="L17" s="98"/>
-      <x:c r="M17" s="98"/>
-      <x:c r="N17" s="98"/>
-      <x:c r="O17" s="98"/>
-      <x:c r="P17" s="98"/>
-      <x:c r="Q17" s="80"/>
-      <x:c r="R17" s="80"/>
-      <x:c r="S17" s="80"/>
+      <x:c r="A17" s="80" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B17" s="80" t="str">
+        <x:v>12062983</x:v>
+      </x:c>
+      <x:c r="C17" s="83" t="str">
+        <x:v>13.10.2026 18:37</x:v>
+      </x:c>
+      <x:c r="D17" s="80" t="str">
+        <x:v>Женщины - Квалификация ЧМ</x:v>
+      </x:c>
+      <x:c r="E17" s="80" t="str">
+        <x:v>Сербия - Финляндия</x:v>
+      </x:c>
+      <x:c r="F17" s="86" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G17" s="80" t="str">
+        <x:v>1:1</x:v>
+      </x:c>
+      <x:c r="H17" s="95" t="str">
+        <x:v>Обе забили, фаворит Финляндия создаёт больше и продолжает давить</x:v>
+      </x:c>
+      <x:c r="I17" s="95" t="str">
+        <x:v>ТБ 3,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J17" s="96" t="n">
+        <x:v>1.925</x:v>
+      </x:c>
+      <x:c r="K17" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L17" s="98" t="str">
+        <x:v>Владение 58:42; xG 0,04:0,74; удары в створ 1:3; мимо 1:3; угловые 0:2; опасные атаки 14:26</x:v>
+      </x:c>
+      <x:c r="M17" s="98" t="str">
+        <x:v>Нет предыдущего снимка этой категории</x:v>
+      </x:c>
+      <x:c r="N17" s="98" t="str">
+        <x:v>Финляндия была фаворитом за 1,67; преимущество по xG, ударам и опасным атакам; обе команды уже забили</x:v>
+      </x:c>
+      <x:c r="O17" s="98" t="str">
+        <x:v>Гол Сербии сильно выше её xG; нужны два гола для полуплюса и три для полного плюса</x:v>
+      </x:c>
+      <x:c r="P17" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q17" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R17" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S17" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T17" s="80"/>
       <x:c r="U17" s="80"/>
       <x:c r="V17" s="89" t="str">
-        <x:f>IF(U17="Выигрыш",J17-1,IF(U17="Поражение",-1,IF(U17="Возврат",0,IF(U17="Полувыигрыш",(J17-1)/2,IF(U17="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U17="","",IF(U17="Плюс",J17-1,IF(U17="Минус",-1,IF(U17="Возврат",0,IF(U17="Полуплюс",(J17-1)/2,IF(U17="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W17" s="80" t="str">
         <x:f>IF(A17="","",IF(U17="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X17" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X17" s="98" t="str">
+        <x:v>Финляндия подтверждает статус фаворита качеством моментов</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="80"/>
-      <x:c r="B18" s="80"/>
-      <x:c r="C18" s="83"/>
-      <x:c r="D18" s="80"/>
-      <x:c r="E18" s="80"/>
-      <x:c r="F18" s="86"/>
-      <x:c r="G18" s="80"/>
-      <x:c r="H18" s="95"/>
-      <x:c r="I18" s="95"/>
-      <x:c r="J18" s="96"/>
-      <x:c r="K18" s="97"/>
-      <x:c r="L18" s="98"/>
-      <x:c r="M18" s="98"/>
-      <x:c r="N18" s="98"/>
-      <x:c r="O18" s="98"/>
-      <x:c r="P18" s="98"/>
-      <x:c r="Q18" s="80"/>
-      <x:c r="R18" s="80"/>
-      <x:c r="S18" s="80"/>
+      <x:c r="A18" s="80" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B18" s="80" t="str">
+        <x:v>12063011</x:v>
+      </x:c>
+      <x:c r="C18" s="83" t="str">
+        <x:v>13.10.2026 18:37</x:v>
+      </x:c>
+      <x:c r="D18" s="80" t="str">
+        <x:v>Женщины - Квалификация ЧМ</x:v>
+      </x:c>
+      <x:c r="E18" s="80" t="str">
+        <x:v>Словакия - Украина</x:v>
+      </x:c>
+      <x:c r="F18" s="86" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G18" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H18" s="95" t="str">
+        <x:v>Фаворит Украина давит, а обе команды регулярно попадают в створ</x:v>
+      </x:c>
+      <x:c r="I18" s="95" t="str">
+        <x:v>ТБ 1,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J18" s="96" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="K18" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L18" s="98" t="str">
+        <x:v>Владение 38:62; удары в створ 2:3; мимо 1:2; угловые 0:2; опасные атаки 17:26</x:v>
+      </x:c>
+      <x:c r="M18" s="98" t="str">
+        <x:v>Нет предыдущего снимка этой категории</x:v>
+      </x:c>
+      <x:c r="N18" s="98" t="str">
+        <x:v>Пять ударов в створ; Украина была фаворитом за 1,67 и ведёт по владению, ударам и давлению</x:v>
+      </x:c>
+      <x:c r="O18" s="98" t="str">
+        <x:v>Голов к 37-й минуте нет; два гола дадут только полуплюс; качество моментов без xG неизвестно</x:v>
+      </x:c>
+      <x:c r="P18" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q18" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R18" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S18" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T18" s="80"/>
       <x:c r="U18" s="80"/>
       <x:c r="V18" s="89" t="str">
-        <x:f>IF(U18="Выигрыш",J18-1,IF(U18="Поражение",-1,IF(U18="Возврат",0,IF(U18="Полувыигрыш",(J18-1)/2,IF(U18="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U18="","",IF(U18="Плюс",J18-1,IF(U18="Минус",-1,IF(U18="Возврат",0,IF(U18="Полуплюс",(J18-1)/2,IF(U18="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W18" s="80" t="str">
         <x:f>IF(A18="","",IF(U18="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X18" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X18" s="98" t="str">
+        <x:v>Низкая линия при пяти ударах в створ</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="80"/>
-      <x:c r="B19" s="80"/>
-      <x:c r="C19" s="83"/>
-      <x:c r="D19" s="80"/>
-      <x:c r="E19" s="80"/>
-      <x:c r="F19" s="86"/>
-      <x:c r="G19" s="80"/>
-      <x:c r="H19" s="95"/>
-      <x:c r="I19" s="95"/>
-      <x:c r="J19" s="96"/>
-      <x:c r="K19" s="97"/>
-      <x:c r="L19" s="98"/>
-      <x:c r="M19" s="98"/>
-      <x:c r="N19" s="98"/>
-      <x:c r="O19" s="98"/>
-      <x:c r="P19" s="98"/>
-      <x:c r="Q19" s="80"/>
-      <x:c r="R19" s="80"/>
-      <x:c r="S19" s="80"/>
+      <x:c r="A19" s="80" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B19" s="80" t="str">
+        <x:v>13285678</x:v>
+      </x:c>
+      <x:c r="C19" s="83" t="str">
+        <x:v>13.10.2026 18:37</x:v>
+      </x:c>
+      <x:c r="D19" s="80" t="str">
+        <x:v>Персидский залив - Клубный чемпионат</x:v>
+      </x:c>
+      <x:c r="E19" s="80" t="str">
+        <x:v>Катар СК - Аль-Завра</x:v>
+      </x:c>
+      <x:c r="F19" s="86" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G19" s="80" t="str">
+        <x:v>1:1</x:v>
+      </x:c>
+      <x:c r="H19" s="95" t="str">
+        <x:v>После свежего ответного гола матч снова открыт для обеих команд</x:v>
+      </x:c>
+      <x:c r="I19" s="95" t="str">
+        <x:v>ТБ 3,0 всего матча</x:v>
+      </x:c>
+      <x:c r="J19" s="96" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="K19" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L19" s="98" t="str">
+        <x:v>Владение 50:50; удары в створ 1:3; мимо 4:2; угловые 1:3; опасные атаки 11:13</x:v>
+      </x:c>
+      <x:c r="M19" s="98" t="str">
+        <x:v>За 14 минут: гол Катар СК; удары в створ +1:+1; удары мимо +1:0; угловые +1:+1; опасные атаки +2:+2</x:v>
+      </x:c>
+      <x:c r="N19" s="98" t="str">
+        <x:v>Свежий ответный гол; равные предматчевые шансы; обеим командам есть смысл искать победу</x:v>
+      </x:c>
+      <x:c r="O19" s="98" t="str">
+        <x:v>Суммарная угроза умеренная; один дополнительный гол даст только возврат; уже 51-я минута</x:v>
+      </x:c>
+      <x:c r="P19" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q19" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R19" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S19" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T19" s="80"/>
       <x:c r="U19" s="80"/>
       <x:c r="V19" s="89" t="str">
-        <x:f>IF(U19="Выигрыш",J19-1,IF(U19="Поражение",-1,IF(U19="Возврат",0,IF(U19="Полувыигрыш",(J19-1)/2,IF(U19="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U19="","",IF(U19="Плюс",J19-1,IF(U19="Минус",-1,IF(U19="Возврат",0,IF(U19="Полуплюс",(J19-1)/2,IF(U19="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W19" s="80" t="str">
         <x:f>IF(A19="","",IF(U19="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X19" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X19" s="98" t="str">
+        <x:v>Умеренный кандидат после свежего ответного гола</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="80"/>
-      <x:c r="B20" s="80"/>
-      <x:c r="C20" s="83"/>
-      <x:c r="D20" s="80"/>
-      <x:c r="E20" s="80"/>
-      <x:c r="F20" s="86"/>
-      <x:c r="G20" s="80"/>
-      <x:c r="H20" s="95"/>
-      <x:c r="I20" s="95"/>
-      <x:c r="J20" s="96"/>
-      <x:c r="K20" s="97"/>
-      <x:c r="L20" s="98"/>
-      <x:c r="M20" s="98"/>
-      <x:c r="N20" s="98"/>
-      <x:c r="O20" s="98"/>
-      <x:c r="P20" s="98"/>
-      <x:c r="Q20" s="80"/>
-      <x:c r="R20" s="80"/>
-      <x:c r="S20" s="80"/>
+      <x:c r="A20" s="80" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B20" s="80" t="str">
+        <x:v>12325194</x:v>
+      </x:c>
+      <x:c r="C20" s="83" t="str">
+        <x:v>13.10.2026 18:43</x:v>
+      </x:c>
+      <x:c r="D20" s="80" t="str">
+        <x:v>Саудовская Аравия - Первый дивизион</x:v>
+      </x:c>
+      <x:c r="E20" s="80" t="str">
+        <x:v>Аль-Сакр - Аль-Джабалайн</x:v>
+      </x:c>
+      <x:c r="F20" s="86" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G20" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H20" s="95" t="str">
+        <x:v>Гости устойчиво давят и подтверждают статус фаворита</x:v>
+      </x:c>
+      <x:c r="I20" s="95" t="str">
+        <x:v>ТБ 1,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J20" s="96" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="K20" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L20" s="98" t="str">
+        <x:v>Владение 35:65; удары в створ 0:3; мимо 2:7; опасные атаки 11:36</x:v>
+      </x:c>
+      <x:c r="M20" s="98" t="str">
+        <x:v>Свежий снимок без сопоставимого предыдущего отбора</x:v>
+      </x:c>
+      <x:c r="N20" s="98" t="str">
+        <x:v>Аль-Джабалайн ведёт по ударам 10:2 и опасным атакам 36:11; низкая защитная линия тотала</x:v>
+      </x:c>
+      <x:c r="O20" s="98" t="str">
+        <x:v>Голов к 27-й минуте нет; угловых нет; для полного плюса нужны два гола</x:v>
+      </x:c>
+      <x:c r="P20" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q20" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R20" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S20" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T20" s="80"/>
       <x:c r="U20" s="80"/>
       <x:c r="V20" s="89" t="str">
-        <x:f>IF(U20="Выигрыш",J20-1,IF(U20="Поражение",-1,IF(U20="Возврат",0,IF(U20="Полувыигрыш",(J20-1)/2,IF(U20="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U20="","",IF(U20="Плюс",J20-1,IF(U20="Минус",-1,IF(U20="Возврат",0,IF(U20="Полуплюс",(J20-1)/2,IF(U20="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W20" s="80" t="str">
         <x:f>IF(A20="","",IF(U20="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X20" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X20" s="98" t="str">
+        <x:v>Сильное давление фаворита при низкой линии</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="80"/>
-      <x:c r="B21" s="80"/>
-      <x:c r="C21" s="83"/>
-      <x:c r="D21" s="80"/>
-      <x:c r="E21" s="80"/>
-      <x:c r="F21" s="86"/>
-      <x:c r="G21" s="80"/>
-      <x:c r="H21" s="95"/>
-      <x:c r="I21" s="95"/>
-      <x:c r="J21" s="96"/>
-      <x:c r="K21" s="97"/>
-      <x:c r="L21" s="98"/>
-      <x:c r="M21" s="98"/>
-      <x:c r="N21" s="98"/>
-      <x:c r="O21" s="98"/>
-      <x:c r="P21" s="98"/>
-      <x:c r="Q21" s="80"/>
-      <x:c r="R21" s="80"/>
-      <x:c r="S21" s="80"/>
+      <x:c r="A21" s="80" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B21" s="80" t="str">
+        <x:v>12471952</x:v>
+      </x:c>
+      <x:c r="C21" s="83" t="str">
+        <x:v>13.10.2026 18:43</x:v>
+      </x:c>
+      <x:c r="D21" s="80" t="str">
+        <x:v>Израиль - Юношеская лига</x:v>
+      </x:c>
+      <x:c r="E21" s="80" t="str">
+        <x:v>Хапоэль Ришон-ле-Цион U19 - Хапоэль Раанана U19</x:v>
+      </x:c>
+      <x:c r="F21" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G21" s="80" t="str">
+        <x:v>1:0</x:v>
+      </x:c>
+      <x:c r="H21" s="95" t="str">
+        <x:v>Юношеский матч сохраняет двустороннюю атакующую активность</x:v>
+      </x:c>
+      <x:c r="I21" s="95" t="str">
+        <x:v>ТБ 2,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J21" s="96" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="K21" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L21" s="98" t="str">
+        <x:v>Владение 46:54; удары в створ 3:1; мимо 0:2; угловые 2:3; опасные атаки 32:22</x:v>
+      </x:c>
+      <x:c r="M21" s="98" t="str">
+        <x:v>Свежий снимок без сопоставимого предыдущего отбора</x:v>
+      </x:c>
+      <x:c r="N21" s="98" t="str">
+        <x:v>Четыре удара в створ и 54 опасные атаки; пять угловых; линия допускает полуплюс при трёх голах</x:v>
+      </x:c>
+      <x:c r="O21" s="98" t="str">
+        <x:v>До перерыва забит один гол; для полного плюса нужны ещё три; качество моментов без xG неизвестно</x:v>
+      </x:c>
+      <x:c r="P21" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q21" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R21" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S21" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T21" s="80"/>
       <x:c r="U21" s="80"/>
       <x:c r="V21" s="89" t="str">
-        <x:f>IF(U21="Выигрыш",J21-1,IF(U21="Поражение",-1,IF(U21="Возврат",0,IF(U21="Полувыигрыш",(J21-1)/2,IF(U21="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U21="","",IF(U21="Плюс",J21-1,IF(U21="Минус",-1,IF(U21="Возврат",0,IF(U21="Полуплюс",(J21-1)/2,IF(U21="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W21" s="80" t="str">
         <x:f>IF(A21="","",IF(U21="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X21" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X21" s="98" t="str">
+        <x:v>Новый юношеский кандидат текущего снимка</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="80"/>

--- a/Live ТБ/Live ТБ.xlsx
+++ b/Live ТБ/Live ТБ.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R3b16fbb84a7a44a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R8d7d23fb87c24003"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="Rfce400a58ee24e13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R39963276a7664700"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="Rde90f5859bde479d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="Rbfcfc3db7aa4402d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -820,7 +820,7 @@
       </x:c>
       <x:c r="B7" s="57" t="n">
         <x:f>COUNTA('Реестр'!$A$6:$A$505)</x:f>
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="55"/>
       <x:c r="D7" s="58" t="str">
@@ -897,7 +897,7 @@
       </x:c>
       <x:c r="B12" s="57" t="n">
         <x:f>COUNTIF('Реестр'!$W$6:$W$505,"Открыт")</x:f>
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C12" s="55"/>
       <x:c r="D12" s="61"/>
@@ -941,7 +941,7 @@
       </x:c>
       <x:c r="B15" s="64" t="n">
         <x:f>IF(B7=0,"",AVERAGEIF('Реестр'!$A$6:$A$505,"&gt;0",'Реестр'!$J$6:$J$505))</x:f>
-        <x:v>1.8796874999999997</x:v>
+        <x:v>1.8797619047619045</x:v>
       </x:c>
       <x:c r="C15" s="55"/>
       <x:c r="D15" s="55"/>
@@ -955,7 +955,7 @@
         <x:v>Дата последнего выбора</x:v>
       </x:c>
       <x:c r="B16" s="70" t="str">
-        <x:v>13.10.2026 18:43</x:v>
+        <x:v>13.10.2026 21:27</x:v>
       </x:c>
       <x:c r="C16" s="55"/>
       <x:c r="D16" s="55"/>
@@ -2301,154 +2301,359 @@
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="80"/>
-      <x:c r="B22" s="80"/>
-      <x:c r="C22" s="83"/>
-      <x:c r="D22" s="80"/>
-      <x:c r="E22" s="80"/>
-      <x:c r="F22" s="86"/>
-      <x:c r="G22" s="80"/>
-      <x:c r="H22" s="95"/>
-      <x:c r="I22" s="95"/>
-      <x:c r="J22" s="96"/>
-      <x:c r="K22" s="97"/>
-      <x:c r="L22" s="98"/>
-      <x:c r="M22" s="98"/>
-      <x:c r="N22" s="98"/>
-      <x:c r="O22" s="98"/>
-      <x:c r="P22" s="98"/>
-      <x:c r="Q22" s="80"/>
-      <x:c r="R22" s="80"/>
-      <x:c r="S22" s="80"/>
+      <x:c r="A22" s="80" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B22" s="80" t="str">
+        <x:v>12407691</x:v>
+      </x:c>
+      <x:c r="C22" s="83" t="str">
+        <x:v>13.10.2026 21:27</x:v>
+      </x:c>
+      <x:c r="D22" s="80" t="str">
+        <x:v>Англия - Трофей Английской лиги</x:v>
+      </x:c>
+      <x:c r="E22" s="80" t="str">
+        <x:v>Джиллингем - Брайтон U21</x:v>
+      </x:c>
+      <x:c r="F22" s="86" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G22" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H22" s="95" t="str">
+        <x:v>Джиллингем создаёт моменты, а молодёжный Брайтон сохраняет открытый сценарий</x:v>
+      </x:c>
+      <x:c r="I22" s="95" t="str">
+        <x:v>ТБ 2,25 всего матча</x:v>
+      </x:c>
+      <x:c r="J22" s="96" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="K22" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L22" s="98" t="str">
+        <x:v>Удары 5; в створ 3; угловые 4; xG Джиллингема 0,75</x:v>
+      </x:c>
+      <x:c r="M22" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N22" s="98" t="str">
+        <x:v>Три удара в створ и четыре угловых к 27-й минуте; хозяева уже создали 0,75 xG; молодёжный соперник</x:v>
+      </x:c>
+      <x:c r="O22" s="98" t="str">
+        <x:v>Счёт 0:0; xG Брайтона не получен; для полного выигрыша нужны три гола</x:v>
+      </x:c>
+      <x:c r="P22" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q22" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R22" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S22" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T22" s="80"/>
       <x:c r="U22" s="80"/>
       <x:c r="V22" s="89" t="str">
-        <x:f>IF(U22="Выигрыш",J22-1,IF(U22="Поражение",-1,IF(U22="Возврат",0,IF(U22="Полувыигрыш",(J22-1)/2,IF(U22="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U22="","",IF(U22="Плюс",J22-1,IF(U22="Минус",-1,IF(U22="Возврат",0,IF(U22="Полуплюс",(J22-1)/2,IF(U22="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W22" s="80" t="str">
         <x:f>IF(A22="","",IF(U22="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X22" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X22" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:27 МСК; при ровно двух дополнительных голах ТБ 2,25 даёт полуминус</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="80"/>
-      <x:c r="B23" s="80"/>
-      <x:c r="C23" s="83"/>
-      <x:c r="D23" s="80"/>
-      <x:c r="E23" s="80"/>
-      <x:c r="F23" s="86"/>
-      <x:c r="G23" s="80"/>
-      <x:c r="H23" s="95"/>
-      <x:c r="I23" s="95"/>
-      <x:c r="J23" s="96"/>
-      <x:c r="K23" s="97"/>
-      <x:c r="L23" s="98"/>
-      <x:c r="M23" s="98"/>
-      <x:c r="N23" s="98"/>
-      <x:c r="O23" s="98"/>
-      <x:c r="P23" s="98"/>
-      <x:c r="Q23" s="80"/>
-      <x:c r="R23" s="80"/>
-      <x:c r="S23" s="80"/>
+      <x:c r="A23" s="80" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B23" s="80" t="str">
+        <x:v>12403135</x:v>
+      </x:c>
+      <x:c r="C23" s="83" t="str">
+        <x:v>13.10.2026 21:27</x:v>
+      </x:c>
+      <x:c r="D23" s="80" t="str">
+        <x:v>Англия - Кубок Национальной лиги</x:v>
+      </x:c>
+      <x:c r="E23" s="80" t="str">
+        <x:v>Гейтсхед - Вулверхэмптон U21</x:v>
+      </x:c>
+      <x:c r="F23" s="86" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G23" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H23" s="95" t="str">
+        <x:v>Равная открытая игра с атакующей молодёжной командой гостей</x:v>
+      </x:c>
+      <x:c r="I23" s="95" t="str">
+        <x:v>ТБ 2,5 всего матча</x:v>
+      </x:c>
+      <x:c r="J23" s="96" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="K23" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L23" s="98" t="str">
+        <x:v>Удары 6; в створ 3; угловые 3; опасные атаки 32:31</x:v>
+      </x:c>
+      <x:c r="M23" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N23" s="98" t="str">
+        <x:v>Три удара в створ и равная активность обеих команд; впереди более часа игры</x:v>
+      </x:c>
+      <x:c r="O23" s="98" t="str">
+        <x:v>Голов пока нет; качество моментов и xG недоступны; нужны три гола</x:v>
+      </x:c>
+      <x:c r="P23" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q23" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R23" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S23" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T23" s="80"/>
       <x:c r="U23" s="80"/>
       <x:c r="V23" s="89" t="str">
-        <x:f>IF(U23="Выигрыш",J23-1,IF(U23="Поражение",-1,IF(U23="Возврат",0,IF(U23="Полувыигрыш",(J23-1)/2,IF(U23="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U23="","",IF(U23="Плюс",J23-1,IF(U23="Минус",-1,IF(U23="Возврат",0,IF(U23="Полуплюс",(J23-1)/2,IF(U23="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W23" s="80" t="str">
         <x:f>IF(A23="","",IF(U23="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X23" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X23" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:27 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="80"/>
-      <x:c r="B24" s="80"/>
-      <x:c r="C24" s="83"/>
-      <x:c r="D24" s="80"/>
-      <x:c r="E24" s="80"/>
-      <x:c r="F24" s="86"/>
-      <x:c r="G24" s="80"/>
-      <x:c r="H24" s="95"/>
-      <x:c r="I24" s="95"/>
-      <x:c r="J24" s="96"/>
-      <x:c r="K24" s="97"/>
-      <x:c r="L24" s="98"/>
-      <x:c r="M24" s="98"/>
-      <x:c r="N24" s="98"/>
-      <x:c r="O24" s="98"/>
-      <x:c r="P24" s="98"/>
-      <x:c r="Q24" s="80"/>
-      <x:c r="R24" s="80"/>
-      <x:c r="S24" s="80"/>
+      <x:c r="A24" s="80" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B24" s="80" t="str">
+        <x:v>12403105</x:v>
+      </x:c>
+      <x:c r="C24" s="83" t="str">
+        <x:v>13.10.2026 21:27</x:v>
+      </x:c>
+      <x:c r="D24" s="80" t="str">
+        <x:v>Англия - Кубок Национальной лиги</x:v>
+      </x:c>
+      <x:c r="E24" s="80" t="str">
+        <x:v>Бостон Юнайтед - Саутгемптон U21</x:v>
+      </x:c>
+      <x:c r="F24" s="86" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G24" s="80" t="str">
+        <x:v>3:2</x:v>
+      </x:c>
+      <x:c r="H24" s="95" t="str">
+        <x:v>Результативная конкурентная игра продолжается при счёте с разницей в один гол</x:v>
+      </x:c>
+      <x:c r="I24" s="95" t="str">
+        <x:v>ТБ 7,5 всего матча</x:v>
+      </x:c>
+      <x:c r="J24" s="96" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="K24" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L24" s="98" t="str">
+        <x:v>Удары 10; в створ 6; угловые 5; опасные атаки 30:24</x:v>
+      </x:c>
+      <x:c r="M24" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N24" s="98" t="str">
+        <x:v>Пять голов к 27-й минуте; счёт 3:2 не закрывает мотивацию; шесть ударов в створ</x:v>
+      </x:c>
+      <x:c r="O24" s="98" t="str">
+        <x:v>Ранняя реализация может резко снизиться; высокая итоговая линия; нужны ещё три гола</x:v>
+      </x:c>
+      <x:c r="P24" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q24" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R24" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S24" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T24" s="80"/>
       <x:c r="U24" s="80"/>
       <x:c r="V24" s="89" t="str">
-        <x:f>IF(U24="Выигрыш",J24-1,IF(U24="Поражение",-1,IF(U24="Возврат",0,IF(U24="Полувыигрыш",(J24-1)/2,IF(U24="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U24="","",IF(U24="Плюс",J24-1,IF(U24="Минус",-1,IF(U24="Возврат",0,IF(U24="Полуплюс",(J24-1)/2,IF(U24="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W24" s="80" t="str">
         <x:f>IF(A24="","",IF(U24="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X24" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X24" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:27 МСК; повышенный риск после пяти ранних голов</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="80"/>
-      <x:c r="B25" s="80"/>
-      <x:c r="C25" s="83"/>
-      <x:c r="D25" s="80"/>
-      <x:c r="E25" s="80"/>
-      <x:c r="F25" s="86"/>
-      <x:c r="G25" s="80"/>
-      <x:c r="H25" s="95"/>
-      <x:c r="I25" s="95"/>
-      <x:c r="J25" s="96"/>
-      <x:c r="K25" s="97"/>
-      <x:c r="L25" s="98"/>
-      <x:c r="M25" s="98"/>
-      <x:c r="N25" s="98"/>
-      <x:c r="O25" s="98"/>
-      <x:c r="P25" s="98"/>
-      <x:c r="Q25" s="80"/>
-      <x:c r="R25" s="80"/>
-      <x:c r="S25" s="80"/>
+      <x:c r="A25" s="80" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B25" s="80" t="str">
+        <x:v>13217859</x:v>
+      </x:c>
+      <x:c r="C25" s="83" t="str">
+        <x:v>13.10.2026 21:27</x:v>
+      </x:c>
+      <x:c r="D25" s="80" t="str">
+        <x:v>Аргентина - Лига профессиональных резервов</x:v>
+      </x:c>
+      <x:c r="E25" s="80" t="str">
+        <x:v>Банфилд резерв - Химнасия Ла-Плата резерв</x:v>
+      </x:c>
+      <x:c r="F25" s="86" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G25" s="80" t="str">
+        <x:v>1:0</x:v>
+      </x:c>
+      <x:c r="H25" s="95" t="str">
+        <x:v>Проигрывающая Химнасия контролирует мяч и поддерживает двусторонний сценарий</x:v>
+      </x:c>
+      <x:c r="I25" s="95" t="str">
+        <x:v>ТБ 2,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J25" s="96" t="n">
+        <x:v>1.925</x:v>
+      </x:c>
+      <x:c r="K25" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L25" s="98" t="str">
+        <x:v>Владение 33:67; удары 7; в створ 3; опасные атаки 20:22</x:v>
+      </x:c>
+      <x:c r="M25" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N25" s="98" t="str">
+        <x:v>Химнасия уступает, но владеет 67% мяча; семь ударов и три в створ к 26-й минуте</x:v>
+      </x:c>
+      <x:c r="O25" s="98" t="str">
+        <x:v>Угловых нет; качество моментов без xG неизвестно; два гола дадут только полувыигрыш</x:v>
+      </x:c>
+      <x:c r="P25" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q25" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R25" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S25" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T25" s="80"/>
       <x:c r="U25" s="80"/>
       <x:c r="V25" s="89" t="str">
-        <x:f>IF(U25="Выигрыш",J25-1,IF(U25="Поражение",-1,IF(U25="Возврат",0,IF(U25="Полувыигрыш",(J25-1)/2,IF(U25="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U25="","",IF(U25="Плюс",J25-1,IF(U25="Минус",-1,IF(U25="Возврат",0,IF(U25="Полуплюс",(J25-1)/2,IF(U25="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W25" s="80" t="str">
         <x:f>IF(A25="","",IF(U25="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X25" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X25" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:27 МСК; два дополнительных гола дают полувыигрыш</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="80"/>
-      <x:c r="B26" s="80"/>
-      <x:c r="C26" s="83"/>
-      <x:c r="D26" s="80"/>
-      <x:c r="E26" s="80"/>
-      <x:c r="F26" s="86"/>
-      <x:c r="G26" s="80"/>
-      <x:c r="H26" s="95"/>
-      <x:c r="I26" s="95"/>
-      <x:c r="J26" s="96"/>
-      <x:c r="K26" s="97"/>
-      <x:c r="L26" s="98"/>
-      <x:c r="M26" s="98"/>
-      <x:c r="N26" s="98"/>
-      <x:c r="O26" s="98"/>
-      <x:c r="P26" s="98"/>
-      <x:c r="Q26" s="80"/>
-      <x:c r="R26" s="80"/>
-      <x:c r="S26" s="80"/>
+      <x:c r="A26" s="80" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B26" s="80" t="str">
+        <x:v>12375322</x:v>
+      </x:c>
+      <x:c r="C26" s="83" t="str">
+        <x:v>13.10.2026 21:27</x:v>
+      </x:c>
+      <x:c r="D26" s="80" t="str">
+        <x:v>Египет - Первый дивизион</x:v>
+      </x:c>
+      <x:c r="E26" s="80" t="str">
+        <x:v>Петроджет - Вади Дегла</x:v>
+      </x:c>
+      <x:c r="F26" s="86" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G26" s="80" t="str">
+        <x:v>1:2</x:v>
+      </x:c>
+      <x:c r="H26" s="95" t="str">
+        <x:v>Петроджет отыгрывается против ведущего соперника, оставшегося в меньшинстве</x:v>
+      </x:c>
+      <x:c r="I26" s="95" t="str">
+        <x:v>ТБ 4 всего матча</x:v>
+      </x:c>
+      <x:c r="J26" s="96" t="n">
+        <x:v>1.975</x:v>
+      </x:c>
+      <x:c r="K26" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L26" s="98" t="str">
+        <x:v>Удары 19; в створ 10; угловые 7; xG 0,76:0,92; удаления 0:1</x:v>
+      </x:c>
+      <x:c r="M26" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N26" s="98" t="str">
+        <x:v>Десять ударов в створ и 1,68 суммарного xG; Петроджет сократил счёт и получил численное преимущество</x:v>
+      </x:c>
+      <x:c r="O26" s="98" t="str">
+        <x:v>59-я минута; один дополнительный гол даёт только возврат; удаление может снизить контратакующую угрозу Вади Дегла</x:v>
+      </x:c>
+      <x:c r="P26" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q26" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R26" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S26" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T26" s="80"/>
       <x:c r="U26" s="80"/>
       <x:c r="V26" s="89" t="str">
-        <x:f>IF(U26="Выигрыш",J26-1,IF(U26="Поражение",-1,IF(U26="Возврат",0,IF(U26="Полувыигрыш",(J26-1)/2,IF(U26="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U26="","",IF(U26="Плюс",J26-1,IF(U26="Минус",-1,IF(U26="Возврат",0,IF(U26="Полуплюс",(J26-1)/2,IF(U26="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W26" s="80" t="str">
         <x:f>IF(A26="","",IF(U26="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X26" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X26" s="98" t="str">
+        <x:v>Лучший текущий сценарий снимка; быстрый live-отбор 21:27 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="80"/>

--- a/Live ТБ/Live ТБ.xlsx
+++ b/Live ТБ/Live ТБ.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R39963276a7664700"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="Rde90f5859bde479d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="Rbfcfc3db7aa4402d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R081d98394ae44fd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R999c901eb4b84c44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="R4cc66e301cb54fdb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -820,7 +820,7 @@
       </x:c>
       <x:c r="B7" s="57" t="n">
         <x:f>COUNTA('Реестр'!$A$6:$A$505)</x:f>
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C7" s="55"/>
       <x:c r="D7" s="58" t="str">
@@ -897,7 +897,7 @@
       </x:c>
       <x:c r="B12" s="57" t="n">
         <x:f>COUNTIF('Реестр'!$W$6:$W$505,"Открыт")</x:f>
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C12" s="55"/>
       <x:c r="D12" s="61"/>
@@ -941,7 +941,7 @@
       </x:c>
       <x:c r="B15" s="64" t="n">
         <x:f>IF(B7=0,"",AVERAGEIF('Реестр'!$A$6:$A$505,"&gt;0",'Реестр'!$J$6:$J$505))</x:f>
-        <x:v>1.8797619047619045</x:v>
+        <x:v>1.8879032258064519</x:v>
       </x:c>
       <x:c r="C15" s="55"/>
       <x:c r="D15" s="55"/>
@@ -955,7 +955,7 @@
         <x:v>Дата последнего выбора</x:v>
       </x:c>
       <x:c r="B16" s="70" t="str">
-        <x:v>13.10.2026 21:27</x:v>
+        <x:v>13.10.2026 21:37</x:v>
       </x:c>
       <x:c r="C16" s="55"/>
       <x:c r="D16" s="55"/>
@@ -2656,304 +2656,714 @@
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="80"/>
-      <x:c r="B27" s="80"/>
-      <x:c r="C27" s="83"/>
-      <x:c r="D27" s="80"/>
-      <x:c r="E27" s="80"/>
-      <x:c r="F27" s="86"/>
-      <x:c r="G27" s="80"/>
-      <x:c r="H27" s="95"/>
-      <x:c r="I27" s="95"/>
-      <x:c r="J27" s="96"/>
-      <x:c r="K27" s="97"/>
-      <x:c r="L27" s="98"/>
-      <x:c r="M27" s="98"/>
-      <x:c r="N27" s="98"/>
-      <x:c r="O27" s="98"/>
-      <x:c r="P27" s="98"/>
-      <x:c r="Q27" s="80"/>
-      <x:c r="R27" s="80"/>
-      <x:c r="S27" s="80"/>
+      <x:c r="A27" s="80" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B27" s="80" t="str">
+        <x:v>12407688</x:v>
+      </x:c>
+      <x:c r="C27" s="83" t="str">
+        <x:v>13.10.2026 21:37</x:v>
+      </x:c>
+      <x:c r="D27" s="80" t="str">
+        <x:v>Англия - Трофей Английской лиги</x:v>
+      </x:c>
+      <x:c r="E27" s="80" t="str">
+        <x:v>Олдем - Лидс U21</x:v>
+      </x:c>
+      <x:c r="F27" s="86" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G27" s="80" t="str">
+        <x:v>1:1</x:v>
+      </x:c>
+      <x:c r="H27" s="95" t="str">
+        <x:v>Открытый обмен при высокой фактической угрозе и инициативе молодёжного Лидса</x:v>
+      </x:c>
+      <x:c r="I27" s="95" t="str">
+        <x:v>ТБ 4,25 всего матча</x:v>
+      </x:c>
+      <x:c r="J27" s="96" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K27" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L27" s="98" t="str">
+        <x:v>Владение 36:64; удары 10; в створ 4; угловые 6; xG 1,12:0,83</x:v>
+      </x:c>
+      <x:c r="M27" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N27" s="98" t="str">
+        <x:v>Суммарный xG 1,95 и шесть угловых к 37-й минуте; счёт остаётся конкурентным</x:v>
+      </x:c>
+      <x:c r="O27" s="98" t="str">
+        <x:v>Высокая линия; для полного выигрыша нужны ещё три гола</x:v>
+      </x:c>
+      <x:c r="P27" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q27" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R27" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S27" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T27" s="80"/>
       <x:c r="U27" s="80"/>
       <x:c r="V27" s="89" t="str">
-        <x:f>IF(U27="Выигрыш",J27-1,IF(U27="Поражение",-1,IF(U27="Возврат",0,IF(U27="Полувыигрыш",(J27-1)/2,IF(U27="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U27="","",IF(U27="Плюс",J27-1,IF(U27="Минус",-1,IF(U27="Возврат",0,IF(U27="Полуплюс",(J27-1)/2,IF(U27="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W27" s="80" t="str">
         <x:f>IF(A27="","",IF(U27="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X27" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X27" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:37 МСК; один из трёх лучших кандидатов снимка</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="80"/>
-      <x:c r="B28" s="80"/>
-      <x:c r="C28" s="83"/>
-      <x:c r="D28" s="80"/>
-      <x:c r="E28" s="80"/>
-      <x:c r="F28" s="86"/>
-      <x:c r="G28" s="80"/>
-      <x:c r="H28" s="95"/>
-      <x:c r="I28" s="95"/>
-      <x:c r="J28" s="96"/>
-      <x:c r="K28" s="97"/>
-      <x:c r="L28" s="98"/>
-      <x:c r="M28" s="98"/>
-      <x:c r="N28" s="98"/>
-      <x:c r="O28" s="98"/>
-      <x:c r="P28" s="98"/>
-      <x:c r="Q28" s="80"/>
-      <x:c r="R28" s="80"/>
-      <x:c r="S28" s="80"/>
+      <x:c r="A28" s="80" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B28" s="80" t="str">
+        <x:v>13285866</x:v>
+      </x:c>
+      <x:c r="C28" s="83" t="str">
+        <x:v>13.10.2026 21:37</x:v>
+      </x:c>
+      <x:c r="D28" s="80" t="str">
+        <x:v>Бразилия - Кубок Гояс U20</x:v>
+      </x:c>
+      <x:c r="E28" s="80" t="str">
+        <x:v>Апаресида U20 - Итаусу U20</x:v>
+      </x:c>
+      <x:c r="F28" s="86" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G28" s="80" t="str">
+        <x:v>0:1</x:v>
+      </x:c>
+      <x:c r="H28" s="95" t="str">
+        <x:v>Двусторонняя активность сохраняется, хозяева вынуждены отыгрываться</x:v>
+      </x:c>
+      <x:c r="I28" s="95" t="str">
+        <x:v>ТБ 2,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J28" s="96" t="n">
+        <x:v>1.825</x:v>
+      </x:c>
+      <x:c r="K28" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L28" s="98" t="str">
+        <x:v>Удары 9; в створ 5; угловые 3; опасные атаки 23:24</x:v>
+      </x:c>
+      <x:c r="M28" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N28" s="98" t="str">
+        <x:v>Пять ударов в створ и равная атакующая активность; молодёжный турнир</x:v>
+      </x:c>
+      <x:c r="O28" s="98" t="str">
+        <x:v>Два дополнительных гола дают только полувыигрыш; xG недоступен</x:v>
+      </x:c>
+      <x:c r="P28" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q28" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R28" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S28" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T28" s="80"/>
       <x:c r="U28" s="80"/>
       <x:c r="V28" s="89" t="str">
-        <x:f>IF(U28="Выигрыш",J28-1,IF(U28="Поражение",-1,IF(U28="Возврат",0,IF(U28="Полувыигрыш",(J28-1)/2,IF(U28="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U28="","",IF(U28="Плюс",J28-1,IF(U28="Минус",-1,IF(U28="Возврат",0,IF(U28="Полуплюс",(J28-1)/2,IF(U28="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W28" s="80" t="str">
         <x:f>IF(A28="","",IF(U28="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X28" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X28" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:37 МСК; один из трёх лучших кандидатов снимка</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="80"/>
-      <x:c r="B29" s="80"/>
-      <x:c r="C29" s="83"/>
-      <x:c r="D29" s="80"/>
-      <x:c r="E29" s="80"/>
-      <x:c r="F29" s="86"/>
-      <x:c r="G29" s="80"/>
-      <x:c r="H29" s="95"/>
-      <x:c r="I29" s="95"/>
-      <x:c r="J29" s="96"/>
-      <x:c r="K29" s="97"/>
-      <x:c r="L29" s="98"/>
-      <x:c r="M29" s="98"/>
-      <x:c r="N29" s="98"/>
-      <x:c r="O29" s="98"/>
-      <x:c r="P29" s="98"/>
-      <x:c r="Q29" s="80"/>
-      <x:c r="R29" s="80"/>
-      <x:c r="S29" s="80"/>
+      <x:c r="A29" s="80" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B29" s="80" t="str">
+        <x:v>12403337</x:v>
+      </x:c>
+      <x:c r="C29" s="83" t="str">
+        <x:v>13.10.2026 21:37</x:v>
+      </x:c>
+      <x:c r="D29" s="80" t="str">
+        <x:v>Англия - Кубок Национальной лиги</x:v>
+      </x:c>
+      <x:c r="E29" s="80" t="str">
+        <x:v>Хартлпул - Ньюкасл U21</x:v>
+      </x:c>
+      <x:c r="F29" s="86" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G29" s="80" t="str">
+        <x:v>1:2</x:v>
+      </x:c>
+      <x:c r="H29" s="95" t="str">
+        <x:v>Конкурентный счёт и высокая двусторонняя ударная активность</x:v>
+      </x:c>
+      <x:c r="I29" s="95" t="str">
+        <x:v>ТБ 5,25 всего матча</x:v>
+      </x:c>
+      <x:c r="J29" s="96" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="K29" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L29" s="98" t="str">
+        <x:v>Удары 12; в створ 6; угловые 5; опасные атаки 18:13</x:v>
+      </x:c>
+      <x:c r="M29" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N29" s="98" t="str">
+        <x:v>Шесть ударов в створ и пять угловых; отстающий Хартлпул сохраняет мотивацию</x:v>
+      </x:c>
+      <x:c r="O29" s="98" t="str">
+        <x:v>Линия уже учитывает три ранних гола; нужны ещё три гола</x:v>
+      </x:c>
+      <x:c r="P29" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q29" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R29" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S29" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T29" s="80"/>
       <x:c r="U29" s="80"/>
       <x:c r="V29" s="89" t="str">
-        <x:f>IF(U29="Выигрыш",J29-1,IF(U29="Поражение",-1,IF(U29="Возврат",0,IF(U29="Полувыигрыш",(J29-1)/2,IF(U29="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U29="","",IF(U29="Плюс",J29-1,IF(U29="Минус",-1,IF(U29="Возврат",0,IF(U29="Полуплюс",(J29-1)/2,IF(U29="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W29" s="80" t="str">
         <x:f>IF(A29="","",IF(U29="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X29" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X29" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:37 МСК; риск высокой линии</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="80"/>
-      <x:c r="B30" s="80"/>
-      <x:c r="C30" s="83"/>
-      <x:c r="D30" s="80"/>
-      <x:c r="E30" s="80"/>
-      <x:c r="F30" s="86"/>
-      <x:c r="G30" s="80"/>
-      <x:c r="H30" s="95"/>
-      <x:c r="I30" s="95"/>
-      <x:c r="J30" s="96"/>
-      <x:c r="K30" s="97"/>
-      <x:c r="L30" s="98"/>
-      <x:c r="M30" s="98"/>
-      <x:c r="N30" s="98"/>
-      <x:c r="O30" s="98"/>
-      <x:c r="P30" s="98"/>
-      <x:c r="Q30" s="80"/>
-      <x:c r="R30" s="80"/>
-      <x:c r="S30" s="80"/>
+      <x:c r="A30" s="80" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B30" s="80" t="str">
+        <x:v>12403104</x:v>
+      </x:c>
+      <x:c r="C30" s="83" t="str">
+        <x:v>13.10.2026 21:37</x:v>
+      </x:c>
+      <x:c r="D30" s="80" t="str">
+        <x:v>Англия - Кубок Национальной лиги</x:v>
+      </x:c>
+      <x:c r="E30" s="80" t="str">
+        <x:v>Саттон Юнайтед - Вест Бромвич U21</x:v>
+      </x:c>
+      <x:c r="F30" s="86" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G30" s="80" t="str">
+        <x:v>2:1</x:v>
+      </x:c>
+      <x:c r="H30" s="95" t="str">
+        <x:v>Саттон продолжает создавать моменты при конкурентном счёте</x:v>
+      </x:c>
+      <x:c r="I30" s="95" t="str">
+        <x:v>ТБ 5,25 всего матча</x:v>
+      </x:c>
+      <x:c r="J30" s="96" t="n">
+        <x:v>1.825</x:v>
+      </x:c>
+      <x:c r="K30" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L30" s="98" t="str">
+        <x:v>Удары 9; в створ 6; угловые 6; опасные атаки 29:6</x:v>
+      </x:c>
+      <x:c r="M30" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N30" s="98" t="str">
+        <x:v>Шесть ударов в створ и явное территориальное давление Саттона</x:v>
+      </x:c>
+      <x:c r="O30" s="98" t="str">
+        <x:v>Высокая линия; активность гостей слабая; нужны ещё три гола</x:v>
+      </x:c>
+      <x:c r="P30" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q30" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R30" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S30" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T30" s="80"/>
       <x:c r="U30" s="80"/>
       <x:c r="V30" s="89" t="str">
-        <x:f>IF(U30="Выигрыш",J30-1,IF(U30="Поражение",-1,IF(U30="Возврат",0,IF(U30="Полувыигрыш",(J30-1)/2,IF(U30="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U30="","",IF(U30="Плюс",J30-1,IF(U30="Минус",-1,IF(U30="Возврат",0,IF(U30="Полуплюс",(J30-1)/2,IF(U30="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W30" s="80" t="str">
         <x:f>IF(A30="","",IF(U30="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X30" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X30" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:37 МСК; риск высокой линии</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="80"/>
-      <x:c r="B31" s="80"/>
-      <x:c r="C31" s="83"/>
-      <x:c r="D31" s="80"/>
-      <x:c r="E31" s="80"/>
-      <x:c r="F31" s="86"/>
-      <x:c r="G31" s="80"/>
-      <x:c r="H31" s="95"/>
-      <x:c r="I31" s="95"/>
-      <x:c r="J31" s="96"/>
-      <x:c r="K31" s="97"/>
-      <x:c r="L31" s="98"/>
-      <x:c r="M31" s="98"/>
-      <x:c r="N31" s="98"/>
-      <x:c r="O31" s="98"/>
-      <x:c r="P31" s="98"/>
-      <x:c r="Q31" s="80"/>
-      <x:c r="R31" s="80"/>
-      <x:c r="S31" s="80"/>
+      <x:c r="A31" s="80" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B31" s="80" t="str">
+        <x:v>12319683</x:v>
+      </x:c>
+      <x:c r="C31" s="83" t="str">
+        <x:v>13.10.2026 21:37</x:v>
+      </x:c>
+      <x:c r="D31" s="80" t="str">
+        <x:v>ЮАР - Премьер-лига</x:v>
+      </x:c>
+      <x:c r="E31" s="80" t="str">
+        <x:v>Дурбан Сити - Амазулу</x:v>
+      </x:c>
+      <x:c r="F31" s="86" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G31" s="80" t="str">
+        <x:v>0:2</x:v>
+      </x:c>
+      <x:c r="H31" s="95" t="str">
+        <x:v>Дурбан вынужден раскрываться после двух пропущенных голов</x:v>
+      </x:c>
+      <x:c r="I31" s="95" t="str">
+        <x:v>ТБ 3,25 всего матча</x:v>
+      </x:c>
+      <x:c r="J31" s="96" t="n">
+        <x:v>1.975</x:v>
+      </x:c>
+      <x:c r="K31" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L31" s="98" t="str">
+        <x:v>Удары 9; в створ 4; угловые 7; опасные атаки 40:33</x:v>
+      </x:c>
+      <x:c r="M31" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N31" s="98" t="str">
+        <x:v>Семь угловых и 73 опасные атаки; два дополнительных гола дают полный выигрыш</x:v>
+      </x:c>
+      <x:c r="O31" s="98" t="str">
+        <x:v>Все четыре удара в створ у Амазулу; атакующая эффективность хозяев пока слабая</x:v>
+      </x:c>
+      <x:c r="P31" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q31" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R31" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S31" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T31" s="80"/>
       <x:c r="U31" s="80"/>
       <x:c r="V31" s="89" t="str">
-        <x:f>IF(U31="Выигрыш",J31-1,IF(U31="Поражение",-1,IF(U31="Возврат",0,IF(U31="Полувыигрыш",(J31-1)/2,IF(U31="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U31="","",IF(U31="Плюс",J31-1,IF(U31="Минус",-1,IF(U31="Возврат",0,IF(U31="Полуплюс",(J31-1)/2,IF(U31="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W31" s="80" t="str">
         <x:f>IF(A31="","",IF(U31="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X31" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X31" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:37 МСК; один из трёх лучших кандидатов снимка</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="80"/>
-      <x:c r="B32" s="80"/>
-      <x:c r="C32" s="83"/>
-      <x:c r="D32" s="80"/>
-      <x:c r="E32" s="80"/>
-      <x:c r="F32" s="86"/>
-      <x:c r="G32" s="80"/>
-      <x:c r="H32" s="95"/>
-      <x:c r="I32" s="95"/>
-      <x:c r="J32" s="96"/>
-      <x:c r="K32" s="97"/>
-      <x:c r="L32" s="98"/>
-      <x:c r="M32" s="98"/>
-      <x:c r="N32" s="98"/>
-      <x:c r="O32" s="98"/>
-      <x:c r="P32" s="98"/>
-      <x:c r="Q32" s="80"/>
-      <x:c r="R32" s="80"/>
-      <x:c r="S32" s="80"/>
+      <x:c r="A32" s="80" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B32" s="80" t="str">
+        <x:v>12319678</x:v>
+      </x:c>
+      <x:c r="C32" s="83" t="str">
+        <x:v>13.10.2026 21:37</x:v>
+      </x:c>
+      <x:c r="D32" s="80" t="str">
+        <x:v>ЮАР - Премьер-лига</x:v>
+      </x:c>
+      <x:c r="E32" s="80" t="str">
+        <x:v>Ричардс-Бей - Мамелоди Сандаунс</x:v>
+      </x:c>
+      <x:c r="F32" s="86" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G32" s="80" t="str">
+        <x:v>1:2</x:v>
+      </x:c>
+      <x:c r="H32" s="95" t="str">
+        <x:v>Доминирующий Мамелоди сохраняет давление при незакрытом счёте</x:v>
+      </x:c>
+      <x:c r="I32" s="95" t="str">
+        <x:v>ТБ 4,5 всего матча</x:v>
+      </x:c>
+      <x:c r="J32" s="96" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="K32" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L32" s="98" t="str">
+        <x:v>Владение 23:77; в створ 2:3; угловые 1:5; xG 0,32:1,07; ключевые передачи 1:13</x:v>
+      </x:c>
+      <x:c r="M32" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N32" s="98" t="str">
+        <x:v>Мамелоди полностью контролирует игру; для выигрыша нужны ещё два гола</x:v>
+      </x:c>
+      <x:c r="O32" s="98" t="str">
+        <x:v>Линия требует пять итоговых голов; хозяева почти не создают</x:v>
+      </x:c>
+      <x:c r="P32" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q32" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R32" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S32" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T32" s="80"/>
       <x:c r="U32" s="80"/>
       <x:c r="V32" s="89" t="str">
-        <x:f>IF(U32="Выигрыш",J32-1,IF(U32="Поражение",-1,IF(U32="Возврат",0,IF(U32="Полувыигрыш",(J32-1)/2,IF(U32="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U32="","",IF(U32="Плюс",J32-1,IF(U32="Минус",-1,IF(U32="Возврат",0,IF(U32="Полуплюс",(J32-1)/2,IF(U32="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W32" s="80" t="str">
         <x:f>IF(A32="","",IF(U32="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X32" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X32" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:37 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="80"/>
-      <x:c r="B33" s="80"/>
-      <x:c r="C33" s="83"/>
-      <x:c r="D33" s="80"/>
-      <x:c r="E33" s="80"/>
-      <x:c r="F33" s="86"/>
-      <x:c r="G33" s="80"/>
-      <x:c r="H33" s="95"/>
-      <x:c r="I33" s="95"/>
-      <x:c r="J33" s="96"/>
-      <x:c r="K33" s="97"/>
-      <x:c r="L33" s="98"/>
-      <x:c r="M33" s="98"/>
-      <x:c r="N33" s="98"/>
-      <x:c r="O33" s="98"/>
-      <x:c r="P33" s="98"/>
-      <x:c r="Q33" s="80"/>
-      <x:c r="R33" s="80"/>
-      <x:c r="S33" s="80"/>
+      <x:c r="A33" s="80" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B33" s="80" t="str">
+        <x:v>13246864</x:v>
+      </x:c>
+      <x:c r="C33" s="83" t="str">
+        <x:v>13.10.2026 21:37</x:v>
+      </x:c>
+      <x:c r="D33" s="80" t="str">
+        <x:v>Марокко - Ботола</x:v>
+      </x:c>
+      <x:c r="E33" s="80" t="str">
+        <x:v>РСБ Беркан - Ренессанс Земамра</x:v>
+      </x:c>
+      <x:c r="F33" s="86" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G33" s="80" t="str">
+        <x:v>0:2</x:v>
+      </x:c>
+      <x:c r="H33" s="95" t="str">
+        <x:v>Беркан уступает два мяча, но продолжает владеть инициативой</x:v>
+      </x:c>
+      <x:c r="I33" s="95" t="str">
+        <x:v>ТБ 3,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J33" s="96" t="n">
+        <x:v>1.975</x:v>
+      </x:c>
+      <x:c r="K33" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L33" s="98" t="str">
+        <x:v>Владение 68:32; удары 9; в створ 3; угловые 3; опасные атаки 31:9</x:v>
+      </x:c>
+      <x:c r="M33" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N33" s="98" t="str">
+        <x:v>Проигрывающий фаворит давит и вынужден раскрываться</x:v>
+      </x:c>
+      <x:c r="O33" s="98" t="str">
+        <x:v>Реализация моментов невысокая; два дополнительных гола дают только полувыигрыш</x:v>
+      </x:c>
+      <x:c r="P33" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q33" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R33" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S33" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T33" s="80"/>
       <x:c r="U33" s="80"/>
       <x:c r="V33" s="89" t="str">
-        <x:f>IF(U33="Выигрыш",J33-1,IF(U33="Поражение",-1,IF(U33="Возврат",0,IF(U33="Полувыигрыш",(J33-1)/2,IF(U33="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U33="","",IF(U33="Плюс",J33-1,IF(U33="Минус",-1,IF(U33="Возврат",0,IF(U33="Полуплюс",(J33-1)/2,IF(U33="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W33" s="80" t="str">
         <x:f>IF(A33="","",IF(U33="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X33" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X33" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:37 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="80"/>
-      <x:c r="B34" s="80"/>
-      <x:c r="C34" s="83"/>
-      <x:c r="D34" s="80"/>
-      <x:c r="E34" s="80"/>
-      <x:c r="F34" s="86"/>
-      <x:c r="G34" s="80"/>
-      <x:c r="H34" s="95"/>
-      <x:c r="I34" s="95"/>
-      <x:c r="J34" s="96"/>
-      <x:c r="K34" s="97"/>
-      <x:c r="L34" s="98"/>
-      <x:c r="M34" s="98"/>
-      <x:c r="N34" s="98"/>
-      <x:c r="O34" s="98"/>
-      <x:c r="P34" s="98"/>
-      <x:c r="Q34" s="80"/>
-      <x:c r="R34" s="80"/>
-      <x:c r="S34" s="80"/>
+      <x:c r="A34" s="80" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B34" s="80" t="str">
+        <x:v>13267993</x:v>
+      </x:c>
+      <x:c r="C34" s="83" t="str">
+        <x:v>13.10.2026 21:37</x:v>
+      </x:c>
+      <x:c r="D34" s="80" t="str">
+        <x:v>Бразилия - Чемпионат Пернамбуку U20</x:v>
+      </x:c>
+      <x:c r="E34" s="80" t="str">
+        <x:v>Америка ПЕ U20 - Ретро U20</x:v>
+      </x:c>
+      <x:c r="F34" s="86" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G34" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H34" s="95" t="str">
+        <x:v>Высокий объём атак при низкой линии тотала</x:v>
+      </x:c>
+      <x:c r="I34" s="95" t="str">
+        <x:v>ТБ 1,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J34" s="96" t="n">
+        <x:v>1.775</x:v>
+      </x:c>
+      <x:c r="K34" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L34" s="98" t="str">
+        <x:v>Удары 12; в створ 2; опасные атаки 31:42; владение 47:53</x:v>
+      </x:c>
+      <x:c r="M34" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N34" s="98" t="str">
+        <x:v>Двенадцать ударов и 73 опасные атаки; молодёжный матч; низкая линия</x:v>
+      </x:c>
+      <x:c r="O34" s="98" t="str">
+        <x:v>Только два удара в створ; при двух итоговых голах будет лишь полувыигрыш</x:v>
+      </x:c>
+      <x:c r="P34" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q34" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R34" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S34" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T34" s="80"/>
       <x:c r="U34" s="80"/>
       <x:c r="V34" s="89" t="str">
-        <x:f>IF(U34="Выигрыш",J34-1,IF(U34="Поражение",-1,IF(U34="Возврат",0,IF(U34="Полувыигрыш",(J34-1)/2,IF(U34="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U34="","",IF(U34="Плюс",J34-1,IF(U34="Минус",-1,IF(U34="Возврат",0,IF(U34="Полуплюс",(J34-1)/2,IF(U34="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W34" s="80" t="str">
         <x:f>IF(A34="","",IF(U34="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X34" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X34" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:37 МСК; низкая точность ударов</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="80"/>
-      <x:c r="B35" s="80"/>
-      <x:c r="C35" s="83"/>
-      <x:c r="D35" s="80"/>
-      <x:c r="E35" s="80"/>
-      <x:c r="F35" s="86"/>
-      <x:c r="G35" s="80"/>
-      <x:c r="H35" s="95"/>
-      <x:c r="I35" s="95"/>
-      <x:c r="J35" s="96"/>
-      <x:c r="K35" s="97"/>
-      <x:c r="L35" s="98"/>
-      <x:c r="M35" s="98"/>
-      <x:c r="N35" s="98"/>
-      <x:c r="O35" s="98"/>
-      <x:c r="P35" s="98"/>
-      <x:c r="Q35" s="80"/>
-      <x:c r="R35" s="80"/>
-      <x:c r="S35" s="80"/>
+      <x:c r="A35" s="80" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B35" s="80" t="str">
+        <x:v>12159729</x:v>
+      </x:c>
+      <x:c r="C35" s="83" t="str">
+        <x:v>13.10.2026 21:37</x:v>
+      </x:c>
+      <x:c r="D35" s="80" t="str">
+        <x:v>Австрия - Земельная лига</x:v>
+      </x:c>
+      <x:c r="E35" s="80" t="str">
+        <x:v>Лебринг - Шладминг</x:v>
+      </x:c>
+      <x:c r="F35" s="86" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G35" s="80" t="str">
+        <x:v>1:0</x:v>
+      </x:c>
+      <x:c r="H35" s="95" t="str">
+        <x:v>Лебринг сохраняет преимущество по моментам, гости должны раскрываться</x:v>
+      </x:c>
+      <x:c r="I35" s="95" t="str">
+        <x:v>ТБ 2,5 всего матча</x:v>
+      </x:c>
+      <x:c r="J35" s="96" t="n">
+        <x:v>1.875</x:v>
+      </x:c>
+      <x:c r="K35" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L35" s="98" t="str">
+        <x:v>Владение 59:41; удары 13; в створ 3; угловые 3; опасные атаки 20:5</x:v>
+      </x:c>
+      <x:c r="M35" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N35" s="98" t="str">
+        <x:v>Высокий объём ударов; ещё два гола дают полный выигрыш</x:v>
+      </x:c>
+      <x:c r="O35" s="98" t="str">
+        <x:v>Только три удара в створ; Шладминг создаёт мало опасных атак</x:v>
+      </x:c>
+      <x:c r="P35" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q35" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R35" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S35" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T35" s="80"/>
       <x:c r="U35" s="80"/>
       <x:c r="V35" s="89" t="str">
-        <x:f>IF(U35="Выигрыш",J35-1,IF(U35="Поражение",-1,IF(U35="Возврат",0,IF(U35="Полувыигрыш",(J35-1)/2,IF(U35="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U35="","",IF(U35="Плюс",J35-1,IF(U35="Минус",-1,IF(U35="Возврат",0,IF(U35="Полуплюс",(J35-1)/2,IF(U35="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W35" s="80" t="str">
         <x:f>IF(A35="","",IF(U35="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X35" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X35" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:37 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="80"/>
-      <x:c r="B36" s="80"/>
-      <x:c r="C36" s="83"/>
-      <x:c r="D36" s="80"/>
-      <x:c r="E36" s="80"/>
-      <x:c r="F36" s="86"/>
-      <x:c r="G36" s="80"/>
-      <x:c r="H36" s="95"/>
-      <x:c r="I36" s="95"/>
-      <x:c r="J36" s="96"/>
-      <x:c r="K36" s="97"/>
-      <x:c r="L36" s="98"/>
-      <x:c r="M36" s="98"/>
-      <x:c r="N36" s="98"/>
-      <x:c r="O36" s="98"/>
-      <x:c r="P36" s="98"/>
-      <x:c r="Q36" s="80"/>
-      <x:c r="R36" s="80"/>
-      <x:c r="S36" s="80"/>
+      <x:c r="A36" s="80" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B36" s="80" t="str">
+        <x:v>12063004</x:v>
+      </x:c>
+      <x:c r="C36" s="83" t="str">
+        <x:v>13.10.2026 21:37</x:v>
+      </x:c>
+      <x:c r="D36" s="80" t="str">
+        <x:v>Женщины - квалификация чемпионата мира</x:v>
+      </x:c>
+      <x:c r="E36" s="80" t="str">
+        <x:v>Исландия - Хорватия</x:v>
+      </x:c>
+      <x:c r="F36" s="86" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G36" s="80" t="str">
+        <x:v>2:0</x:v>
+      </x:c>
+      <x:c r="H36" s="95" t="str">
+        <x:v>Исландия полностью доминирует и продолжает создавать моменты</x:v>
+      </x:c>
+      <x:c r="I36" s="95" t="str">
+        <x:v>ТБ 3,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J36" s="96" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="K36" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L36" s="98" t="str">
+        <x:v>Владение 71:29; удары 12:0; в створ 5:0; угловые 7:0; опасные атаки 66:19</x:v>
+      </x:c>
+      <x:c r="M36" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N36" s="98" t="str">
+        <x:v>Полное статистическое превосходство Исландии; семь угловых и пять ударов в створ</x:v>
+      </x:c>
+      <x:c r="O36" s="98" t="str">
+        <x:v>Сценарий односторонний; два дополнительных гола дают только полувыигрыш; 51-я минута</x:v>
+      </x:c>
+      <x:c r="P36" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q36" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R36" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S36" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T36" s="80"/>
       <x:c r="U36" s="80"/>
       <x:c r="V36" s="89" t="str">
-        <x:f>IF(U36="Выигрыш",J36-1,IF(U36="Поражение",-1,IF(U36="Возврат",0,IF(U36="Полувыигрыш",(J36-1)/2,IF(U36="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U36="","",IF(U36="Плюс",J36-1,IF(U36="Минус",-1,IF(U36="Возврат",0,IF(U36="Полуплюс",(J36-1)/2,IF(U36="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W36" s="80" t="str">
         <x:f>IF(A36="","",IF(U36="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X36" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X36" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:37 МСК; односторонний сценарий</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="80"/>

--- a/Live ТБ/Live ТБ.xlsx
+++ b/Live ТБ/Live ТБ.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R081d98394ae44fd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R999c901eb4b84c44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="R4cc66e301cb54fdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="Rce3d3746c41242ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R82a51537fe724d02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="R20180f2a27624bb0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -820,7 +820,7 @@
       </x:c>
       <x:c r="B7" s="57" t="n">
         <x:f>COUNTA('Реестр'!$A$6:$A$505)</x:f>
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C7" s="55"/>
       <x:c r="D7" s="58" t="str">
@@ -897,7 +897,7 @@
       </x:c>
       <x:c r="B12" s="57" t="n">
         <x:f>COUNTIF('Реестр'!$W$6:$W$505,"Открыт")</x:f>
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C12" s="55"/>
       <x:c r="D12" s="61"/>
@@ -941,7 +941,7 @@
       </x:c>
       <x:c r="B15" s="64" t="n">
         <x:f>IF(B7=0,"",AVERAGEIF('Реестр'!$A$6:$A$505,"&gt;0",'Реестр'!$J$6:$J$505))</x:f>
-        <x:v>1.8879032258064519</x:v>
+        <x:v>1.8959302325581397</x:v>
       </x:c>
       <x:c r="C15" s="55"/>
       <x:c r="D15" s="55"/>
@@ -955,7 +955,7 @@
         <x:v>Дата последнего выбора</x:v>
       </x:c>
       <x:c r="B16" s="70" t="str">
-        <x:v>13.10.2026 21:37</x:v>
+        <x:v>13.10.2026 21:50</x:v>
       </x:c>
       <x:c r="C16" s="55"/>
       <x:c r="D16" s="55"/>
@@ -3366,364 +3366,856 @@
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="80"/>
-      <x:c r="B37" s="80"/>
-      <x:c r="C37" s="83"/>
-      <x:c r="D37" s="80"/>
-      <x:c r="E37" s="80"/>
-      <x:c r="F37" s="86"/>
-      <x:c r="G37" s="80"/>
-      <x:c r="H37" s="95"/>
-      <x:c r="I37" s="95"/>
-      <x:c r="J37" s="96"/>
-      <x:c r="K37" s="97"/>
-      <x:c r="L37" s="98"/>
-      <x:c r="M37" s="98"/>
-      <x:c r="N37" s="98"/>
-      <x:c r="O37" s="98"/>
-      <x:c r="P37" s="98"/>
-      <x:c r="Q37" s="80"/>
-      <x:c r="R37" s="80"/>
-      <x:c r="S37" s="80"/>
+      <x:c r="A37" s="80" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B37" s="80" t="str">
+        <x:v>13288669</x:v>
+      </x:c>
+      <x:c r="C37" s="83" t="str">
+        <x:v>13.10.2026 21:50</x:v>
+      </x:c>
+      <x:c r="D37" s="80" t="str">
+        <x:v>Польша - IV лига</x:v>
+      </x:c>
+      <x:c r="E37" s="80" t="str">
+        <x:v>Полония Лазиска-Гурне - Пшемша-Севеж</x:v>
+      </x:c>
+      <x:c r="F37" s="86" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G37" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H37" s="95" t="str">
+        <x:v>Высокая плотность ударов в створ при низкой линии</x:v>
+      </x:c>
+      <x:c r="I37" s="95" t="str">
+        <x:v>ТБ 1,25 всего матча</x:v>
+      </x:c>
+      <x:c r="J37" s="96" t="n">
+        <x:v>1.875</x:v>
+      </x:c>
+      <x:c r="K37" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L37" s="98" t="str">
+        <x:v>Удары 5:11; в створ 3:6; опасные атаки 41:35; угловые 3:2; владение 45:55</x:v>
+      </x:c>
+      <x:c r="M37" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N37" s="98" t="str">
+        <x:v>Девять ударов в створ при нулевом счёте; низкая линия</x:v>
+      </x:c>
+      <x:c r="O37" s="98" t="str">
+        <x:v>Осталось около 35 минут; один гол даёт полупроигрыш</x:v>
+      </x:c>
+      <x:c r="P37" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q37" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R37" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S37" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T37" s="80"/>
       <x:c r="U37" s="80"/>
       <x:c r="V37" s="89" t="str">
-        <x:f>IF(U37="Выигрыш",J37-1,IF(U37="Поражение",-1,IF(U37="Возврат",0,IF(U37="Полувыигрыш",(J37-1)/2,IF(U37="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U37="","",IF(U37="Плюс",J37-1,IF(U37="Минус",-1,IF(U37="Возврат",0,IF(U37="Полуплюс",(J37-1)/2,IF(U37="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W37" s="80" t="str">
         <x:f>IF(A37="","",IF(U37="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X37" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X37" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:50 МСК; лучший кандидат снимка по плотности ударов в створ</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="80"/>
-      <x:c r="B38" s="80"/>
-      <x:c r="C38" s="83"/>
-      <x:c r="D38" s="80"/>
-      <x:c r="E38" s="80"/>
-      <x:c r="F38" s="86"/>
-      <x:c r="G38" s="80"/>
-      <x:c r="H38" s="95"/>
-      <x:c r="I38" s="95"/>
-      <x:c r="J38" s="96"/>
-      <x:c r="K38" s="97"/>
-      <x:c r="L38" s="98"/>
-      <x:c r="M38" s="98"/>
-      <x:c r="N38" s="98"/>
-      <x:c r="O38" s="98"/>
-      <x:c r="P38" s="98"/>
-      <x:c r="Q38" s="80"/>
-      <x:c r="R38" s="80"/>
-      <x:c r="S38" s="80"/>
+      <x:c r="A38" s="80" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B38" s="80" t="str">
+        <x:v>12407699</x:v>
+      </x:c>
+      <x:c r="C38" s="83" t="str">
+        <x:v>13.10.2026 21:50</x:v>
+      </x:c>
+      <x:c r="D38" s="80" t="str">
+        <x:v>Англия - Трофей Английской лиги</x:v>
+      </x:c>
+      <x:c r="E38" s="80" t="str">
+        <x:v>Челтнем - Тоттенхэм U21</x:v>
+      </x:c>
+      <x:c r="F38" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G38" s="80" t="str">
+        <x:v>1:0</x:v>
+      </x:c>
+      <x:c r="H38" s="95" t="str">
+        <x:v>Тоттенхэм U21 уступает и должен раскрываться после перерыва</x:v>
+      </x:c>
+      <x:c r="I38" s="95" t="str">
+        <x:v>ТБ 3 всего матча</x:v>
+      </x:c>
+      <x:c r="J38" s="96" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="K38" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L38" s="98" t="str">
+        <x:v>Удары 7:4; в створ 3:1; опасные атаки 26:20; угловые 4:4; владение 45:55; xG 1,27:0,68</x:v>
+      </x:c>
+      <x:c r="M38" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N38" s="98" t="str">
+        <x:v>Суммарный xG 1,95; одиннадцать ударов и восемь угловых</x:v>
+      </x:c>
+      <x:c r="O38" s="98" t="str">
+        <x:v>У гостей только один удар в створ; два новых гола дают лишь возврат</x:v>
+      </x:c>
+      <x:c r="P38" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q38" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R38" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S38" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T38" s="80"/>
       <x:c r="U38" s="80"/>
       <x:c r="V38" s="89" t="str">
-        <x:f>IF(U38="Выигрыш",J38-1,IF(U38="Поражение",-1,IF(U38="Возврат",0,IF(U38="Полувыигрыш",(J38-1)/2,IF(U38="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U38="","",IF(U38="Плюс",J38-1,IF(U38="Минус",-1,IF(U38="Возврат",0,IF(U38="Полуплюс",(J38-1)/2,IF(U38="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W38" s="80" t="str">
         <x:f>IF(A38="","",IF(U38="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X38" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X38" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:50 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="80"/>
-      <x:c r="B39" s="80"/>
-      <x:c r="C39" s="83"/>
-      <x:c r="D39" s="80"/>
-      <x:c r="E39" s="80"/>
-      <x:c r="F39" s="86"/>
-      <x:c r="G39" s="80"/>
-      <x:c r="H39" s="95"/>
-      <x:c r="I39" s="95"/>
-      <x:c r="J39" s="96"/>
-      <x:c r="K39" s="97"/>
-      <x:c r="L39" s="98"/>
-      <x:c r="M39" s="98"/>
-      <x:c r="N39" s="98"/>
-      <x:c r="O39" s="98"/>
-      <x:c r="P39" s="98"/>
-      <x:c r="Q39" s="80"/>
-      <x:c r="R39" s="80"/>
-      <x:c r="S39" s="80"/>
+      <x:c r="A39" s="80" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B39" s="80" t="str">
+        <x:v>12457698</x:v>
+      </x:c>
+      <x:c r="C39" s="83" t="str">
+        <x:v>13.10.2026 21:50</x:v>
+      </x:c>
+      <x:c r="D39" s="80" t="str">
+        <x:v>Азия - Лига чемпионов АФК</x:v>
+      </x:c>
+      <x:c r="E39" s="80" t="str">
+        <x:v>Аль-Иттихад Джидда - Шабаб Аль-Ахли</x:v>
+      </x:c>
+      <x:c r="F39" s="86" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G39" s="80" t="str">
+        <x:v>0:2</x:v>
+      </x:c>
+      <x:c r="H39" s="95" t="str">
+        <x:v>Аль-Иттихад проигрывает два мяча и продолжает территориальное давление</x:v>
+      </x:c>
+      <x:c r="I39" s="95" t="str">
+        <x:v>ТБ 4,25 всего матча</x:v>
+      </x:c>
+      <x:c r="J39" s="96" t="n">
+        <x:v>2.025</x:v>
+      </x:c>
+      <x:c r="K39" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L39" s="98" t="str">
+        <x:v>Удары 8:5; в створ 4:2; опасные атаки 25:6; угловые 3:0; владение 68:32; xG 0,25:1,19</x:v>
+      </x:c>
+      <x:c r="M39" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N39" s="98" t="str">
+        <x:v>Тринадцать ударов и шесть в створ; проигрывающая команда владеет инициативой</x:v>
+      </x:c>
+      <x:c r="O39" s="98" t="str">
+        <x:v>xG хозяев только 0,25; два дополнительных гола дают полупроигрыш</x:v>
+      </x:c>
+      <x:c r="P39" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q39" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R39" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S39" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T39" s="80"/>
       <x:c r="U39" s="80"/>
       <x:c r="V39" s="89" t="str">
-        <x:f>IF(U39="Выигрыш",J39-1,IF(U39="Поражение",-1,IF(U39="Возврат",0,IF(U39="Полувыигрыш",(J39-1)/2,IF(U39="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U39="","",IF(U39="Плюс",J39-1,IF(U39="Минус",-1,IF(U39="Возврат",0,IF(U39="Полуплюс",(J39-1)/2,IF(U39="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W39" s="80" t="str">
         <x:f>IF(A39="","",IF(U39="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X39" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X39" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:50 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="80"/>
-      <x:c r="B40" s="80"/>
-      <x:c r="C40" s="83"/>
-      <x:c r="D40" s="80"/>
-      <x:c r="E40" s="80"/>
-      <x:c r="F40" s="86"/>
-      <x:c r="G40" s="80"/>
-      <x:c r="H40" s="95"/>
-      <x:c r="I40" s="95"/>
-      <x:c r="J40" s="96"/>
-      <x:c r="K40" s="97"/>
-      <x:c r="L40" s="98"/>
-      <x:c r="M40" s="98"/>
-      <x:c r="N40" s="98"/>
-      <x:c r="O40" s="98"/>
-      <x:c r="P40" s="98"/>
-      <x:c r="Q40" s="80"/>
-      <x:c r="R40" s="80"/>
-      <x:c r="S40" s="80"/>
+      <x:c r="A40" s="80" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B40" s="80" t="str">
+        <x:v>13285299</x:v>
+      </x:c>
+      <x:c r="C40" s="83" t="str">
+        <x:v>13.10.2026 21:50</x:v>
+      </x:c>
+      <x:c r="D40" s="80" t="str">
+        <x:v>Аргентина - Лига резервов</x:v>
+      </x:c>
+      <x:c r="E40" s="80" t="str">
+        <x:v>Док-Суд резерв - Дефенсорес Унидос резерв</x:v>
+      </x:c>
+      <x:c r="F40" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G40" s="80" t="str">
+        <x:v>2:1</x:v>
+      </x:c>
+      <x:c r="H40" s="95" t="str">
+        <x:v>Конкурентный счёт и сохраняющееся преимущество хозяев по активности</x:v>
+      </x:c>
+      <x:c r="I40" s="95" t="str">
+        <x:v>ТБ 4,5 всего матча</x:v>
+      </x:c>
+      <x:c r="J40" s="96" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="K40" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L40" s="98" t="str">
+        <x:v>Удары 7:3; в створ 4:2; опасные атаки 43:26; угловые 0:1; владение 52:48</x:v>
+      </x:c>
+      <x:c r="M40" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N40" s="98" t="str">
+        <x:v>Три гола и шесть ударов в створ за первый тайм</x:v>
+      </x:c>
+      <x:c r="O40" s="98" t="str">
+        <x:v>Только один угловой; гости создают заметно меньше</x:v>
+      </x:c>
+      <x:c r="P40" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q40" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R40" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S40" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T40" s="80"/>
       <x:c r="U40" s="80"/>
       <x:c r="V40" s="89" t="str">
-        <x:f>IF(U40="Выигрыш",J40-1,IF(U40="Поражение",-1,IF(U40="Возврат",0,IF(U40="Полувыигрыш",(J40-1)/2,IF(U40="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U40="","",IF(U40="Плюс",J40-1,IF(U40="Минус",-1,IF(U40="Возврат",0,IF(U40="Полуплюс",(J40-1)/2,IF(U40="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W40" s="80" t="str">
         <x:f>IF(A40="","",IF(U40="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X40" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X40" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:50 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="80"/>
-      <x:c r="B41" s="80"/>
-      <x:c r="C41" s="83"/>
-      <x:c r="D41" s="80"/>
-      <x:c r="E41" s="80"/>
-      <x:c r="F41" s="86"/>
-      <x:c r="G41" s="80"/>
-      <x:c r="H41" s="95"/>
-      <x:c r="I41" s="95"/>
-      <x:c r="J41" s="96"/>
-      <x:c r="K41" s="97"/>
-      <x:c r="L41" s="98"/>
-      <x:c r="M41" s="98"/>
-      <x:c r="N41" s="98"/>
-      <x:c r="O41" s="98"/>
-      <x:c r="P41" s="98"/>
-      <x:c r="Q41" s="80"/>
-      <x:c r="R41" s="80"/>
-      <x:c r="S41" s="80"/>
+      <x:c r="A41" s="80" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B41" s="80" t="str">
+        <x:v>12319680</x:v>
+      </x:c>
+      <x:c r="C41" s="83" t="str">
+        <x:v>13.10.2026 21:50</x:v>
+      </x:c>
+      <x:c r="D41" s="80" t="str">
+        <x:v>ЮАР - Премьер-лига</x:v>
+      </x:c>
+      <x:c r="E41" s="80" t="str">
+        <x:v>Кайзер Чифс - Стелленбос</x:v>
+      </x:c>
+      <x:c r="F41" s="86" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G41" s="80" t="str">
+        <x:v>1:1</x:v>
+      </x:c>
+      <x:c r="H41" s="95" t="str">
+        <x:v>Ничья при территориальном преимуществе Кайзер Чифс и активности обеих команд</x:v>
+      </x:c>
+      <x:c r="I41" s="95" t="str">
+        <x:v>ТБ 2,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J41" s="96" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="K41" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L41" s="98" t="str">
+        <x:v>Удары 5:5; в створ 1:1; опасные атаки 42:30; угловые 3:3; владение 66:34; xG 0,67:0,55</x:v>
+      </x:c>
+      <x:c r="M41" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N41" s="98" t="str">
+        <x:v>Суммарный xG 1,22; обе команды забили; один гол даёт полувыигрыш</x:v>
+      </x:c>
+      <x:c r="O41" s="98" t="str">
+        <x:v>Только два удара в створ; верхняя граница рабочего окна</x:v>
+      </x:c>
+      <x:c r="P41" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q41" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R41" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S41" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T41" s="80"/>
       <x:c r="U41" s="80"/>
       <x:c r="V41" s="89" t="str">
-        <x:f>IF(U41="Выигрыш",J41-1,IF(U41="Поражение",-1,IF(U41="Возврат",0,IF(U41="Полувыигрыш",(J41-1)/2,IF(U41="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U41="","",IF(U41="Плюс",J41-1,IF(U41="Минус",-1,IF(U41="Возврат",0,IF(U41="Полуплюс",(J41-1)/2,IF(U41="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W41" s="80" t="str">
         <x:f>IF(A41="","",IF(U41="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X41" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X41" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:50 МСК; повышенный временной риск</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="80"/>
-      <x:c r="B42" s="80"/>
-      <x:c r="C42" s="83"/>
-      <x:c r="D42" s="80"/>
-      <x:c r="E42" s="80"/>
-      <x:c r="F42" s="86"/>
-      <x:c r="G42" s="80"/>
-      <x:c r="H42" s="95"/>
-      <x:c r="I42" s="95"/>
-      <x:c r="J42" s="96"/>
-      <x:c r="K42" s="97"/>
-      <x:c r="L42" s="98"/>
-      <x:c r="M42" s="98"/>
-      <x:c r="N42" s="98"/>
-      <x:c r="O42" s="98"/>
-      <x:c r="P42" s="98"/>
-      <x:c r="Q42" s="80"/>
-      <x:c r="R42" s="80"/>
-      <x:c r="S42" s="80"/>
+      <x:c r="A42" s="80" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B42" s="80" t="str">
+        <x:v>13217858</x:v>
+      </x:c>
+      <x:c r="C42" s="83" t="str">
+        <x:v>13.10.2026 21:50</x:v>
+      </x:c>
+      <x:c r="D42" s="80" t="str">
+        <x:v>Аргентина - Лига профессиональных резервов</x:v>
+      </x:c>
+      <x:c r="E42" s="80" t="str">
+        <x:v>Атлетико Рафаэла резерв - Эстудиантес Рио-Куарто резерв</x:v>
+      </x:c>
+      <x:c r="F42" s="86" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G42" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H42" s="95" t="str">
+        <x:v>Равная активная игра при низкой линии тотала</x:v>
+      </x:c>
+      <x:c r="I42" s="95" t="str">
+        <x:v>ТБ 1,5 всего матча</x:v>
+      </x:c>
+      <x:c r="J42" s="96" t="n">
+        <x:v>1.9</x:v>
+      </x:c>
+      <x:c r="K42" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L42" s="98" t="str">
+        <x:v>Удары 4:5; в створ 1:2; опасные атаки 21:33; угловые 1:2; владение 54:46</x:v>
+      </x:c>
+      <x:c r="M42" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N42" s="98" t="str">
+        <x:v>Девять ударов, три в створ и около часа игрового времени</x:v>
+      </x:c>
+      <x:c r="O42" s="98" t="str">
+        <x:v>Нет явного доминирующего источника моментов; xG недоступен</x:v>
+      </x:c>
+      <x:c r="P42" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q42" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R42" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S42" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T42" s="80"/>
       <x:c r="U42" s="80"/>
       <x:c r="V42" s="89" t="str">
-        <x:f>IF(U42="Выигрыш",J42-1,IF(U42="Поражение",-1,IF(U42="Возврат",0,IF(U42="Полувыигрыш",(J42-1)/2,IF(U42="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U42="","",IF(U42="Плюс",J42-1,IF(U42="Минус",-1,IF(U42="Возврат",0,IF(U42="Полуплюс",(J42-1)/2,IF(U42="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W42" s="80" t="str">
         <x:f>IF(A42="","",IF(U42="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X42" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X42" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:50 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="80"/>
-      <x:c r="B43" s="80"/>
-      <x:c r="C43" s="83"/>
-      <x:c r="D43" s="80"/>
-      <x:c r="E43" s="80"/>
-      <x:c r="F43" s="86"/>
-      <x:c r="G43" s="80"/>
-      <x:c r="H43" s="95"/>
-      <x:c r="I43" s="95"/>
-      <x:c r="J43" s="96"/>
-      <x:c r="K43" s="97"/>
-      <x:c r="L43" s="98"/>
-      <x:c r="M43" s="98"/>
-      <x:c r="N43" s="98"/>
-      <x:c r="O43" s="98"/>
-      <x:c r="P43" s="98"/>
-      <x:c r="Q43" s="80"/>
-      <x:c r="R43" s="80"/>
-      <x:c r="S43" s="80"/>
+      <x:c r="A43" s="80" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B43" s="80" t="str">
+        <x:v>13285298</x:v>
+      </x:c>
+      <x:c r="C43" s="83" t="str">
+        <x:v>13.10.2026 21:50</x:v>
+      </x:c>
+      <x:c r="D43" s="80" t="str">
+        <x:v>Аргентина - Лига резервов</x:v>
+      </x:c>
+      <x:c r="E43" s="80" t="str">
+        <x:v>Кильмес резерв - Депортиво Арменио резерв</x:v>
+      </x:c>
+      <x:c r="F43" s="86" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G43" s="80" t="str">
+        <x:v>1:0</x:v>
+      </x:c>
+      <x:c r="H43" s="95" t="str">
+        <x:v>Гости уступают, владеют мячом и должны менять игру</x:v>
+      </x:c>
+      <x:c r="I43" s="95" t="str">
+        <x:v>ТБ 2,5 всего матча</x:v>
+      </x:c>
+      <x:c r="J43" s="96" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K43" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L43" s="98" t="str">
+        <x:v>Удары 5:1; в створ 2:1; опасные атаки 33:26; угловые 3:1; владение 47:53; пенальти 1:0</x:v>
+      </x:c>
+      <x:c r="M43" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N43" s="98" t="str">
+        <x:v>Проигрывающая команда сохраняет владение; конкурентный счёт</x:v>
+      </x:c>
+      <x:c r="O43" s="98" t="str">
+        <x:v>Только шесть ударов; первый гол забит с пенальти; xG недоступен</x:v>
+      </x:c>
+      <x:c r="P43" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q43" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R43" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S43" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T43" s="80"/>
       <x:c r="U43" s="80"/>
       <x:c r="V43" s="89" t="str">
-        <x:f>IF(U43="Выигрыш",J43-1,IF(U43="Поражение",-1,IF(U43="Возврат",0,IF(U43="Полувыигрыш",(J43-1)/2,IF(U43="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U43="","",IF(U43="Плюс",J43-1,IF(U43="Минус",-1,IF(U43="Возврат",0,IF(U43="Полуплюс",(J43-1)/2,IF(U43="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W43" s="80" t="str">
         <x:f>IF(A43="","",IF(U43="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X43" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X43" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:50 МСК; пограничный кандидат</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="80"/>
-      <x:c r="B44" s="80"/>
-      <x:c r="C44" s="83"/>
-      <x:c r="D44" s="80"/>
-      <x:c r="E44" s="80"/>
-      <x:c r="F44" s="86"/>
-      <x:c r="G44" s="80"/>
-      <x:c r="H44" s="95"/>
-      <x:c r="I44" s="95"/>
-      <x:c r="J44" s="96"/>
-      <x:c r="K44" s="97"/>
-      <x:c r="L44" s="98"/>
-      <x:c r="M44" s="98"/>
-      <x:c r="N44" s="98"/>
-      <x:c r="O44" s="98"/>
-      <x:c r="P44" s="98"/>
-      <x:c r="Q44" s="80"/>
-      <x:c r="R44" s="80"/>
-      <x:c r="S44" s="80"/>
+      <x:c r="A44" s="80" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B44" s="80" t="str">
+        <x:v>12062985</x:v>
+      </x:c>
+      <x:c r="C44" s="83" t="str">
+        <x:v>13.10.2026 21:50</x:v>
+      </x:c>
+      <x:c r="D44" s="80" t="str">
+        <x:v>Женщины - квалификация чемпионата мира</x:v>
+      </x:c>
+      <x:c r="E44" s="80" t="str">
+        <x:v>Португалия - Северная Ирландия</x:v>
+      </x:c>
+      <x:c r="F44" s="86" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G44" s="80" t="str">
+        <x:v>0:1</x:v>
+      </x:c>
+      <x:c r="H44" s="95" t="str">
+        <x:v>Явный фаворит неожиданно уступает и вынужден усиливать давление</x:v>
+      </x:c>
+      <x:c r="I44" s="95" t="str">
+        <x:v>ТБ 3 всего матча</x:v>
+      </x:c>
+      <x:c r="J44" s="96" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="K44" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L44" s="98" t="str">
+        <x:v>Удары 5:3; в створ 1:2; опасные атаки 19:8; угловые 3:1; владение 81:19; xG 0,48:0,23</x:v>
+      </x:c>
+      <x:c r="M44" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N44" s="98" t="str">
+        <x:v>Огромное владение Португалии; более 55 минут игрового времени</x:v>
+      </x:c>
+      <x:c r="O44" s="98" t="str">
+        <x:v>Суммарный xG только 0,71; два новых гола дают лишь возврат</x:v>
+      </x:c>
+      <x:c r="P44" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q44" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R44" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S44" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T44" s="80"/>
       <x:c r="U44" s="80"/>
       <x:c r="V44" s="89" t="str">
-        <x:f>IF(U44="Выигрыш",J44-1,IF(U44="Поражение",-1,IF(U44="Возврат",0,IF(U44="Полувыигрыш",(J44-1)/2,IF(U44="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U44="","",IF(U44="Плюс",J44-1,IF(U44="Минус",-1,IF(U44="Возврат",0,IF(U44="Полуплюс",(J44-1)/2,IF(U44="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W44" s="80" t="str">
         <x:f>IF(A44="","",IF(U44="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X44" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X44" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:50 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="80"/>
-      <x:c r="B45" s="80"/>
-      <x:c r="C45" s="83"/>
-      <x:c r="D45" s="80"/>
-      <x:c r="E45" s="80"/>
-      <x:c r="F45" s="86"/>
-      <x:c r="G45" s="80"/>
-      <x:c r="H45" s="95"/>
-      <x:c r="I45" s="95"/>
-      <x:c r="J45" s="96"/>
-      <x:c r="K45" s="97"/>
-      <x:c r="L45" s="98"/>
-      <x:c r="M45" s="98"/>
-      <x:c r="N45" s="98"/>
-      <x:c r="O45" s="98"/>
-      <x:c r="P45" s="98"/>
-      <x:c r="Q45" s="80"/>
-      <x:c r="R45" s="80"/>
-      <x:c r="S45" s="80"/>
+      <x:c r="A45" s="80" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B45" s="80" t="str">
+        <x:v>13217800</x:v>
+      </x:c>
+      <x:c r="C45" s="83" t="str">
+        <x:v>13.10.2026 21:50</x:v>
+      </x:c>
+      <x:c r="D45" s="80" t="str">
+        <x:v>Аргентина - Лига профессиональных резервов</x:v>
+      </x:c>
+      <x:c r="E45" s="80" t="str">
+        <x:v>Индепендьенте резерв - Уракан резерв</x:v>
+      </x:c>
+      <x:c r="F45" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G45" s="80" t="str">
+        <x:v>2:0</x:v>
+      </x:c>
+      <x:c r="H45" s="95" t="str">
+        <x:v>Уракан должен раскрываться после перерыва при двухголовом отставании</x:v>
+      </x:c>
+      <x:c r="I45" s="95" t="str">
+        <x:v>ТБ 3,5 всего матча</x:v>
+      </x:c>
+      <x:c r="J45" s="96" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K45" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L45" s="98" t="str">
+        <x:v>Удары 4:3; в створ 3:1; опасные атаки 16:12; угловые 4:4; владение 55:45; пенальти 1:0</x:v>
+      </x:c>
+      <x:c r="M45" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N45" s="98" t="str">
+        <x:v>Восемь угловых и четыре удара в створ; впереди второй тайм</x:v>
+      </x:c>
+      <x:c r="O45" s="98" t="str">
+        <x:v>Общий темп ударов невысок; один гол забит с пенальти</x:v>
+      </x:c>
+      <x:c r="P45" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q45" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R45" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S45" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T45" s="80"/>
       <x:c r="U45" s="80"/>
       <x:c r="V45" s="89" t="str">
-        <x:f>IF(U45="Выигрыш",J45-1,IF(U45="Поражение",-1,IF(U45="Возврат",0,IF(U45="Полувыигрыш",(J45-1)/2,IF(U45="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U45="","",IF(U45="Плюс",J45-1,IF(U45="Минус",-1,IF(U45="Возврат",0,IF(U45="Полуплюс",(J45-1)/2,IF(U45="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W45" s="80" t="str">
         <x:f>IF(A45="","",IF(U45="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X45" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X45" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:50 МСК; пограничный кандидат</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="80"/>
-      <x:c r="B46" s="80"/>
-      <x:c r="C46" s="83"/>
-      <x:c r="D46" s="80"/>
-      <x:c r="E46" s="80"/>
-      <x:c r="F46" s="86"/>
-      <x:c r="G46" s="80"/>
-      <x:c r="H46" s="95"/>
-      <x:c r="I46" s="95"/>
-      <x:c r="J46" s="96"/>
-      <x:c r="K46" s="97"/>
-      <x:c r="L46" s="98"/>
-      <x:c r="M46" s="98"/>
-      <x:c r="N46" s="98"/>
-      <x:c r="O46" s="98"/>
-      <x:c r="P46" s="98"/>
-      <x:c r="Q46" s="80"/>
-      <x:c r="R46" s="80"/>
-      <x:c r="S46" s="80"/>
+      <x:c r="A46" s="80" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B46" s="80" t="str">
+        <x:v>12407276</x:v>
+      </x:c>
+      <x:c r="C46" s="83" t="str">
+        <x:v>13.10.2026 21:50</x:v>
+      </x:c>
+      <x:c r="D46" s="80" t="str">
+        <x:v>Англия - Трофей Английской лиги</x:v>
+      </x:c>
+      <x:c r="E46" s="80" t="str">
+        <x:v>Рединг - Челси U21</x:v>
+      </x:c>
+      <x:c r="F46" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G46" s="80" t="str">
+        <x:v>0:2</x:v>
+      </x:c>
+      <x:c r="H46" s="95" t="str">
+        <x:v>Рединг должен отыгрываться, а Челси U21 получает пространство для атак</x:v>
+      </x:c>
+      <x:c r="I46" s="95" t="str">
+        <x:v>ТБ 4 всего матча</x:v>
+      </x:c>
+      <x:c r="J46" s="96" t="n">
+        <x:v>1.8</x:v>
+      </x:c>
+      <x:c r="K46" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L46" s="98" t="str">
+        <x:v>Удары 8:5; в створ 3:2; опасные атаки 20:20; угловые 4:2; владение 49:51; xG 0,46:1,28</x:v>
+      </x:c>
+      <x:c r="M46" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N46" s="98" t="str">
+        <x:v>Тринадцать ударов, пять в створ и суммарный xG 1,74</x:v>
+      </x:c>
+      <x:c r="O46" s="98" t="str">
+        <x:v>Для полного выигрыша нужны ещё три гола; два дают возврат</x:v>
+      </x:c>
+      <x:c r="P46" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q46" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R46" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S46" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T46" s="80"/>
       <x:c r="U46" s="80"/>
       <x:c r="V46" s="89" t="str">
-        <x:f>IF(U46="Выигрыш",J46-1,IF(U46="Поражение",-1,IF(U46="Возврат",0,IF(U46="Полувыигрыш",(J46-1)/2,IF(U46="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U46="","",IF(U46="Плюс",J46-1,IF(U46="Минус",-1,IF(U46="Возврат",0,IF(U46="Полуплюс",(J46-1)/2,IF(U46="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W46" s="80" t="str">
         <x:f>IF(A46="","",IF(U46="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X46" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X46" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:50 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="80"/>
-      <x:c r="B47" s="80"/>
-      <x:c r="C47" s="83"/>
-      <x:c r="D47" s="80"/>
-      <x:c r="E47" s="80"/>
-      <x:c r="F47" s="86"/>
-      <x:c r="G47" s="80"/>
-      <x:c r="H47" s="95"/>
-      <x:c r="I47" s="95"/>
-      <x:c r="J47" s="96"/>
-      <x:c r="K47" s="97"/>
-      <x:c r="L47" s="98"/>
-      <x:c r="M47" s="98"/>
-      <x:c r="N47" s="98"/>
-      <x:c r="O47" s="98"/>
-      <x:c r="P47" s="98"/>
-      <x:c r="Q47" s="80"/>
-      <x:c r="R47" s="80"/>
-      <x:c r="S47" s="80"/>
+      <x:c r="A47" s="80" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B47" s="80" t="str">
+        <x:v>12403134</x:v>
+      </x:c>
+      <x:c r="C47" s="83" t="str">
+        <x:v>13.10.2026 21:50</x:v>
+      </x:c>
+      <x:c r="D47" s="80" t="str">
+        <x:v>Англия - Кубок Национальной лиги</x:v>
+      </x:c>
+      <x:c r="E47" s="80" t="str">
+        <x:v>Сканторп - Дерби U21</x:v>
+      </x:c>
+      <x:c r="F47" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G47" s="80" t="str">
+        <x:v>2:0</x:v>
+      </x:c>
+      <x:c r="H47" s="95" t="str">
+        <x:v>Дерби U21 должен раскрываться, Сканторп сохраняет территориальное преимущество</x:v>
+      </x:c>
+      <x:c r="I47" s="95" t="str">
+        <x:v>ТБ 3,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J47" s="96" t="n">
+        <x:v>1.925</x:v>
+      </x:c>
+      <x:c r="K47" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L47" s="98" t="str">
+        <x:v>Удары 6:3; в створ 3:2; опасные атаки 26:10; угловые 5:0; владение 50:50</x:v>
+      </x:c>
+      <x:c r="M47" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N47" s="98" t="str">
+        <x:v>Пять ударов в створ и пять угловых; впереди второй тайм</x:v>
+      </x:c>
+      <x:c r="O47" s="98" t="str">
+        <x:v>Активность гостей невысока; два новых гола дают только полувыигрыш</x:v>
+      </x:c>
+      <x:c r="P47" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q47" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R47" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S47" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T47" s="80"/>
       <x:c r="U47" s="80"/>
       <x:c r="V47" s="89" t="str">
-        <x:f>IF(U47="Выигрыш",J47-1,IF(U47="Поражение",-1,IF(U47="Возврат",0,IF(U47="Полувыигрыш",(J47-1)/2,IF(U47="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U47="","",IF(U47="Плюс",J47-1,IF(U47="Минус",-1,IF(U47="Возврат",0,IF(U47="Полуплюс",(J47-1)/2,IF(U47="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W47" s="80" t="str">
         <x:f>IF(A47="","",IF(U47="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X47" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X47" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:50 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="80"/>
-      <x:c r="B48" s="80"/>
-      <x:c r="C48" s="83"/>
-      <x:c r="D48" s="80"/>
-      <x:c r="E48" s="80"/>
-      <x:c r="F48" s="86"/>
-      <x:c r="G48" s="80"/>
-      <x:c r="H48" s="95"/>
-      <x:c r="I48" s="95"/>
-      <x:c r="J48" s="96"/>
-      <x:c r="K48" s="97"/>
-      <x:c r="L48" s="98"/>
-      <x:c r="M48" s="98"/>
-      <x:c r="N48" s="98"/>
-      <x:c r="O48" s="98"/>
-      <x:c r="P48" s="98"/>
-      <x:c r="Q48" s="80"/>
-      <x:c r="R48" s="80"/>
-      <x:c r="S48" s="80"/>
+      <x:c r="A48" s="80" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B48" s="80" t="str">
+        <x:v>12411994</x:v>
+      </x:c>
+      <x:c r="C48" s="83" t="str">
+        <x:v>13.10.2026 21:50</x:v>
+      </x:c>
+      <x:c r="D48" s="80" t="str">
+        <x:v>Англия - Кубок Премьер-лиги U21</x:v>
+      </x:c>
+      <x:c r="E48" s="80" t="str">
+        <x:v>Бромли U21 - Ковентри U21</x:v>
+      </x:c>
+      <x:c r="F48" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G48" s="80" t="str">
+        <x:v>1:0</x:v>
+      </x:c>
+      <x:c r="H48" s="95" t="str">
+        <x:v>Ковентри уступает, но превосходит соперника по владению и активности</x:v>
+      </x:c>
+      <x:c r="I48" s="95" t="str">
+        <x:v>ТБ 2,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J48" s="96" t="n">
+        <x:v>1.975</x:v>
+      </x:c>
+      <x:c r="K48" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L48" s="98" t="str">
+        <x:v>Удары 2:6; в створ 1:2; опасные атаки 18:30; угловые 2:2; владение 41:59</x:v>
+      </x:c>
+      <x:c r="M48" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10–15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N48" s="98" t="str">
+        <x:v>Проигрывающая команда ведёт по ударам и опасным атакам; молодёжный турнир</x:v>
+      </x:c>
+      <x:c r="O48" s="98" t="str">
+        <x:v>Только три удара в створ; два новых гола дают лишь полувыигрыш</x:v>
+      </x:c>
+      <x:c r="P48" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q48" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R48" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S48" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T48" s="80"/>
       <x:c r="U48" s="80"/>
       <x:c r="V48" s="89" t="str">
-        <x:f>IF(U48="Выигрыш",J48-1,IF(U48="Поражение",-1,IF(U48="Возврат",0,IF(U48="Полувыигрыш",(J48-1)/2,IF(U48="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U48="","",IF(U48="Плюс",J48-1,IF(U48="Минус",-1,IF(U48="Возврат",0,IF(U48="Полуплюс",(J48-1)/2,IF(U48="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W48" s="80" t="str">
         <x:f>IF(A48="","",IF(U48="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X48" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X48" s="98" t="str">
+        <x:v>Быстрый live-отбор 21:50 МСК</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="80"/>

--- a/Live ТБ/Live ТБ.xlsx
+++ b/Live ТБ/Live ТБ.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="Rce3d3746c41242ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R82a51537fe724d02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="R20180f2a27624bb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R8dfca66f155b4ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R531534400fdb4d38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="R7db021a17b4b462a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -820,7 +820,7 @@
       </x:c>
       <x:c r="B7" s="57" t="n">
         <x:f>COUNTA('Реестр'!$A$6:$A$505)</x:f>
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C7" s="55"/>
       <x:c r="D7" s="58" t="str">
@@ -897,7 +897,7 @@
       </x:c>
       <x:c r="B12" s="57" t="n">
         <x:f>COUNTIF('Реестр'!$W$6:$W$505,"Открыт")</x:f>
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C12" s="55"/>
       <x:c r="D12" s="61"/>
@@ -941,7 +941,7 @@
       </x:c>
       <x:c r="B15" s="64" t="n">
         <x:f>IF(B7=0,"",AVERAGEIF('Реестр'!$A$6:$A$505,"&gt;0",'Реестр'!$J$6:$J$505))</x:f>
-        <x:v>1.8959302325581397</x:v>
+        <x:v>1.8968750000000003</x:v>
       </x:c>
       <x:c r="C15" s="55"/>
       <x:c r="D15" s="55"/>
@@ -955,7 +955,7 @@
         <x:v>Дата последнего выбора</x:v>
       </x:c>
       <x:c r="B16" s="70" t="str">
-        <x:v>13.10.2026 21:50</x:v>
+        <x:v>13.10.2026 22:18</x:v>
       </x:c>
       <x:c r="C16" s="55"/>
       <x:c r="D16" s="55"/>
@@ -4218,154 +4218,359 @@
       </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="80"/>
-      <x:c r="B49" s="80"/>
-      <x:c r="C49" s="83"/>
-      <x:c r="D49" s="80"/>
-      <x:c r="E49" s="80"/>
-      <x:c r="F49" s="86"/>
-      <x:c r="G49" s="80"/>
-      <x:c r="H49" s="95"/>
-      <x:c r="I49" s="95"/>
-      <x:c r="J49" s="96"/>
-      <x:c r="K49" s="97"/>
-      <x:c r="L49" s="98"/>
-      <x:c r="M49" s="98"/>
-      <x:c r="N49" s="98"/>
-      <x:c r="O49" s="98"/>
-      <x:c r="P49" s="98"/>
-      <x:c r="Q49" s="80"/>
-      <x:c r="R49" s="80"/>
-      <x:c r="S49" s="80"/>
+      <x:c r="A49" s="80" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B49" s="80" t="str">
+        <x:v>13284855</x:v>
+      </x:c>
+      <x:c r="C49" s="83" t="str">
+        <x:v>13.10.2026 22:18</x:v>
+      </x:c>
+      <x:c r="D49" s="80" t="str">
+        <x:v>Англия - Северная лига, дивизион 1</x:v>
+      </x:c>
+      <x:c r="E49" s="80" t="str">
+        <x:v>Вест Окленд - Беверли Таун</x:v>
+      </x:c>
+      <x:c r="F49" s="86" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G49" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H49" s="95" t="str">
+        <x:v>Высокая плотность ударов в створ при нулевом счёте</x:v>
+      </x:c>
+      <x:c r="I49" s="95" t="str">
+        <x:v>ТБ 2,25 всего матча</x:v>
+      </x:c>
+      <x:c r="J49" s="96" t="n">
+        <x:v>2.025</x:v>
+      </x:c>
+      <x:c r="K49" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L49" s="98" t="str">
+        <x:v>Удары 9:4; в створ 6:3; опасные атаки 24:20; угловые 3:2; владение 51:49</x:v>
+      </x:c>
+      <x:c r="M49" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10-15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N49" s="98" t="str">
+        <x:v>Девять ударов в створ без гола; активность распределена между командами</x:v>
+      </x:c>
+      <x:c r="O49" s="98" t="str">
+        <x:v>Два дополнительных гола дают полупроигрыш; xG недоступен</x:v>
+      </x:c>
+      <x:c r="P49" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q49" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R49" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S49" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T49" s="80"/>
       <x:c r="U49" s="80"/>
       <x:c r="V49" s="89" t="str">
-        <x:f>IF(U49="Выигрыш",J49-1,IF(U49="Поражение",-1,IF(U49="Возврат",0,IF(U49="Полувыигрыш",(J49-1)/2,IF(U49="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U49="","",IF(U49="Плюс",J49-1,IF(U49="Минус",-1,IF(U49="Возврат",0,IF(U49="Полуплюс",(J49-1)/2,IF(U49="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W49" s="80" t="str">
         <x:f>IF(A49="","",IF(U49="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X49" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X49" s="98" t="str">
+        <x:v>Быстрый live-отбор 22:18 МСК; топ-1 прохода</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="80"/>
-      <x:c r="B50" s="80"/>
-      <x:c r="C50" s="83"/>
-      <x:c r="D50" s="80"/>
-      <x:c r="E50" s="80"/>
-      <x:c r="F50" s="86"/>
-      <x:c r="G50" s="80"/>
-      <x:c r="H50" s="95"/>
-      <x:c r="I50" s="95"/>
-      <x:c r="J50" s="96"/>
-      <x:c r="K50" s="97"/>
-      <x:c r="L50" s="98"/>
-      <x:c r="M50" s="98"/>
-      <x:c r="N50" s="98"/>
-      <x:c r="O50" s="98"/>
-      <x:c r="P50" s="98"/>
-      <x:c r="Q50" s="80"/>
-      <x:c r="R50" s="80"/>
-      <x:c r="S50" s="80"/>
+      <x:c r="A50" s="80" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B50" s="80" t="str">
+        <x:v>12273461</x:v>
+      </x:c>
+      <x:c r="C50" s="83" t="str">
+        <x:v>13.10.2026 22:18</x:v>
+      </x:c>
+      <x:c r="D50" s="80" t="str">
+        <x:v>Англия - Северная Премьер-лига</x:v>
+      </x:c>
+      <x:c r="E50" s="80" t="str">
+        <x:v>Юнайтед оф Манчестер - Эмли</x:v>
+      </x:c>
+      <x:c r="F50" s="86" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G50" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H50" s="95" t="str">
+        <x:v>Эмли создаёт явное преимущество по ударам и ударам в створ</x:v>
+      </x:c>
+      <x:c r="I50" s="95" t="str">
+        <x:v>ТБ 2 всего матча</x:v>
+      </x:c>
+      <x:c r="J50" s="96" t="n">
+        <x:v>1.775</x:v>
+      </x:c>
+      <x:c r="K50" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L50" s="98" t="str">
+        <x:v>Удары 5:10; в створ 2:6; опасные атаки 13:25; угловые 0:1; владение 36:64</x:v>
+      </x:c>
+      <x:c r="M50" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10-15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N50" s="98" t="str">
+        <x:v>Пятнадцать ударов и восемь в створ; гости заметно активнее</x:v>
+      </x:c>
+      <x:c r="O50" s="98" t="str">
+        <x:v>Два гола дают только возврат; мало угловых; xG недоступен</x:v>
+      </x:c>
+      <x:c r="P50" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q50" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R50" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S50" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T50" s="80"/>
       <x:c r="U50" s="80"/>
       <x:c r="V50" s="89" t="str">
-        <x:f>IF(U50="Выигрыш",J50-1,IF(U50="Поражение",-1,IF(U50="Возврат",0,IF(U50="Полувыигрыш",(J50-1)/2,IF(U50="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U50="","",IF(U50="Плюс",J50-1,IF(U50="Минус",-1,IF(U50="Возврат",0,IF(U50="Полуплюс",(J50-1)/2,IF(U50="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W50" s="80" t="str">
         <x:f>IF(A50="","",IF(U50="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X50" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X50" s="98" t="str">
+        <x:v>Быстрый live-отбор 22:18 МСК; топ-2 прохода</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="80"/>
-      <x:c r="B51" s="80"/>
-      <x:c r="C51" s="83"/>
-      <x:c r="D51" s="80"/>
-      <x:c r="E51" s="80"/>
-      <x:c r="F51" s="86"/>
-      <x:c r="G51" s="80"/>
-      <x:c r="H51" s="95"/>
-      <x:c r="I51" s="95"/>
-      <x:c r="J51" s="96"/>
-      <x:c r="K51" s="97"/>
-      <x:c r="L51" s="98"/>
-      <x:c r="M51" s="98"/>
-      <x:c r="N51" s="98"/>
-      <x:c r="O51" s="98"/>
-      <x:c r="P51" s="98"/>
-      <x:c r="Q51" s="80"/>
-      <x:c r="R51" s="80"/>
-      <x:c r="S51" s="80"/>
+      <x:c r="A51" s="80" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B51" s="80" t="str">
+        <x:v>12261910</x:v>
+      </x:c>
+      <x:c r="C51" s="83" t="str">
+        <x:v>13.10.2026 22:18</x:v>
+      </x:c>
+      <x:c r="D51" s="80" t="str">
+        <x:v>Шотландия - Кубок вызова</x:v>
+      </x:c>
+      <x:c r="E51" s="80" t="str">
+        <x:v>Эдинбург - Сент-Миррен B</x:v>
+      </x:c>
+      <x:c r="F51" s="86" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G51" s="80" t="str">
+        <x:v>0:1</x:v>
+      </x:c>
+      <x:c r="H51" s="95" t="str">
+        <x:v>Конкурентная игра с преимуществом гостей по качеству атак</x:v>
+      </x:c>
+      <x:c r="I51" s="95" t="str">
+        <x:v>ТБ 3,5 всего матча</x:v>
+      </x:c>
+      <x:c r="J51" s="96" t="n">
+        <x:v>1.95</x:v>
+      </x:c>
+      <x:c r="K51" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L51" s="98" t="str">
+        <x:v>Удары 7:7; в створ 3:5; угловые 1:4; опасные атаки 13:25; владение 50:50</x:v>
+      </x:c>
+      <x:c r="M51" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10-15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N51" s="98" t="str">
+        <x:v>Четырнадцать ударов и восемь в створ; обе команды участвуют в игре</x:v>
+      </x:c>
+      <x:c r="O51" s="98" t="str">
+        <x:v>Для выигрыша нужны ещё три гола; xG недоступен</x:v>
+      </x:c>
+      <x:c r="P51" s="98" t="str">
+        <x:v>Средняя</x:v>
+      </x:c>
+      <x:c r="Q51" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R51" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S51" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T51" s="80"/>
       <x:c r="U51" s="80"/>
       <x:c r="V51" s="89" t="str">
-        <x:f>IF(U51="Выигрыш",J51-1,IF(U51="Поражение",-1,IF(U51="Возврат",0,IF(U51="Полувыигрыш",(J51-1)/2,IF(U51="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U51="","",IF(U51="Плюс",J51-1,IF(U51="Минус",-1,IF(U51="Возврат",0,IF(U51="Полуплюс",(J51-1)/2,IF(U51="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W51" s="80" t="str">
         <x:f>IF(A51="","",IF(U51="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X51" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X51" s="98" t="str">
+        <x:v>Быстрый live-отбор 22:18 МСК; топ-3 прохода</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="80"/>
-      <x:c r="B52" s="80"/>
-      <x:c r="C52" s="83"/>
-      <x:c r="D52" s="80"/>
-      <x:c r="E52" s="80"/>
-      <x:c r="F52" s="86"/>
-      <x:c r="G52" s="80"/>
-      <x:c r="H52" s="95"/>
-      <x:c r="I52" s="95"/>
-      <x:c r="J52" s="96"/>
-      <x:c r="K52" s="97"/>
-      <x:c r="L52" s="98"/>
-      <x:c r="M52" s="98"/>
-      <x:c r="N52" s="98"/>
-      <x:c r="O52" s="98"/>
-      <x:c r="P52" s="98"/>
-      <x:c r="Q52" s="80"/>
-      <x:c r="R52" s="80"/>
-      <x:c r="S52" s="80"/>
+      <x:c r="A52" s="80" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B52" s="80" t="str">
+        <x:v>13041499</x:v>
+      </x:c>
+      <x:c r="C52" s="83" t="str">
+        <x:v>13.10.2026 22:18</x:v>
+      </x:c>
+      <x:c r="D52" s="80" t="str">
+        <x:v>Лига чемпионов УЕФА</x:v>
+      </x:c>
+      <x:c r="E52" s="80" t="str">
+        <x:v>Викинг - Бавария</x:v>
+      </x:c>
+      <x:c r="F52" s="86" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G52" s="80" t="str">
+        <x:v>1:0</x:v>
+      </x:c>
+      <x:c r="H52" s="95" t="str">
+        <x:v>Бавария проигрывает и полностью доминирует</x:v>
+      </x:c>
+      <x:c r="I52" s="95" t="str">
+        <x:v>ТБ 4,75 всего матча</x:v>
+      </x:c>
+      <x:c r="J52" s="96" t="n">
+        <x:v>1.925</x:v>
+      </x:c>
+      <x:c r="K52" s="97" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L52" s="98" t="str">
+        <x:v>Удары 1:6; в створ 1:2; угловые 1:5; опасные атаки 3:18; владение 23:77; xG 0,16:0,21</x:v>
+      </x:c>
+      <x:c r="M52" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10-15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N52" s="98" t="str">
+        <x:v>Бавария проигрывает, владеет 77% и ведёт по ударам 6:1 и угловым 5:1</x:v>
+      </x:c>
+      <x:c r="O52" s="98" t="str">
+        <x:v>Суммарный xG только 0,37; четыре дополнительных гола дают лишь полувыигрыш</x:v>
+      </x:c>
+      <x:c r="P52" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q52" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R52" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S52" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T52" s="80"/>
       <x:c r="U52" s="80"/>
       <x:c r="V52" s="89" t="str">
-        <x:f>IF(U52="Выигрыш",J52-1,IF(U52="Поражение",-1,IF(U52="Возврат",0,IF(U52="Полувыигрыш",(J52-1)/2,IF(U52="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U52="","",IF(U52="Плюс",J52-1,IF(U52="Минус",-1,IF(U52="Возврат",0,IF(U52="Полуплюс",(J52-1)/2,IF(U52="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W52" s="80" t="str">
         <x:f>IF(A52="","",IF(U52="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X52" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X52" s="98" t="str">
+        <x:v>Быстрый live-отбор 22:18 МСК; топ-4; агрессивный выбор; подтверждение прематчевого кандидата</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="80"/>
-      <x:c r="B53" s="80"/>
-      <x:c r="C53" s="83"/>
-      <x:c r="D53" s="80"/>
-      <x:c r="E53" s="80"/>
-      <x:c r="F53" s="86"/>
-      <x:c r="G53" s="80"/>
-      <x:c r="H53" s="95"/>
-      <x:c r="I53" s="95"/>
-      <x:c r="J53" s="96"/>
-      <x:c r="K53" s="97"/>
-      <x:c r="L53" s="98"/>
-      <x:c r="M53" s="98"/>
-      <x:c r="N53" s="98"/>
-      <x:c r="O53" s="98"/>
-      <x:c r="P53" s="98"/>
-      <x:c r="Q53" s="80"/>
-      <x:c r="R53" s="80"/>
-      <x:c r="S53" s="80"/>
+      <x:c r="A53" s="80" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B53" s="80" t="str">
+        <x:v>13041972</x:v>
+      </x:c>
+      <x:c r="C53" s="83" t="str">
+        <x:v>13.10.2026 22:18</x:v>
+      </x:c>
+      <x:c r="D53" s="80" t="str">
+        <x:v>Лига чемпионов УЕФА</x:v>
+      </x:c>
+      <x:c r="E53" s="80" t="str">
+        <x:v>Вильярреал - Наполи</x:v>
+      </x:c>
+      <x:c r="F53" s="86" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G53" s="80" t="str">
+        <x:v>0:1</x:v>
+      </x:c>
+      <x:c r="H53" s="95" t="str">
+        <x:v>Проигрывающий хозяин должен раскрываться</x:v>
+      </x:c>
+      <x:c r="I53" s="95" t="str">
+        <x:v>ТБ 3,25 всего матча</x:v>
+      </x:c>
+      <x:c r="J53" s="96" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="K53" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L53" s="98" t="str">
+        <x:v>Удары 4:2; в створ 0:2; угловые 3:1; опасные атаки 10:8; владение 58:42; xG 0,44:0,77</x:v>
+      </x:c>
+      <x:c r="M53" s="98" t="str">
+        <x:v>Один свежий снимок; раздельная динамика за 10-15 минут недоступна</x:v>
+      </x:c>
+      <x:c r="N53" s="98" t="str">
+        <x:v>Ранний гол; суммарный xG 1,21; Вильярреал уже подаёт и атакует</x:v>
+      </x:c>
+      <x:c r="O53" s="98" t="str">
+        <x:v>Два дополнительных гола дают полупроигрыш; у хозяев нет ударов в створ</x:v>
+      </x:c>
+      <x:c r="P53" s="98" t="str">
+        <x:v>Высокая</x:v>
+      </x:c>
+      <x:c r="Q53" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R53" s="80" t="str">
+        <x:v>ТБ live v1 от 13.10.2026</x:v>
+      </x:c>
+      <x:c r="S53" s="80" t="str">
+        <x:v>BetsAPI / Bet365</x:v>
+      </x:c>
       <x:c r="T53" s="80"/>
       <x:c r="U53" s="80"/>
       <x:c r="V53" s="89" t="str">
-        <x:f>IF(U53="Выигрыш",J53-1,IF(U53="Поражение",-1,IF(U53="Возврат",0,IF(U53="Полувыигрыш",(J53-1)/2,IF(U53="Полупроигрыш",-0.5,"")))))</x:f>
+        <x:f>IF(U53="","",IF(U53="Плюс",J53-1,IF(U53="Минус",-1,IF(U53="Возврат",0,IF(U53="Полуплюс",(J53-1)/2,IF(U53="Полуминус",-0.5,""))))))</x:f>
       </x:c>
       <x:c r="W53" s="80" t="str">
         <x:f>IF(A53="","",IF(U53="","Открыт","Рассчитан"))</x:f>
-      </x:c>
-      <x:c r="X53" s="98"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X53" s="98" t="str">
+        <x:v>Быстрый live-отбор 22:18 МСК; топ-5 прохода</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="80"/>

--- a/Live ТБ/Live ТБ.xlsx
+++ b/Live ТБ/Live ТБ.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="Rf81b702c1117467a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R63447f27c6e24db1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="Rdf2469d43d784f51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R9ba0e1b21a1f4ad5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R3b09298c027245c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="R41a58ae6ab2748bc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -889,11 +889,11 @@
       </x:c>
       <x:c r="C6" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Оптимальный")</x:f>
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D6" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный")</x:f>
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6"/>
       <x:c r="F6"/>
@@ -931,11 +931,11 @@
       </x:c>
       <x:c r="C8" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Оптимальный",'Реестр'!$W$6:$W$505,"Открыт")</x:f>
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$W$6:$W$505,"Открыт")</x:f>
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E8"/>
       <x:c r="F8"/>
@@ -6292,25 +6292,63 @@
       </x:c>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="80"/>
-      <x:c r="B59" s="80"/>
-      <x:c r="C59" s="83"/>
-      <x:c r="D59" s="80"/>
-      <x:c r="E59" s="80"/>
-      <x:c r="F59" s="86"/>
-      <x:c r="G59" s="80"/>
-      <x:c r="H59" s="95"/>
-      <x:c r="I59" s="95"/>
-      <x:c r="J59" s="96"/>
-      <x:c r="K59" s="97"/>
-      <x:c r="L59" s="98"/>
-      <x:c r="M59" s="98"/>
-      <x:c r="N59" s="98"/>
-      <x:c r="O59" s="98"/>
-      <x:c r="P59" s="98"/>
-      <x:c r="Q59" s="80"/>
-      <x:c r="R59" s="80"/>
-      <x:c r="S59" s="80"/>
+      <x:c r="A59" s="80" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B59" s="80" t="str">
+        <x:v>13224347</x:v>
+      </x:c>
+      <x:c r="C59" s="83" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="D59" s="80" t="str">
+        <x:v>Греция - Суперлига 2</x:v>
+      </x:c>
+      <x:c r="E59" s="80" t="str">
+        <x:v>Олимпиакос Б - Афины Каллитея</x:v>
+      </x:c>
+      <x:c r="F59" s="86" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G59" s="80" t="str">
+        <x:v>0:1</x:v>
+      </x:c>
+      <x:c r="H59" s="95" t="str">
+        <x:v>Гости создают угрозу; хозяевам нужно отыгрываться</x:v>
+      </x:c>
+      <x:c r="I59" s="95" t="str">
+        <x:v>ТБ 2 (Матч)</x:v>
+      </x:c>
+      <x:c r="J59" s="96" t="n">
+        <x:v>1.525</x:v>
+      </x:c>
+      <x:c r="K59" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L59" s="98" t="str">
+        <x:v>corners 2:1; dangerous_attacks 20:46; off_target 3:4; on_target 3:9; possession_rt 46:54; redcards 0:0</x:v>
+      </x:c>
+      <x:c r="M59" s="98" t="str">
+        <x:v>Нет отдельных снимков за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N59" s="98" t="str">
+        <x:v>Гости создают угрозу; хозяевам нужно отыгрываться</x:v>
+      </x:c>
+      <x:c r="O59" s="98" t="str">
+        <x:v>Лидер может снизить темп; удары и сейвы источника не полностью согласованы</x:v>
+      </x:c>
+      <x:c r="P59" s="98" t="str">
+        <x:v>Один снимок; xG и свежая динамика недоступны; внешней проверки нет</x:v>
+      </x:c>
+      <x:c r="Q59" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R59" s="80" t="str">
+        <x:v>ТБ live v2 от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S59" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; Резервная команда против взрослой; run 38538525336 attempt 2</x:v>
+      </x:c>
       <x:c r="T59" s="80"/>
       <x:c r="U59" s="80"/>
       <x:c r="V59" s="89" t="str">
@@ -6318,40 +6356,96 @@
       </x:c>
       <x:c r="W59" s="80" t="str">
         <x:f>IF(A59="","",IF(U59="","Открыт",IF(ISNUMBER(V59),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X59" s="98"/>
-      <x:c r="Y59" s="5"/>
-      <x:c r="Z59" s="5"/>
-      <x:c r="AA59" s="5"/>
-      <x:c r="AB59" s="118"/>
-      <x:c r="AC59" s="119"/>
-      <x:c r="AD59" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X59" s="98" t="str">
+        <x:v>Ещё 1 гол - возврат; исходные условия первичного ответа</x:v>
+      </x:c>
+      <x:c r="Y59" s="5" t="str">
+        <x:v>Оптимальный</x:v>
+      </x:c>
+      <x:c r="Z59" s="5" t="str">
+        <x:v>20261014T155823-13224347</x:v>
+      </x:c>
+      <x:c r="AA59" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB59" s="118" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AC59" s="119" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="AD59" s="119" t="str">
+        <x:v>14.10.2026 15:59</x:v>
+      </x:c>
       <x:c r="AE59" s="5" t="str">
         <x:f>IF(A59="","",IF(Z59="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z59,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z59,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF59" s="5"/>
-      <x:c r="AG59" s="5"/>
+      <x:c r="AG59" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="80"/>
-      <x:c r="B60" s="80"/>
-      <x:c r="C60" s="83"/>
-      <x:c r="D60" s="80"/>
-      <x:c r="E60" s="80"/>
-      <x:c r="F60" s="86"/>
-      <x:c r="G60" s="80"/>
-      <x:c r="H60" s="95"/>
-      <x:c r="I60" s="95"/>
-      <x:c r="J60" s="96"/>
-      <x:c r="K60" s="97"/>
-      <x:c r="L60" s="98"/>
-      <x:c r="M60" s="98"/>
-      <x:c r="N60" s="98"/>
-      <x:c r="O60" s="98"/>
-      <x:c r="P60" s="98"/>
-      <x:c r="Q60" s="80"/>
-      <x:c r="R60" s="80"/>
-      <x:c r="S60" s="80"/>
+      <x:c r="A60" s="80" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B60" s="80" t="str">
+        <x:v>13224347</x:v>
+      </x:c>
+      <x:c r="C60" s="83" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="D60" s="80" t="str">
+        <x:v>Греция - Суперлига 2</x:v>
+      </x:c>
+      <x:c r="E60" s="80" t="str">
+        <x:v>Олимпиакос Б - Афины Каллитея</x:v>
+      </x:c>
+      <x:c r="F60" s="86" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G60" s="80" t="str">
+        <x:v>0:1</x:v>
+      </x:c>
+      <x:c r="H60" s="95" t="str">
+        <x:v>Гости создают угрозу; хозяевам нужно отыгрываться</x:v>
+      </x:c>
+      <x:c r="I60" s="95" t="str">
+        <x:v>ТБ 2.5 (Матч)</x:v>
+      </x:c>
+      <x:c r="J60" s="96" t="n">
+        <x:v>2.25</x:v>
+      </x:c>
+      <x:c r="K60" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L60" s="98" t="str">
+        <x:v>corners 2:1; dangerous_attacks 20:46; off_target 3:4; on_target 3:9; possession_rt 46:54; redcards 0:0</x:v>
+      </x:c>
+      <x:c r="M60" s="98" t="str">
+        <x:v>Нет отдельных снимков за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N60" s="98" t="str">
+        <x:v>Гости создают угрозу; хозяевам нужно отыгрываться</x:v>
+      </x:c>
+      <x:c r="O60" s="98" t="str">
+        <x:v>Лидер может снизить темп; удары и сейвы источника не полностью согласованы</x:v>
+      </x:c>
+      <x:c r="P60" s="98" t="str">
+        <x:v>Один снимок; xG и свежая динамика недоступны; внешней проверки нет</x:v>
+      </x:c>
+      <x:c r="Q60" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R60" s="80" t="str">
+        <x:v>ТБ live v2 от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S60" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; Резервная команда против взрослой; run 38538525336 attempt 2</x:v>
+      </x:c>
       <x:c r="T60" s="80"/>
       <x:c r="U60" s="80"/>
       <x:c r="V60" s="89" t="str">
@@ -6359,40 +6453,96 @@
       </x:c>
       <x:c r="W60" s="80" t="str">
         <x:f>IF(A60="","",IF(U60="","Открыт",IF(ISNUMBER(V60),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X60" s="98"/>
-      <x:c r="Y60" s="5"/>
-      <x:c r="Z60" s="5"/>
-      <x:c r="AA60" s="5"/>
-      <x:c r="AB60" s="118"/>
-      <x:c r="AC60" s="119"/>
-      <x:c r="AD60" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X60" s="98" t="str">
+        <x:v>Без возврата; исходные условия первичного ответа</x:v>
+      </x:c>
+      <x:c r="Y60" s="5" t="str">
+        <x:v>Агрессивный</x:v>
+      </x:c>
+      <x:c r="Z60" s="5" t="str">
+        <x:v>20261014T155823-13224347</x:v>
+      </x:c>
+      <x:c r="AA60" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB60" s="118" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="AC60" s="119" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="AD60" s="119" t="str">
+        <x:v>14.10.2026 15:59</x:v>
+      </x:c>
       <x:c r="AE60" s="5" t="str">
         <x:f>IF(A60="","",IF(Z60="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z60,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z60,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF60" s="5"/>
-      <x:c r="AG60" s="5"/>
+      <x:c r="AG60" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="80"/>
-      <x:c r="B61" s="80"/>
-      <x:c r="C61" s="83"/>
-      <x:c r="D61" s="80"/>
-      <x:c r="E61" s="80"/>
-      <x:c r="F61" s="86"/>
-      <x:c r="G61" s="80"/>
-      <x:c r="H61" s="95"/>
-      <x:c r="I61" s="95"/>
-      <x:c r="J61" s="96"/>
-      <x:c r="K61" s="97"/>
-      <x:c r="L61" s="98"/>
-      <x:c r="M61" s="98"/>
-      <x:c r="N61" s="98"/>
-      <x:c r="O61" s="98"/>
-      <x:c r="P61" s="98"/>
-      <x:c r="Q61" s="80"/>
-      <x:c r="R61" s="80"/>
-      <x:c r="S61" s="80"/>
+      <x:c r="A61" s="80" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B61" s="80" t="str">
+        <x:v>13294263</x:v>
+      </x:c>
+      <x:c r="C61" s="83" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="D61" s="80" t="str">
+        <x:v>Албания / Мальта - Юношеская лига УЕФА</x:v>
+      </x:c>
+      <x:c r="E61" s="80" t="str">
+        <x:v>Партизани U19 - Валлетта U19</x:v>
+      </x:c>
+      <x:c r="F61" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G61" s="80" t="str">
+        <x:v>2:0</x:v>
+      </x:c>
+      <x:c r="H61" s="95" t="str">
+        <x:v>Хозяева способны продолжить результативность самостоятельно</x:v>
+      </x:c>
+      <x:c r="I61" s="95" t="str">
+        <x:v>ТБ 3.5 (Матч)</x:v>
+      </x:c>
+      <x:c r="J61" s="96" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="K61" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L61" s="98" t="str">
+        <x:v>corners 6:2; dangerous_attacks 41:16; off_target 10:2; on_target 4:1; possession_rt 58:42; redcards 0:0</x:v>
+      </x:c>
+      <x:c r="M61" s="98" t="str">
+        <x:v>Нет отдельных снимков за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N61" s="98" t="str">
+        <x:v>Хозяева способны продолжить результативность самостоятельно</x:v>
+      </x:c>
+      <x:c r="O61" s="98" t="str">
+        <x:v>Снижение активности при комфортном счёте</x:v>
+      </x:c>
+      <x:c r="P61" s="98" t="str">
+        <x:v>Один снимок; xG и свежая динамика недоступны; внешней проверки нет</x:v>
+      </x:c>
+      <x:c r="Q61" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R61" s="80" t="str">
+        <x:v>ТБ live v2 от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S61" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; Молодёжный/юниорский; run 38538525336 attempt 2</x:v>
+      </x:c>
       <x:c r="T61" s="80"/>
       <x:c r="U61" s="80"/>
       <x:c r="V61" s="89" t="str">
@@ -6400,40 +6550,96 @@
       </x:c>
       <x:c r="W61" s="80" t="str">
         <x:f>IF(A61="","",IF(U61="","Открыт",IF(ISNUMBER(V61),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X61" s="98"/>
-      <x:c r="Y61" s="5"/>
-      <x:c r="Z61" s="5"/>
-      <x:c r="AA61" s="5"/>
-      <x:c r="AB61" s="118"/>
-      <x:c r="AC61" s="119"/>
-      <x:c r="AD61" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X61" s="98" t="str">
+        <x:v>Без возврата; исходные условия первичного ответа</x:v>
+      </x:c>
+      <x:c r="Y61" s="5" t="str">
+        <x:v>Оптимальный</x:v>
+      </x:c>
+      <x:c r="Z61" s="5" t="str">
+        <x:v>20261014T155823-13294263</x:v>
+      </x:c>
+      <x:c r="AA61" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB61" s="118" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AC61" s="119" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="AD61" s="119" t="str">
+        <x:v>14.10.2026 15:59</x:v>
+      </x:c>
       <x:c r="AE61" s="5" t="str">
         <x:f>IF(A61="","",IF(Z61="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z61,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z61,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF61" s="5"/>
-      <x:c r="AG61" s="5"/>
+      <x:c r="AG61" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="80"/>
-      <x:c r="B62" s="80"/>
-      <x:c r="C62" s="83"/>
-      <x:c r="D62" s="80"/>
-      <x:c r="E62" s="80"/>
-      <x:c r="F62" s="86"/>
-      <x:c r="G62" s="80"/>
-      <x:c r="H62" s="95"/>
-      <x:c r="I62" s="95"/>
-      <x:c r="J62" s="96"/>
-      <x:c r="K62" s="97"/>
-      <x:c r="L62" s="98"/>
-      <x:c r="M62" s="98"/>
-      <x:c r="N62" s="98"/>
-      <x:c r="O62" s="98"/>
-      <x:c r="P62" s="98"/>
-      <x:c r="Q62" s="80"/>
-      <x:c r="R62" s="80"/>
-      <x:c r="S62" s="80"/>
+      <x:c r="A62" s="80" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B62" s="80" t="str">
+        <x:v>13294263</x:v>
+      </x:c>
+      <x:c r="C62" s="83" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="D62" s="80" t="str">
+        <x:v>Албания / Мальта - Юношеская лига УЕФА</x:v>
+      </x:c>
+      <x:c r="E62" s="80" t="str">
+        <x:v>Партизани U19 - Валлетта U19</x:v>
+      </x:c>
+      <x:c r="F62" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G62" s="80" t="str">
+        <x:v>2:0</x:v>
+      </x:c>
+      <x:c r="H62" s="95" t="str">
+        <x:v>Хозяева способны продолжить результативность самостоятельно</x:v>
+      </x:c>
+      <x:c r="I62" s="95" t="str">
+        <x:v>ТБ 4 (Матч)</x:v>
+      </x:c>
+      <x:c r="J62" s="96" t="n">
+        <x:v>2.05</x:v>
+      </x:c>
+      <x:c r="K62" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L62" s="98" t="str">
+        <x:v>corners 6:2; dangerous_attacks 41:16; off_target 10:2; on_target 4:1; possession_rt 58:42; redcards 0:0</x:v>
+      </x:c>
+      <x:c r="M62" s="98" t="str">
+        <x:v>Нет отдельных снимков за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N62" s="98" t="str">
+        <x:v>Хозяева способны продолжить результативность самостоятельно</x:v>
+      </x:c>
+      <x:c r="O62" s="98" t="str">
+        <x:v>Снижение активности при комфортном счёте</x:v>
+      </x:c>
+      <x:c r="P62" s="98" t="str">
+        <x:v>Один снимок; xG и свежая динамика недоступны; внешней проверки нет</x:v>
+      </x:c>
+      <x:c r="Q62" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R62" s="80" t="str">
+        <x:v>ТБ live v2 от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S62" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; Молодёжный/юниорский; run 38538525336 attempt 2</x:v>
+      </x:c>
       <x:c r="T62" s="80"/>
       <x:c r="U62" s="80"/>
       <x:c r="V62" s="89" t="str">
@@ -6441,40 +6647,96 @@
       </x:c>
       <x:c r="W62" s="80" t="str">
         <x:f>IF(A62="","",IF(U62="","Открыт",IF(ISNUMBER(V62),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X62" s="98"/>
-      <x:c r="Y62" s="5"/>
-      <x:c r="Z62" s="5"/>
-      <x:c r="AA62" s="5"/>
-      <x:c r="AB62" s="118"/>
-      <x:c r="AC62" s="119"/>
-      <x:c r="AD62" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X62" s="98" t="str">
+        <x:v>Ещё 2 гола - возврат; исходные условия первичного ответа</x:v>
+      </x:c>
+      <x:c r="Y62" s="5" t="str">
+        <x:v>Агрессивный</x:v>
+      </x:c>
+      <x:c r="Z62" s="5" t="str">
+        <x:v>20261014T155823-13294263</x:v>
+      </x:c>
+      <x:c r="AA62" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB62" s="118" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AC62" s="119" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="AD62" s="119" t="str">
+        <x:v>14.10.2026 15:59</x:v>
+      </x:c>
       <x:c r="AE62" s="5" t="str">
         <x:f>IF(A62="","",IF(Z62="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z62,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z62,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF62" s="5"/>
-      <x:c r="AG62" s="5"/>
+      <x:c r="AG62" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="80"/>
-      <x:c r="B63" s="80"/>
-      <x:c r="C63" s="83"/>
-      <x:c r="D63" s="80"/>
-      <x:c r="E63" s="80"/>
-      <x:c r="F63" s="86"/>
-      <x:c r="G63" s="80"/>
-      <x:c r="H63" s="95"/>
-      <x:c r="I63" s="95"/>
-      <x:c r="J63" s="96"/>
-      <x:c r="K63" s="97"/>
-      <x:c r="L63" s="98"/>
-      <x:c r="M63" s="98"/>
-      <x:c r="N63" s="98"/>
-      <x:c r="O63" s="98"/>
-      <x:c r="P63" s="98"/>
-      <x:c r="Q63" s="80"/>
-      <x:c r="R63" s="80"/>
-      <x:c r="S63" s="80"/>
+      <x:c r="A63" s="80" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B63" s="80" t="str">
+        <x:v>13288150</x:v>
+      </x:c>
+      <x:c r="C63" s="83" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="D63" s="80" t="str">
+        <x:v>Египет - Второй дивизион Б</x:v>
+      </x:c>
+      <x:c r="E63" s="80" t="str">
+        <x:v>Спортинг - Александрия Петролеум</x:v>
+      </x:c>
+      <x:c r="F63" s="86" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G63" s="80" t="str">
+        <x:v>1:1</x:v>
+      </x:c>
+      <x:c r="H63" s="95" t="str">
+        <x:v>Угроза с обеих сторон при равном счёте</x:v>
+      </x:c>
+      <x:c r="I63" s="95" t="str">
+        <x:v>ТБ 3.5 (Матч)</x:v>
+      </x:c>
+      <x:c r="J63" s="96" t="n">
+        <x:v>1.6667</x:v>
+      </x:c>
+      <x:c r="K63" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L63" s="98" t="str">
+        <x:v>corners 1:3; dangerous_attacks 10:15; off_target 0:1; on_target 2:3; possession_rt 52:48; redcards 0:0</x:v>
+      </x:c>
+      <x:c r="M63" s="98" t="str">
+        <x:v>Нет отдельных снимков за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N63" s="98" t="str">
+        <x:v>Угроза с обеих сторон при равном счёте</x:v>
+      </x:c>
+      <x:c r="O63" s="98" t="str">
+        <x:v>Ранняя реализация могла опередить качество моментов</x:v>
+      </x:c>
+      <x:c r="P63" s="98" t="str">
+        <x:v>Один снимок; xG и свежая динамика недоступны; внешней проверки нет</x:v>
+      </x:c>
+      <x:c r="Q63" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R63" s="80" t="str">
+        <x:v>ТБ live v2 от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S63" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; Взрослый мужской; run 38538525336 attempt 2</x:v>
+      </x:c>
       <x:c r="T63" s="80"/>
       <x:c r="U63" s="80"/>
       <x:c r="V63" s="89" t="str">
@@ -6482,40 +6744,96 @@
       </x:c>
       <x:c r="W63" s="80" t="str">
         <x:f>IF(A63="","",IF(U63="","Открыт",IF(ISNUMBER(V63),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X63" s="98"/>
-      <x:c r="Y63" s="5"/>
-      <x:c r="Z63" s="5"/>
-      <x:c r="AA63" s="5"/>
-      <x:c r="AB63" s="118"/>
-      <x:c r="AC63" s="119"/>
-      <x:c r="AD63" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X63" s="98" t="str">
+        <x:v>Без возврата; исходные условия первичного ответа</x:v>
+      </x:c>
+      <x:c r="Y63" s="5" t="str">
+        <x:v>Оптимальный</x:v>
+      </x:c>
+      <x:c r="Z63" s="5" t="str">
+        <x:v>20261014T155823-13288150</x:v>
+      </x:c>
+      <x:c r="AA63" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB63" s="118" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AC63" s="119" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="AD63" s="119" t="str">
+        <x:v>14.10.2026 15:59</x:v>
+      </x:c>
       <x:c r="AE63" s="5" t="str">
         <x:f>IF(A63="","",IF(Z63="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z63,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z63,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF63" s="5"/>
-      <x:c r="AG63" s="5"/>
+      <x:c r="AG63" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="80"/>
-      <x:c r="B64" s="80"/>
-      <x:c r="C64" s="83"/>
-      <x:c r="D64" s="80"/>
-      <x:c r="E64" s="80"/>
-      <x:c r="F64" s="86"/>
-      <x:c r="G64" s="80"/>
-      <x:c r="H64" s="95"/>
-      <x:c r="I64" s="95"/>
-      <x:c r="J64" s="96"/>
-      <x:c r="K64" s="97"/>
-      <x:c r="L64" s="98"/>
-      <x:c r="M64" s="98"/>
-      <x:c r="N64" s="98"/>
-      <x:c r="O64" s="98"/>
-      <x:c r="P64" s="98"/>
-      <x:c r="Q64" s="80"/>
-      <x:c r="R64" s="80"/>
-      <x:c r="S64" s="80"/>
+      <x:c r="A64" s="80" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B64" s="80" t="str">
+        <x:v>13288150</x:v>
+      </x:c>
+      <x:c r="C64" s="83" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="D64" s="80" t="str">
+        <x:v>Египет - Второй дивизион Б</x:v>
+      </x:c>
+      <x:c r="E64" s="80" t="str">
+        <x:v>Спортинг - Александрия Петролеум</x:v>
+      </x:c>
+      <x:c r="F64" s="86" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G64" s="80" t="str">
+        <x:v>1:1</x:v>
+      </x:c>
+      <x:c r="H64" s="95" t="str">
+        <x:v>Угроза с обеих сторон при равном счёте</x:v>
+      </x:c>
+      <x:c r="I64" s="95" t="str">
+        <x:v>ТБ 2.5 (1-й тайм)</x:v>
+      </x:c>
+      <x:c r="J64" s="96" t="n">
+        <x:v>2.075</x:v>
+      </x:c>
+      <x:c r="K64" s="97" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L64" s="98" t="str">
+        <x:v>corners 1:3; dangerous_attacks 10:15; off_target 0:1; on_target 2:3; possession_rt 52:48; redcards 0:0</x:v>
+      </x:c>
+      <x:c r="M64" s="98" t="str">
+        <x:v>Нет отдельных снимков за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N64" s="98" t="str">
+        <x:v>Угроза с обеих сторон при равном счёте</x:v>
+      </x:c>
+      <x:c r="O64" s="98" t="str">
+        <x:v>Ранняя реализация могла опередить качество моментов</x:v>
+      </x:c>
+      <x:c r="P64" s="98" t="str">
+        <x:v>Один снимок; xG и свежая динамика недоступны; внешней проверки нет</x:v>
+      </x:c>
+      <x:c r="Q64" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R64" s="80" t="str">
+        <x:v>ТБ live v2 от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S64" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; Взрослый мужской; run 38538525336 attempt 2</x:v>
+      </x:c>
       <x:c r="T64" s="80"/>
       <x:c r="U64" s="80"/>
       <x:c r="V64" s="89" t="str">
@@ -6523,40 +6841,96 @@
       </x:c>
       <x:c r="W64" s="80" t="str">
         <x:f>IF(A64="","",IF(U64="","Открыт",IF(ISNUMBER(V64),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X64" s="98"/>
-      <x:c r="Y64" s="5"/>
-      <x:c r="Z64" s="5"/>
-      <x:c r="AA64" s="5"/>
-      <x:c r="AB64" s="118"/>
-      <x:c r="AC64" s="119"/>
-      <x:c r="AD64" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X64" s="98" t="str">
+        <x:v>Гол до перерыва; исходные условия первичного ответа</x:v>
+      </x:c>
+      <x:c r="Y64" s="5" t="str">
+        <x:v>Агрессивный</x:v>
+      </x:c>
+      <x:c r="Z64" s="5" t="str">
+        <x:v>20261014T155823-13288150</x:v>
+      </x:c>
+      <x:c r="AA64" s="5" t="str">
+        <x:v>1-й тайм</x:v>
+      </x:c>
+      <x:c r="AB64" s="118" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="AC64" s="119" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="AD64" s="119" t="str">
+        <x:v>14.10.2026 15:59</x:v>
+      </x:c>
       <x:c r="AE64" s="5" t="str">
         <x:f>IF(A64="","",IF(Z64="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z64,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z64,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF64" s="5"/>
-      <x:c r="AG64" s="5"/>
+      <x:c r="AG64" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="80"/>
-      <x:c r="B65" s="80"/>
-      <x:c r="C65" s="83"/>
-      <x:c r="D65" s="80"/>
-      <x:c r="E65" s="80"/>
-      <x:c r="F65" s="86"/>
-      <x:c r="G65" s="80"/>
-      <x:c r="H65" s="95"/>
-      <x:c r="I65" s="95"/>
-      <x:c r="J65" s="96"/>
-      <x:c r="K65" s="97"/>
-      <x:c r="L65" s="98"/>
-      <x:c r="M65" s="98"/>
-      <x:c r="N65" s="98"/>
-      <x:c r="O65" s="98"/>
-      <x:c r="P65" s="98"/>
-      <x:c r="Q65" s="80"/>
-      <x:c r="R65" s="80"/>
-      <x:c r="S65" s="80"/>
+      <x:c r="A65" s="80" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B65" s="80" t="str">
+        <x:v>13146450</x:v>
+      </x:c>
+      <x:c r="C65" s="83" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="D65" s="80" t="str">
+        <x:v>Словакия - Кубок</x:v>
+      </x:c>
+      <x:c r="E65" s="80" t="str">
+        <x:v>Вельке Лудинце - Зволен</x:v>
+      </x:c>
+      <x:c r="F65" s="86" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G65" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H65" s="95" t="str">
+        <x:v>Давление гостей подкреплено ударами</x:v>
+      </x:c>
+      <x:c r="I65" s="95" t="str">
+        <x:v>ТБ 0.5 (1-й тайм)</x:v>
+      </x:c>
+      <x:c r="J65" s="96" t="n">
+        <x:v>1.5333</x:v>
+      </x:c>
+      <x:c r="K65" s="97" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L65" s="98" t="str">
+        <x:v>corners 1:2; dangerous_attacks 10:32; off_target 0:6; on_target 0:3; possession_rt 40:60; redcards 0:0</x:v>
+      </x:c>
+      <x:c r="M65" s="98" t="str">
+        <x:v>Нет отдельных снимков за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N65" s="98" t="str">
+        <x:v>Давление гостей подкреплено ударами</x:v>
+      </x:c>
+      <x:c r="O65" s="98" t="str">
+        <x:v>Односторонняя игра и ограниченное время до перерыва</x:v>
+      </x:c>
+      <x:c r="P65" s="98" t="str">
+        <x:v>Один снимок; xG и свежая динамика недоступны; внешней проверки нет</x:v>
+      </x:c>
+      <x:c r="Q65" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R65" s="80" t="str">
+        <x:v>ТБ live v2 от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S65" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; Взрослый мужской; run 38538525336 attempt 2</x:v>
+      </x:c>
       <x:c r="T65" s="80"/>
       <x:c r="U65" s="80"/>
       <x:c r="V65" s="89" t="str">
@@ -6564,40 +6938,96 @@
       </x:c>
       <x:c r="W65" s="80" t="str">
         <x:f>IF(A65="","",IF(U65="","Открыт",IF(ISNUMBER(V65),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X65" s="98"/>
-      <x:c r="Y65" s="5"/>
-      <x:c r="Z65" s="5"/>
-      <x:c r="AA65" s="5"/>
-      <x:c r="AB65" s="118"/>
-      <x:c r="AC65" s="119"/>
-      <x:c r="AD65" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X65" s="98" t="str">
+        <x:v>Гол до перерыва; исходные условия первичного ответа</x:v>
+      </x:c>
+      <x:c r="Y65" s="5" t="str">
+        <x:v>Оптимальный</x:v>
+      </x:c>
+      <x:c r="Z65" s="5" t="str">
+        <x:v>20261014T155823-13146450</x:v>
+      </x:c>
+      <x:c r="AA65" s="5" t="str">
+        <x:v>1-й тайм</x:v>
+      </x:c>
+      <x:c r="AB65" s="118" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="AC65" s="119" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="AD65" s="119" t="str">
+        <x:v>14.10.2026 15:59</x:v>
+      </x:c>
       <x:c r="AE65" s="5" t="str">
         <x:f>IF(A65="","",IF(Z65="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z65,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z65,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF65" s="5"/>
-      <x:c r="AG65" s="5"/>
+      <x:c r="AG65" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="80"/>
-      <x:c r="B66" s="80"/>
-      <x:c r="C66" s="83"/>
-      <x:c r="D66" s="80"/>
-      <x:c r="E66" s="80"/>
-      <x:c r="F66" s="86"/>
-      <x:c r="G66" s="80"/>
-      <x:c r="H66" s="95"/>
-      <x:c r="I66" s="95"/>
-      <x:c r="J66" s="96"/>
-      <x:c r="K66" s="97"/>
-      <x:c r="L66" s="98"/>
-      <x:c r="M66" s="98"/>
-      <x:c r="N66" s="98"/>
-      <x:c r="O66" s="98"/>
-      <x:c r="P66" s="98"/>
-      <x:c r="Q66" s="80"/>
-      <x:c r="R66" s="80"/>
-      <x:c r="S66" s="80"/>
+      <x:c r="A66" s="80" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B66" s="80" t="str">
+        <x:v>13146450</x:v>
+      </x:c>
+      <x:c r="C66" s="83" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="D66" s="80" t="str">
+        <x:v>Словакия - Кубок</x:v>
+      </x:c>
+      <x:c r="E66" s="80" t="str">
+        <x:v>Вельке Лудинце - Зволен</x:v>
+      </x:c>
+      <x:c r="F66" s="86" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G66" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H66" s="95" t="str">
+        <x:v>Давление гостей подкреплено ударами</x:v>
+      </x:c>
+      <x:c r="I66" s="95" t="str">
+        <x:v>ТБ 0.75 (1-й тайм)</x:v>
+      </x:c>
+      <x:c r="J66" s="96" t="n">
+        <x:v>1.875</x:v>
+      </x:c>
+      <x:c r="K66" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L66" s="98" t="str">
+        <x:v>corners 1:2; dangerous_attacks 10:32; off_target 0:6; on_target 0:3; possession_rt 40:60; redcards 0:0</x:v>
+      </x:c>
+      <x:c r="M66" s="98" t="str">
+        <x:v>Нет отдельных снимков за 10-15 минут</x:v>
+      </x:c>
+      <x:c r="N66" s="98" t="str">
+        <x:v>Давление гостей подкреплено ударами</x:v>
+      </x:c>
+      <x:c r="O66" s="98" t="str">
+        <x:v>Односторонняя игра и ограниченное время до перерыва</x:v>
+      </x:c>
+      <x:c r="P66" s="98" t="str">
+        <x:v>Один снимок; xG и свежая динамика недоступны; внешней проверки нет</x:v>
+      </x:c>
+      <x:c r="Q66" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R66" s="80" t="str">
+        <x:v>ТБ live v2 от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S66" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; Взрослый мужской; run 38538525336 attempt 2</x:v>
+      </x:c>
       <x:c r="T66" s="80"/>
       <x:c r="U66" s="80"/>
       <x:c r="V66" s="89" t="str">
@@ -6605,19 +7035,37 @@
       </x:c>
       <x:c r="W66" s="80" t="str">
         <x:f>IF(A66="","",IF(U66="","Открыт",IF(ISNUMBER(V66),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X66" s="98"/>
-      <x:c r="Y66" s="5"/>
-      <x:c r="Z66" s="5"/>
-      <x:c r="AA66" s="5"/>
-      <x:c r="AB66" s="118"/>
-      <x:c r="AC66" s="119"/>
-      <x:c r="AD66" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X66" s="98" t="str">
+        <x:v>1 гол до перерыва - полувыигрыш; 2 - полный; исходные условия первичного ответа</x:v>
+      </x:c>
+      <x:c r="Y66" s="5" t="str">
+        <x:v>Агрессивный</x:v>
+      </x:c>
+      <x:c r="Z66" s="5" t="str">
+        <x:v>20261014T155823-13146450</x:v>
+      </x:c>
+      <x:c r="AA66" s="5" t="str">
+        <x:v>1-й тайм</x:v>
+      </x:c>
+      <x:c r="AB66" s="118" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="AC66" s="119" t="str">
+        <x:v>14.10.2026 15:58:23</x:v>
+      </x:c>
+      <x:c r="AD66" s="119" t="str">
+        <x:v>14.10.2026 15:59</x:v>
+      </x:c>
       <x:c r="AE66" s="5" t="str">
         <x:f>IF(A66="","",IF(Z66="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z66,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z66,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF66" s="5"/>
-      <x:c r="AG66" s="5"/>
+      <x:c r="AG66" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="80"/>

--- a/Live ТБ/Live ТБ.xlsx
+++ b/Live ТБ/Live ТБ.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R9ba0e1b21a1f4ad5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="R3b09298c027245c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="R41a58ae6ab2748bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R97522867614449da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="Rb8619bd57ec84073"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="R68faba8d7cde4584"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -889,11 +889,11 @@
       </x:c>
       <x:c r="C6" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Оптимальный")</x:f>
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D6" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный")</x:f>
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E6"/>
       <x:c r="F6"/>
@@ -931,11 +931,11 @@
       </x:c>
       <x:c r="C8" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Оптимальный",'Реестр'!$W$6:$W$505,"Открыт")</x:f>
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D8" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$W$6:$W$505,"Открыт")</x:f>
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E8"/>
       <x:c r="F8"/>
@@ -7068,25 +7068,63 @@
       </x:c>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="80"/>
-      <x:c r="B67" s="80"/>
-      <x:c r="C67" s="83"/>
-      <x:c r="D67" s="80"/>
-      <x:c r="E67" s="80"/>
-      <x:c r="F67" s="86"/>
-      <x:c r="G67" s="80"/>
-      <x:c r="H67" s="95"/>
-      <x:c r="I67" s="95"/>
-      <x:c r="J67" s="96"/>
-      <x:c r="K67" s="97"/>
-      <x:c r="L67" s="98"/>
-      <x:c r="M67" s="98"/>
-      <x:c r="N67" s="98"/>
-      <x:c r="O67" s="98"/>
-      <x:c r="P67" s="98"/>
-      <x:c r="Q67" s="80"/>
-      <x:c r="R67" s="80"/>
-      <x:c r="S67" s="80"/>
+      <x:c r="A67" s="80" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B67" s="80" t="str">
+        <x:v>13288150</x:v>
+      </x:c>
+      <x:c r="C67" s="83" t="str">
+        <x:v>14.10.2026 16:23:10</x:v>
+      </x:c>
+      <x:c r="D67" s="80" t="str">
+        <x:v>Египет - Второй дивизион Б</x:v>
+      </x:c>
+      <x:c r="E67" s="80" t="str">
+        <x:v>Спортинг - Александрия Петролеум</x:v>
+      </x:c>
+      <x:c r="F67" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G67" s="80" t="str">
+        <x:v>1:1</x:v>
+      </x:c>
+      <x:c r="H67" s="95" t="str">
+        <x:v>Обе команды создают угрозу при равном счёте</x:v>
+      </x:c>
+      <x:c r="I67" s="95" t="str">
+        <x:v>ТБ 3 матча</x:v>
+      </x:c>
+      <x:c r="J67" s="96" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="K67" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L67" s="98" t="str">
+        <x:v>Угловые 1:3; Опасные атаки 23:30; Мимо 2:3; В створ 3:4; Владение 48:52; Удаления 0:0</x:v>
+      </x:c>
+      <x:c r="M67" s="98" t="str">
+        <x:v>Нет предыдущего сохранённого снимка</x:v>
+      </x:c>
+      <x:c r="N67" s="98" t="str">
+        <x:v>Обе команды создают угрозу при равном счёте</x:v>
+      </x:c>
+      <x:c r="O67" s="98" t="str">
+        <x:v>После перерыва темп может снизиться</x:v>
+      </x:c>
+      <x:c r="P67" s="98" t="str">
+        <x:v>Один накопленный снимок; xG и свежая динамика не подтверждены</x:v>
+      </x:c>
+      <x:c r="Q67" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R67" s="80" t="str">
+        <x:v>ТБ live v2; динамика и точечная проверка от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S67" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; взрослый мужской; run 38571307563</x:v>
+      </x:c>
       <x:c r="T67" s="80"/>
       <x:c r="U67" s="80"/>
       <x:c r="V67" s="89" t="str">
@@ -7094,40 +7132,96 @@
       </x:c>
       <x:c r="W67" s="80" t="str">
         <x:f>IF(A67="","",IF(U67="","Открыт",IF(ISNUMBER(V67),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X67" s="98"/>
-      <x:c r="Y67" s="5"/>
-      <x:c r="Z67" s="5"/>
-      <x:c r="AA67" s="5"/>
-      <x:c r="AB67" s="118"/>
-      <x:c r="AC67" s="119"/>
-      <x:c r="AD67" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X67" s="98" t="str">
+        <x:v>Ещё 1 гол - возврат; первичный ответ. Время вывода зафиксировано сразу после текста перед внешним поиском. Два резервных кандидата проверены за 16 сек, новых подтверждений нет, в прогнозы не включены.</x:v>
+      </x:c>
+      <x:c r="Y67" s="5" t="str">
+        <x:v>Оптимальный</x:v>
+      </x:c>
+      <x:c r="Z67" s="5" t="str">
+        <x:v>20261014T162310-13288150</x:v>
+      </x:c>
+      <x:c r="AA67" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB67" s="118" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AC67" s="119" t="str">
+        <x:v>14.10.2026 16:23:10</x:v>
+      </x:c>
+      <x:c r="AD67" s="119" t="str">
+        <x:v>14.10.2026 16:24:10</x:v>
+      </x:c>
       <x:c r="AE67" s="5" t="str">
         <x:f>IF(A67="","",IF(Z67="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z67,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z67,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF67" s="5"/>
-      <x:c r="AG67" s="5"/>
+      <x:c r="AG67" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="80"/>
-      <x:c r="B68" s="80"/>
-      <x:c r="C68" s="83"/>
-      <x:c r="D68" s="80"/>
-      <x:c r="E68" s="80"/>
-      <x:c r="F68" s="86"/>
-      <x:c r="G68" s="80"/>
-      <x:c r="H68" s="95"/>
-      <x:c r="I68" s="95"/>
-      <x:c r="J68" s="96"/>
-      <x:c r="K68" s="97"/>
-      <x:c r="L68" s="98"/>
-      <x:c r="M68" s="98"/>
-      <x:c r="N68" s="98"/>
-      <x:c r="O68" s="98"/>
-      <x:c r="P68" s="98"/>
-      <x:c r="Q68" s="80"/>
-      <x:c r="R68" s="80"/>
-      <x:c r="S68" s="80"/>
+      <x:c r="A68" s="80" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B68" s="80" t="str">
+        <x:v>13288150</x:v>
+      </x:c>
+      <x:c r="C68" s="83" t="str">
+        <x:v>14.10.2026 16:23:10</x:v>
+      </x:c>
+      <x:c r="D68" s="80" t="str">
+        <x:v>Египет - Второй дивизион Б</x:v>
+      </x:c>
+      <x:c r="E68" s="80" t="str">
+        <x:v>Спортинг - Александрия Петролеум</x:v>
+      </x:c>
+      <x:c r="F68" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G68" s="80" t="str">
+        <x:v>1:1</x:v>
+      </x:c>
+      <x:c r="H68" s="95" t="str">
+        <x:v>Обе команды создают угрозу при равном счёте</x:v>
+      </x:c>
+      <x:c r="I68" s="95" t="str">
+        <x:v>ТБ 3.5 матча</x:v>
+      </x:c>
+      <x:c r="J68" s="96" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="K68" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L68" s="98" t="str">
+        <x:v>Угловые 1:3; Опасные атаки 23:30; Мимо 2:3; В створ 3:4; Владение 48:52; Удаления 0:0</x:v>
+      </x:c>
+      <x:c r="M68" s="98" t="str">
+        <x:v>Нет предыдущего сохранённого снимка</x:v>
+      </x:c>
+      <x:c r="N68" s="98" t="str">
+        <x:v>Обе команды создают угрозу при равном счёте</x:v>
+      </x:c>
+      <x:c r="O68" s="98" t="str">
+        <x:v>После перерыва темп может снизиться</x:v>
+      </x:c>
+      <x:c r="P68" s="98" t="str">
+        <x:v>Один накопленный снимок; xG и свежая динамика не подтверждены</x:v>
+      </x:c>
+      <x:c r="Q68" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R68" s="80" t="str">
+        <x:v>ТБ live v2; динамика и точечная проверка от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S68" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; взрослый мужской; run 38571307563</x:v>
+      </x:c>
       <x:c r="T68" s="80"/>
       <x:c r="U68" s="80"/>
       <x:c r="V68" s="89" t="str">
@@ -7135,40 +7229,96 @@
       </x:c>
       <x:c r="W68" s="80" t="str">
         <x:f>IF(A68="","",IF(U68="","Открыт",IF(ISNUMBER(V68),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X68" s="98"/>
-      <x:c r="Y68" s="5"/>
-      <x:c r="Z68" s="5"/>
-      <x:c r="AA68" s="5"/>
-      <x:c r="AB68" s="118"/>
-      <x:c r="AC68" s="119"/>
-      <x:c r="AD68" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X68" s="98" t="str">
+        <x:v>Без возврата; первичный ответ. Время вывода зафиксировано сразу после текста перед внешним поиском. Два резервных кандидата проверены за 16 сек, новых подтверждений нет, в прогнозы не включены.</x:v>
+      </x:c>
+      <x:c r="Y68" s="5" t="str">
+        <x:v>Агрессивный</x:v>
+      </x:c>
+      <x:c r="Z68" s="5" t="str">
+        <x:v>20261014T162310-13288150</x:v>
+      </x:c>
+      <x:c r="AA68" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB68" s="118" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AC68" s="119" t="str">
+        <x:v>14.10.2026 16:23:10</x:v>
+      </x:c>
+      <x:c r="AD68" s="119" t="str">
+        <x:v>14.10.2026 16:24:10</x:v>
+      </x:c>
       <x:c r="AE68" s="5" t="str">
         <x:f>IF(A68="","",IF(Z68="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z68,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z68,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF68" s="5"/>
-      <x:c r="AG68" s="5"/>
+      <x:c r="AG68" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="80"/>
-      <x:c r="B69" s="80"/>
-      <x:c r="C69" s="83"/>
-      <x:c r="D69" s="80"/>
-      <x:c r="E69" s="80"/>
-      <x:c r="F69" s="86"/>
-      <x:c r="G69" s="80"/>
-      <x:c r="H69" s="95"/>
-      <x:c r="I69" s="95"/>
-      <x:c r="J69" s="96"/>
-      <x:c r="K69" s="97"/>
-      <x:c r="L69" s="98"/>
-      <x:c r="M69" s="98"/>
-      <x:c r="N69" s="98"/>
-      <x:c r="O69" s="98"/>
-      <x:c r="P69" s="98"/>
-      <x:c r="Q69" s="80"/>
-      <x:c r="R69" s="80"/>
-      <x:c r="S69" s="80"/>
+      <x:c r="A69" s="80" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B69" s="80" t="str">
+        <x:v>13288143</x:v>
+      </x:c>
+      <x:c r="C69" s="83" t="str">
+        <x:v>14.10.2026 16:23:10</x:v>
+      </x:c>
+      <x:c r="D69" s="80" t="str">
+        <x:v>Египет - Второй дивизион Б</x:v>
+      </x:c>
+      <x:c r="E69" s="80" t="str">
+        <x:v>Иттихад Эль-Шорта - Миср Иншуранс</x:v>
+      </x:c>
+      <x:c r="F69" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G69" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H69" s="95" t="str">
+        <x:v>Взаимная угроза с преимуществом гостей</x:v>
+      </x:c>
+      <x:c r="I69" s="95" t="str">
+        <x:v>ТБ 1.25 матча</x:v>
+      </x:c>
+      <x:c r="J69" s="96" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="K69" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L69" s="98" t="str">
+        <x:v>Угловые 3:3; Опасные атаки 27:44; Мимо 2:3; В створ 2:4; Владение 43:57; Удаления 0:0</x:v>
+      </x:c>
+      <x:c r="M69" s="98" t="str">
+        <x:v>Нет предыдущего сохранённого снимка</x:v>
+      </x:c>
+      <x:c r="N69" s="98" t="str">
+        <x:v>Взаимная угроза с преимуществом гостей</x:v>
+      </x:c>
+      <x:c r="O69" s="98" t="str">
+        <x:v>Шесть ударов в створ не показывают качество моментов и их давность</x:v>
+      </x:c>
+      <x:c r="P69" s="98" t="str">
+        <x:v>Один накопленный снимок; xG и свежая динамика не подтверждены</x:v>
+      </x:c>
+      <x:c r="Q69" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R69" s="80" t="str">
+        <x:v>ТБ live v2; динамика и точечная проверка от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S69" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; взрослый мужской; run 38571307563</x:v>
+      </x:c>
       <x:c r="T69" s="80"/>
       <x:c r="U69" s="80"/>
       <x:c r="V69" s="89" t="str">
@@ -7176,40 +7326,96 @@
       </x:c>
       <x:c r="W69" s="80" t="str">
         <x:f>IF(A69="","",IF(U69="","Открыт",IF(ISNUMBER(V69),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X69" s="98"/>
-      <x:c r="Y69" s="5"/>
-      <x:c r="Z69" s="5"/>
-      <x:c r="AA69" s="5"/>
-      <x:c r="AB69" s="118"/>
-      <x:c r="AC69" s="119"/>
-      <x:c r="AD69" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X69" s="98" t="str">
+        <x:v>Ещё 1 гол - полупроигрыш; первичный ответ. Время вывода зафиксировано сразу после текста перед внешним поиском. Два резервных кандидата проверены за 16 сек, новых подтверждений нет, в прогнозы не включены.</x:v>
+      </x:c>
+      <x:c r="Y69" s="5" t="str">
+        <x:v>Оптимальный</x:v>
+      </x:c>
+      <x:c r="Z69" s="5" t="str">
+        <x:v>20261014T162310-13288143</x:v>
+      </x:c>
+      <x:c r="AA69" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB69" s="118" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="AC69" s="119" t="str">
+        <x:v>14.10.2026 16:23:10</x:v>
+      </x:c>
+      <x:c r="AD69" s="119" t="str">
+        <x:v>14.10.2026 16:24:10</x:v>
+      </x:c>
       <x:c r="AE69" s="5" t="str">
         <x:f>IF(A69="","",IF(Z69="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z69,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z69,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF69" s="5"/>
-      <x:c r="AG69" s="5"/>
+      <x:c r="AG69" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="80"/>
-      <x:c r="B70" s="80"/>
-      <x:c r="C70" s="83"/>
-      <x:c r="D70" s="80"/>
-      <x:c r="E70" s="80"/>
-      <x:c r="F70" s="86"/>
-      <x:c r="G70" s="80"/>
-      <x:c r="H70" s="95"/>
-      <x:c r="I70" s="95"/>
-      <x:c r="J70" s="96"/>
-      <x:c r="K70" s="97"/>
-      <x:c r="L70" s="98"/>
-      <x:c r="M70" s="98"/>
-      <x:c r="N70" s="98"/>
-      <x:c r="O70" s="98"/>
-      <x:c r="P70" s="98"/>
-      <x:c r="Q70" s="80"/>
-      <x:c r="R70" s="80"/>
-      <x:c r="S70" s="80"/>
+      <x:c r="A70" s="80" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B70" s="80" t="str">
+        <x:v>13288143</x:v>
+      </x:c>
+      <x:c r="C70" s="83" t="str">
+        <x:v>14.10.2026 16:23:10</x:v>
+      </x:c>
+      <x:c r="D70" s="80" t="str">
+        <x:v>Египет - Второй дивизион Б</x:v>
+      </x:c>
+      <x:c r="E70" s="80" t="str">
+        <x:v>Иттихад Эль-Шорта - Миср Иншуранс</x:v>
+      </x:c>
+      <x:c r="F70" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G70" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H70" s="95" t="str">
+        <x:v>Взаимная угроза с преимуществом гостей</x:v>
+      </x:c>
+      <x:c r="I70" s="95" t="str">
+        <x:v>ТБ 1.5 матча</x:v>
+      </x:c>
+      <x:c r="J70" s="96" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="K70" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L70" s="98" t="str">
+        <x:v>Угловые 3:3; Опасные атаки 27:44; Мимо 2:3; В створ 2:4; Владение 43:57; Удаления 0:0</x:v>
+      </x:c>
+      <x:c r="M70" s="98" t="str">
+        <x:v>Нет предыдущего сохранённого снимка</x:v>
+      </x:c>
+      <x:c r="N70" s="98" t="str">
+        <x:v>Взаимная угроза с преимуществом гостей</x:v>
+      </x:c>
+      <x:c r="O70" s="98" t="str">
+        <x:v>Шесть ударов в створ не показывают качество моментов и их давность</x:v>
+      </x:c>
+      <x:c r="P70" s="98" t="str">
+        <x:v>Один накопленный снимок; xG и свежая динамика не подтверждены</x:v>
+      </x:c>
+      <x:c r="Q70" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R70" s="80" t="str">
+        <x:v>ТБ live v2; динамика и точечная проверка от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S70" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; взрослый мужской; run 38571307563</x:v>
+      </x:c>
       <x:c r="T70" s="80"/>
       <x:c r="U70" s="80"/>
       <x:c r="V70" s="89" t="str">
@@ -7217,40 +7423,96 @@
       </x:c>
       <x:c r="W70" s="80" t="str">
         <x:f>IF(A70="","",IF(U70="","Открыт",IF(ISNUMBER(V70),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X70" s="98"/>
-      <x:c r="Y70" s="5"/>
-      <x:c r="Z70" s="5"/>
-      <x:c r="AA70" s="5"/>
-      <x:c r="AB70" s="118"/>
-      <x:c r="AC70" s="119"/>
-      <x:c r="AD70" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X70" s="98" t="str">
+        <x:v>Без возврата; первичный ответ. Время вывода зафиксировано сразу после текста перед внешним поиском. Два резервных кандидата проверены за 16 сек, новых подтверждений нет, в прогнозы не включены.</x:v>
+      </x:c>
+      <x:c r="Y70" s="5" t="str">
+        <x:v>Агрессивный</x:v>
+      </x:c>
+      <x:c r="Z70" s="5" t="str">
+        <x:v>20261014T162310-13288143</x:v>
+      </x:c>
+      <x:c r="AA70" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB70" s="118" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="AC70" s="119" t="str">
+        <x:v>14.10.2026 16:23:10</x:v>
+      </x:c>
+      <x:c r="AD70" s="119" t="str">
+        <x:v>14.10.2026 16:24:10</x:v>
+      </x:c>
       <x:c r="AE70" s="5" t="str">
         <x:f>IF(A70="","",IF(Z70="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z70,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z70,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF70" s="5"/>
-      <x:c r="AG70" s="5"/>
+      <x:c r="AG70" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="80"/>
-      <x:c r="B71" s="80"/>
-      <x:c r="C71" s="83"/>
-      <x:c r="D71" s="80"/>
-      <x:c r="E71" s="80"/>
-      <x:c r="F71" s="86"/>
-      <x:c r="G71" s="80"/>
-      <x:c r="H71" s="95"/>
-      <x:c r="I71" s="95"/>
-      <x:c r="J71" s="96"/>
-      <x:c r="K71" s="97"/>
-      <x:c r="L71" s="98"/>
-      <x:c r="M71" s="98"/>
-      <x:c r="N71" s="98"/>
-      <x:c r="O71" s="98"/>
-      <x:c r="P71" s="98"/>
-      <x:c r="Q71" s="80"/>
-      <x:c r="R71" s="80"/>
-      <x:c r="S71" s="80"/>
+      <x:c r="A71" s="80" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B71" s="80" t="str">
+        <x:v>13288144</x:v>
+      </x:c>
+      <x:c r="C71" s="83" t="str">
+        <x:v>14.10.2026 16:23:10</x:v>
+      </x:c>
+      <x:c r="D71" s="80" t="str">
+        <x:v>Египет - Второй дивизион Б</x:v>
+      </x:c>
+      <x:c r="E71" s="80" t="str">
+        <x:v>МС Ага - Бияла</x:v>
+      </x:c>
+      <x:c r="F71" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G71" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H71" s="95" t="str">
+        <x:v>Хозяева создают одностороннюю угрозу; для оптимального достаточно одного гола</x:v>
+      </x:c>
+      <x:c r="I71" s="95" t="str">
+        <x:v>ТБ 0.5 матча</x:v>
+      </x:c>
+      <x:c r="J71" s="96" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="K71" s="97" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L71" s="98" t="str">
+        <x:v>Угловые 1:0; Опасные атаки 17:10; Мимо 2:0; В створ 4:0; Владение 47:53; Удаления 0:0</x:v>
+      </x:c>
+      <x:c r="M71" s="98" t="str">
+        <x:v>Нет предыдущего сохранённого снимка</x:v>
+      </x:c>
+      <x:c r="N71" s="98" t="str">
+        <x:v>Хозяева создают одностороннюю угрозу; для оптимального достаточно одного гола</x:v>
+      </x:c>
+      <x:c r="O71" s="98" t="str">
+        <x:v>Гости пока почти не помогают результативности</x:v>
+      </x:c>
+      <x:c r="P71" s="98" t="str">
+        <x:v>Один накопленный снимок; xG и свежая динамика не подтверждены</x:v>
+      </x:c>
+      <x:c r="Q71" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R71" s="80" t="str">
+        <x:v>ТБ live v2; динамика и точечная проверка от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S71" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; взрослый мужской; run 38571307563</x:v>
+      </x:c>
       <x:c r="T71" s="80"/>
       <x:c r="U71" s="80"/>
       <x:c r="V71" s="89" t="str">
@@ -7258,40 +7520,96 @@
       </x:c>
       <x:c r="W71" s="80" t="str">
         <x:f>IF(A71="","",IF(U71="","Открыт",IF(ISNUMBER(V71),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X71" s="98"/>
-      <x:c r="Y71" s="5"/>
-      <x:c r="Z71" s="5"/>
-      <x:c r="AA71" s="5"/>
-      <x:c r="AB71" s="118"/>
-      <x:c r="AC71" s="119"/>
-      <x:c r="AD71" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X71" s="98" t="str">
+        <x:v>Без возврата; первичный ответ. Время вывода зафиксировано сразу после текста перед внешним поиском. Два резервных кандидата проверены за 16 сек, новых подтверждений нет, в прогнозы не включены.</x:v>
+      </x:c>
+      <x:c r="Y71" s="5" t="str">
+        <x:v>Оптимальный</x:v>
+      </x:c>
+      <x:c r="Z71" s="5" t="str">
+        <x:v>20261014T162310-13288144</x:v>
+      </x:c>
+      <x:c r="AA71" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB71" s="118" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="AC71" s="119" t="str">
+        <x:v>14.10.2026 16:23:10</x:v>
+      </x:c>
+      <x:c r="AD71" s="119" t="str">
+        <x:v>14.10.2026 16:24:10</x:v>
+      </x:c>
       <x:c r="AE71" s="5" t="str">
         <x:f>IF(A71="","",IF(Z71="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z71,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z71,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF71" s="5"/>
-      <x:c r="AG71" s="5"/>
+      <x:c r="AG71" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="80"/>
-      <x:c r="B72" s="80"/>
-      <x:c r="C72" s="83"/>
-      <x:c r="D72" s="80"/>
-      <x:c r="E72" s="80"/>
-      <x:c r="F72" s="86"/>
-      <x:c r="G72" s="80"/>
-      <x:c r="H72" s="95"/>
-      <x:c r="I72" s="95"/>
-      <x:c r="J72" s="96"/>
-      <x:c r="K72" s="97"/>
-      <x:c r="L72" s="98"/>
-      <x:c r="M72" s="98"/>
-      <x:c r="N72" s="98"/>
-      <x:c r="O72" s="98"/>
-      <x:c r="P72" s="98"/>
-      <x:c r="Q72" s="80"/>
-      <x:c r="R72" s="80"/>
-      <x:c r="S72" s="80"/>
+      <x:c r="A72" s="80" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B72" s="80" t="str">
+        <x:v>13288144</x:v>
+      </x:c>
+      <x:c r="C72" s="83" t="str">
+        <x:v>14.10.2026 16:23:10</x:v>
+      </x:c>
+      <x:c r="D72" s="80" t="str">
+        <x:v>Египет - Второй дивизион Б</x:v>
+      </x:c>
+      <x:c r="E72" s="80" t="str">
+        <x:v>МС Ага - Бияла</x:v>
+      </x:c>
+      <x:c r="F72" s="86" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G72" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H72" s="95" t="str">
+        <x:v>Хозяева создают одностороннюю угрозу; для оптимального достаточно одного гола</x:v>
+      </x:c>
+      <x:c r="I72" s="95" t="str">
+        <x:v>ТБ 0.75 матча</x:v>
+      </x:c>
+      <x:c r="J72" s="96" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="K72" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L72" s="98" t="str">
+        <x:v>Угловые 1:0; Опасные атаки 17:10; Мимо 2:0; В створ 4:0; Владение 47:53; Удаления 0:0</x:v>
+      </x:c>
+      <x:c r="M72" s="98" t="str">
+        <x:v>Нет предыдущего сохранённого снимка</x:v>
+      </x:c>
+      <x:c r="N72" s="98" t="str">
+        <x:v>Хозяева создают одностороннюю угрозу; для оптимального достаточно одного гола</x:v>
+      </x:c>
+      <x:c r="O72" s="98" t="str">
+        <x:v>Гости пока почти не помогают результативности</x:v>
+      </x:c>
+      <x:c r="P72" s="98" t="str">
+        <x:v>Один накопленный снимок; xG и свежая динамика не подтверждены</x:v>
+      </x:c>
+      <x:c r="Q72" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R72" s="80" t="str">
+        <x:v>ТБ live v2; динамика и точечная проверка от 14.10.2026</x:v>
+      </x:c>
+      <x:c r="S72" s="80" t="str">
+        <x:v>BetsAPI / Bet365 full markets; взрослый мужской; run 38571307563</x:v>
+      </x:c>
       <x:c r="T72" s="80"/>
       <x:c r="U72" s="80"/>
       <x:c r="V72" s="89" t="str">
@@ -7299,19 +7617,37 @@
       </x:c>
       <x:c r="W72" s="80" t="str">
         <x:f>IF(A72="","",IF(U72="","Открыт",IF(ISNUMBER(V72),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X72" s="98"/>
-      <x:c r="Y72" s="5"/>
-      <x:c r="Z72" s="5"/>
-      <x:c r="AA72" s="5"/>
-      <x:c r="AB72" s="118"/>
-      <x:c r="AC72" s="119"/>
-      <x:c r="AD72" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X72" s="98" t="str">
+        <x:v>Ещё 1 гол - полувыигрыш; 2 - полный выигрыш; первичный ответ. Время вывода зафиксировано сразу после текста перед внешним поиском. Два резервных кандидата проверены за 16 сек, новых подтверждений нет, в прогнозы не включены.</x:v>
+      </x:c>
+      <x:c r="Y72" s="5" t="str">
+        <x:v>Агрессивный</x:v>
+      </x:c>
+      <x:c r="Z72" s="5" t="str">
+        <x:v>20261014T162310-13288144</x:v>
+      </x:c>
+      <x:c r="AA72" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB72" s="118" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="AC72" s="119" t="str">
+        <x:v>14.10.2026 16:23:10</x:v>
+      </x:c>
+      <x:c r="AD72" s="119" t="str">
+        <x:v>14.10.2026 16:24:10</x:v>
+      </x:c>
       <x:c r="AE72" s="5" t="str">
         <x:f>IF(A72="","",IF(Z72="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z72,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z72,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF72" s="5"/>
-      <x:c r="AG72" s="5"/>
+      <x:c r="AG72" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="80"/>

--- a/Live ТБ/Live ТБ.xlsx
+++ b/Live ТБ/Live ТБ.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R97522867614449da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="Rb8619bd57ec84073"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="R68faba8d7cde4584"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" r:id="R518d3d0de3904d0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр" sheetId="2" r:id="Rb8b4f380b534441c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="3" r:id="R3d7c7b229e7d42c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -889,11 +889,11 @@
       </x:c>
       <x:c r="C6" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Оптимальный")</x:f>
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный")</x:f>
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E6"/>
       <x:c r="F6"/>
@@ -910,11 +910,11 @@
       </x:c>
       <x:c r="C7" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Оптимальный",'Реестр'!$W$6:$W$505,"Рассчитан")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D7" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$W$6:$W$505,"Рассчитан")</x:f>
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E7"/>
       <x:c r="F7"/>
@@ -935,7 +935,7 @@
       </x:c>
       <x:c r="D8" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$W$6:$W$505,"Открыт")</x:f>
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E8"/>
       <x:c r="F8"/>
@@ -952,7 +952,7 @@
       </x:c>
       <x:c r="C9" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Оптимальный",'Реестр'!$U$6:$U$505,"Выигрыш")+COUNTIFS('Реестр'!$Y$6:$Y$505,"Оптимальный",'Реестр'!$U$6:$U$505,"Плюс")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D9" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$U$6:$U$505,"Выигрыш")+COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$U$6:$U$505,"Плюс")</x:f>
@@ -998,7 +998,7 @@
       </x:c>
       <x:c r="D11" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$U$6:$U$505,"Возврат")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E11"/>
       <x:c r="F11"/>
@@ -1036,11 +1036,11 @@
       </x:c>
       <x:c r="C13" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Оптимальный",'Реестр'!$U$6:$U$505,"Поражение")+COUNTIFS('Реестр'!$Y$6:$Y$505,"Оптимальный",'Реестр'!$U$6:$U$505,"Минус")</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D13" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$U$6:$U$505,"Поражение")+COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$U$6:$U$505,"Минус")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E13"/>
       <x:c r="F13"/>
@@ -1057,11 +1057,11 @@
       </x:c>
       <x:c r="C14" s="128" t="n">
         <x:f>SUMIFS('Реестр'!$V$6:$V$505,'Реестр'!$Y$6:$Y$505,"Оптимальный",'Реестр'!$W$6:$W$505,"Рассчитан")</x:f>
-        <x:v>0</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D14" s="128" t="n">
         <x:f>SUMIFS('Реестр'!$V$6:$V$505,'Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$W$6:$W$505,"Рассчитан")</x:f>
-        <x:v>0</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="E14"/>
       <x:c r="F14"/>
@@ -1076,11 +1076,13 @@
         <x:f>IF(B7=0,"",B14/B7)</x:f>
         <x:v>0.06981132075471698</x:v>
       </x:c>
-      <x:c r="C15" s="129" t="str">
+      <x:c r="C15" s="129" t="n">
         <x:f>IF(C7=0,"",C14/C7)</x:f>
-      </x:c>
-      <x:c r="D15" s="129" t="str">
+        <x:v>-0.4666666666666666</x:v>
+      </x:c>
+      <x:c r="D15" s="129" t="n">
         <x:f>IF(D7=0,"",D14/D7)</x:f>
+        <x:v>-0.75</x:v>
       </x:c>
       <x:c r="E15"/>
       <x:c r="F15"/>
@@ -1095,11 +1097,13 @@
         <x:f>IF(B7=0,"",SUMIFS('Реестр'!$J$6:$J$505,'Реестр'!$Y$6:$Y$505,"История без разделения",'Реестр'!$W$6:$W$505,"Рассчитан")/B7)</x:f>
         <x:v>1.9047169811320754</x:v>
       </x:c>
-      <x:c r="C16" s="125" t="str">
+      <x:c r="C16" s="125" t="n">
         <x:f>IF(C7=0,"",SUMIFS('Реестр'!$J$6:$J$505,'Реестр'!$Y$6:$Y$505,"Оптимальный",'Реестр'!$W$6:$W$505,"Рассчитан")/C7)</x:f>
-      </x:c>
-      <x:c r="D16" s="125" t="str">
+        <x:v>1.5527666666666669</x:v>
+      </x:c>
+      <x:c r="D16" s="125" t="n">
         <x:f>IF(D7=0,"",SUMIFS('Реестр'!$J$6:$J$505,'Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$W$6:$W$505,"Рассчитан")/D7)</x:f>
+        <x:v>2.0625</x:v>
       </x:c>
       <x:c r="E16"/>
       <x:c r="F16"/>
@@ -1114,11 +1118,13 @@
         <x:f>IF(B7=0,"",(B9+B10)/B7)</x:f>
         <x:v>0.5283018867924528</x:v>
       </x:c>
-      <x:c r="C17" s="126" t="str">
+      <x:c r="C17" s="126" t="n">
         <x:f>IF(C7=0,"",(C9+C10)/C7)</x:f>
-      </x:c>
-      <x:c r="D17" s="126" t="str">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
+      <x:c r="D17" s="126" t="n">
         <x:f>IF(D7=0,"",(D9+D10)/D7)</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="23" customHeight="1">
@@ -1142,11 +1148,11 @@
       <x:c r="B20" s="124"/>
       <x:c r="C20" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Оптимальный",'Реестр'!$AE$6:$AE$505,"Да")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D20" s="124" t="n">
         <x:f>COUNTIFS('Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$AE$6:$AE$505,"Да")</x:f>
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="23" customHeight="1">
@@ -1156,11 +1162,11 @@
       <x:c r="B21" s="128"/>
       <x:c r="C21" s="128" t="n">
         <x:f>SUMIFS('Реестр'!$V$6:$V$505,'Реестр'!$Y$6:$Y$505,"Оптимальный",'Реестр'!$AE$6:$AE$505,"Да")</x:f>
-        <x:v>0</x:v>
+        <x:v>-1.4</x:v>
       </x:c>
       <x:c r="D21" s="128" t="n">
         <x:f>SUMIFS('Реестр'!$V$6:$V$505,'Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$AE$6:$AE$505,"Да")</x:f>
-        <x:v>0</x:v>
+        <x:v>-2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -1168,11 +1174,13 @@
         <x:v>ROI по парам</x:v>
       </x:c>
       <x:c r="B22" s="129"/>
-      <x:c r="C22" s="129" t="str">
+      <x:c r="C22" s="129" t="n">
         <x:f>IF(C20=0,"",C21/C20)</x:f>
-      </x:c>
-      <x:c r="D22" s="129" t="str">
+        <x:v>-0.4666666666666666</x:v>
+      </x:c>
+      <x:c r="D22" s="129" t="n">
         <x:f>IF(D20=0,"",D21/D20)</x:f>
+        <x:v>-0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -1180,11 +1188,13 @@
         <x:v>Средний коэф. по парам</x:v>
       </x:c>
       <x:c r="B23" s="125"/>
-      <x:c r="C23" s="125" t="str">
+      <x:c r="C23" s="125" t="n">
         <x:f>IF(C20=0,"",SUMIFS('Реестр'!$J$6:$J$505,'Реестр'!$Y$6:$Y$505,"Оптимальный",'Реестр'!$AE$6:$AE$505,"Да")/C20)</x:f>
-      </x:c>
-      <x:c r="D23" s="125" t="str">
+        <x:v>1.5527666666666669</x:v>
+      </x:c>
+      <x:c r="D23" s="125" t="n">
         <x:f>IF(D20=0,"",SUMIFS('Реестр'!$J$6:$J$505,'Реестр'!$Y$6:$Y$505,"Агрессивный",'Реестр'!$AE$6:$AE$505,"Да")/D20)</x:f>
+        <x:v>2.058333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -6349,14 +6359,19 @@
       <x:c r="S59" s="80" t="str">
         <x:v>BetsAPI / Bet365 full markets; Резервная команда против взрослой; run 38538525336 attempt 2</x:v>
       </x:c>
-      <x:c r="T59" s="80"/>
-      <x:c r="U59" s="80"/>
-      <x:c r="V59" s="89" t="str">
+      <x:c r="T59" s="80" t="str">
+        <x:v>0:1</x:v>
+      </x:c>
+      <x:c r="U59" s="80" t="str">
+        <x:v>Поражение</x:v>
+      </x:c>
+      <x:c r="V59" s="89" t="n">
         <x:f>IF(A59="","",IF(U59="","",IF(U59="Выигрыш",J59-1,IF(U59="Полувыигрыш",(J59-1)/2,IF(U59="Возврат",0,IF(U59="Полупроигрыш",-0.5,IF(U59="Поражение",-1,"Проверить результат")))))))</x:f>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="W59" s="80" t="str">
         <x:f>IF(A59="","",IF(U59="","Открыт",IF(ISNUMBER(V59),"Рассчитан","Проверить результат")))</x:f>
-        <x:v>Открыт</x:v>
+        <x:v>Рассчитан</x:v>
       </x:c>
       <x:c r="X59" s="98" t="str">
         <x:v>Ещё 1 гол - возврат; исходные условия первичного ответа</x:v>
@@ -6381,9 +6396,11 @@
       </x:c>
       <x:c r="AE59" s="5" t="str">
         <x:f>IF(A59="","",IF(Z59="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z59,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z59,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AF59" s="5"/>
+        <x:v>Да</x:v>
+      </x:c>
+      <x:c r="AF59" s="5" t="str">
+        <x:v>https://www.sofascore.com/football/match/olympiacos-athens-kallithea-fc/fpbsFoid | FT 0:1; матч завершён | Проверено 14.10.2026 17:14:56 МСК</x:v>
+      </x:c>
       <x:c r="AG59" s="5" t="str">
         <x:v>Два контура v2</x:v>
       </x:c>
@@ -6446,14 +6463,19 @@
       <x:c r="S60" s="80" t="str">
         <x:v>BetsAPI / Bet365 full markets; Резервная команда против взрослой; run 38538525336 attempt 2</x:v>
       </x:c>
-      <x:c r="T60" s="80"/>
-      <x:c r="U60" s="80"/>
-      <x:c r="V60" s="89" t="str">
+      <x:c r="T60" s="80" t="str">
+        <x:v>0:1</x:v>
+      </x:c>
+      <x:c r="U60" s="80" t="str">
+        <x:v>Поражение</x:v>
+      </x:c>
+      <x:c r="V60" s="89" t="n">
         <x:f>IF(A60="","",IF(U60="","",IF(U60="Выигрыш",J60-1,IF(U60="Полувыигрыш",(J60-1)/2,IF(U60="Возврат",0,IF(U60="Полупроигрыш",-0.5,IF(U60="Поражение",-1,"Проверить результат")))))))</x:f>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="W60" s="80" t="str">
         <x:f>IF(A60="","",IF(U60="","Открыт",IF(ISNUMBER(V60),"Рассчитан","Проверить результат")))</x:f>
-        <x:v>Открыт</x:v>
+        <x:v>Рассчитан</x:v>
       </x:c>
       <x:c r="X60" s="98" t="str">
         <x:v>Без возврата; исходные условия первичного ответа</x:v>
@@ -6478,9 +6500,11 @@
       </x:c>
       <x:c r="AE60" s="5" t="str">
         <x:f>IF(A60="","",IF(Z60="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z60,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z60,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AF60" s="5"/>
+        <x:v>Да</x:v>
+      </x:c>
+      <x:c r="AF60" s="5" t="str">
+        <x:v>https://www.sofascore.com/football/match/olympiacos-athens-kallithea-fc/fpbsFoid | FT 0:1; матч завершён | Проверено 14.10.2026 17:14:56 МСК</x:v>
+      </x:c>
       <x:c r="AG60" s="5" t="str">
         <x:v>Два контура v2</x:v>
       </x:c>
@@ -6543,14 +6567,19 @@
       <x:c r="S61" s="80" t="str">
         <x:v>BetsAPI / Bet365 full markets; Молодёжный/юниорский; run 38538525336 attempt 2</x:v>
       </x:c>
-      <x:c r="T61" s="80"/>
-      <x:c r="U61" s="80"/>
-      <x:c r="V61" s="89" t="str">
+      <x:c r="T61" s="80" t="str">
+        <x:v>4:0</x:v>
+      </x:c>
+      <x:c r="U61" s="80" t="str">
+        <x:v>Выигрыш</x:v>
+      </x:c>
+      <x:c r="V61" s="89" t="n">
         <x:f>IF(A61="","",IF(U61="","",IF(U61="Выигрыш",J61-1,IF(U61="Полувыигрыш",(J61-1)/2,IF(U61="Возврат",0,IF(U61="Полупроигрыш",-0.5,IF(U61="Поражение",-1,"Проверить результат")))))))</x:f>
+        <x:v>0.6000000000000001</x:v>
       </x:c>
       <x:c r="W61" s="80" t="str">
         <x:f>IF(A61="","",IF(U61="","Открыт",IF(ISNUMBER(V61),"Рассчитан","Проверить результат")))</x:f>
-        <x:v>Открыт</x:v>
+        <x:v>Рассчитан</x:v>
       </x:c>
       <x:c r="X61" s="98" t="str">
         <x:v>Без возврата; исходные условия первичного ответа</x:v>
@@ -6575,9 +6604,11 @@
       </x:c>
       <x:c r="AE61" s="5" t="str">
         <x:f>IF(A61="","",IF(Z61="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z61,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z61,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AF61" s="5"/>
+        <x:v>Да</x:v>
+      </x:c>
+      <x:c r="AF61" s="5" t="str">
+        <x:v>https://www.sofascore.com/football/match/partizani-tirana-u19-u19-valletta-u19/AQRgsxFik | FT 4:0; матч завершён; суммарный счёт двух матчей 6:0 не используется | Проверено 14.10.2026 17:14:56 МСК</x:v>
+      </x:c>
       <x:c r="AG61" s="5" t="str">
         <x:v>Два контура v2</x:v>
       </x:c>
@@ -6640,14 +6671,19 @@
       <x:c r="S62" s="80" t="str">
         <x:v>BetsAPI / Bet365 full markets; Молодёжный/юниорский; run 38538525336 attempt 2</x:v>
       </x:c>
-      <x:c r="T62" s="80"/>
-      <x:c r="U62" s="80"/>
-      <x:c r="V62" s="89" t="str">
+      <x:c r="T62" s="80" t="str">
+        <x:v>4:0</x:v>
+      </x:c>
+      <x:c r="U62" s="80" t="str">
+        <x:v>Возврат</x:v>
+      </x:c>
+      <x:c r="V62" s="89" t="n">
         <x:f>IF(A62="","",IF(U62="","",IF(U62="Выигрыш",J62-1,IF(U62="Полувыигрыш",(J62-1)/2,IF(U62="Возврат",0,IF(U62="Полупроигрыш",-0.5,IF(U62="Поражение",-1,"Проверить результат")))))))</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W62" s="80" t="str">
         <x:f>IF(A62="","",IF(U62="","Открыт",IF(ISNUMBER(V62),"Рассчитан","Проверить результат")))</x:f>
-        <x:v>Открыт</x:v>
+        <x:v>Рассчитан</x:v>
       </x:c>
       <x:c r="X62" s="98" t="str">
         <x:v>Ещё 2 гола - возврат; исходные условия первичного ответа</x:v>
@@ -6672,9 +6708,11 @@
       </x:c>
       <x:c r="AE62" s="5" t="str">
         <x:f>IF(A62="","",IF(Z62="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z62,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z62,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AF62" s="5"/>
+        <x:v>Да</x:v>
+      </x:c>
+      <x:c r="AF62" s="5" t="str">
+        <x:v>https://www.sofascore.com/football/match/partizani-tirana-u19-u19-valletta-u19/AQRgsxFik | FT 4:0; матч завершён; ТБ 4 возвращён | Проверено 14.10.2026 17:14:56 МСК</x:v>
+      </x:c>
       <x:c r="AG62" s="5" t="str">
         <x:v>Два контура v2</x:v>
       </x:c>
@@ -6834,14 +6872,19 @@
       <x:c r="S64" s="80" t="str">
         <x:v>BetsAPI / Bet365 full markets; Взрослый мужской; run 38538525336 attempt 2</x:v>
       </x:c>
-      <x:c r="T64" s="80"/>
-      <x:c r="U64" s="80"/>
-      <x:c r="V64" s="89" t="str">
+      <x:c r="T64" s="80" t="str">
+        <x:v>1:1</x:v>
+      </x:c>
+      <x:c r="U64" s="80" t="str">
+        <x:v>Поражение</x:v>
+      </x:c>
+      <x:c r="V64" s="89" t="n">
         <x:f>IF(A64="","",IF(U64="","",IF(U64="Выигрыш",J64-1,IF(U64="Полувыигрыш",(J64-1)/2,IF(U64="Возврат",0,IF(U64="Полупроигрыш",-0.5,IF(U64="Поражение",-1,"Проверить результат")))))))</x:f>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="W64" s="80" t="str">
         <x:f>IF(A64="","",IF(U64="","Открыт",IF(ISNUMBER(V64),"Рассчитан","Проверить результат")))</x:f>
-        <x:v>Открыт</x:v>
+        <x:v>Рассчитан</x:v>
       </x:c>
       <x:c r="X64" s="98" t="str">
         <x:v>Гол до перерыва; исходные условия первичного ответа</x:v>
@@ -6868,7 +6911,9 @@
         <x:f>IF(A64="","",IF(Z64="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z64,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z64,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
         <x:v>Нет</x:v>
       </x:c>
-      <x:c r="AF64" s="5"/>
+      <x:c r="AF64" s="5" t="str">
+        <x:v>https://www.sofascore.com/football/match/sporting-alexandria-alexandria-petroleum/AWcesKjie | HT 1:1; первый тайм завершён | Проверено 14.10.2026 17:14:56 МСК</x:v>
+      </x:c>
       <x:c r="AG64" s="5" t="str">
         <x:v>Два контура v2</x:v>
       </x:c>
@@ -6931,14 +6976,19 @@
       <x:c r="S65" s="80" t="str">
         <x:v>BetsAPI / Bet365 full markets; Взрослый мужской; run 38538525336 attempt 2</x:v>
       </x:c>
-      <x:c r="T65" s="80"/>
-      <x:c r="U65" s="80"/>
-      <x:c r="V65" s="89" t="str">
+      <x:c r="T65" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="U65" s="80" t="str">
+        <x:v>Поражение</x:v>
+      </x:c>
+      <x:c r="V65" s="89" t="n">
         <x:f>IF(A65="","",IF(U65="","",IF(U65="Выигрыш",J65-1,IF(U65="Полувыигрыш",(J65-1)/2,IF(U65="Возврат",0,IF(U65="Полупроигрыш",-0.5,IF(U65="Поражение",-1,"Проверить результат")))))))</x:f>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="W65" s="80" t="str">
         <x:f>IF(A65="","",IF(U65="","Открыт",IF(ISNUMBER(V65),"Рассчитан","Проверить результат")))</x:f>
-        <x:v>Открыт</x:v>
+        <x:v>Рассчитан</x:v>
       </x:c>
       <x:c r="X65" s="98" t="str">
         <x:v>Гол до перерыва; исходные условия первичного ответа</x:v>
@@ -6963,9 +7013,11 @@
       </x:c>
       <x:c r="AE65" s="5" t="str">
         <x:f>IF(A65="","",IF(Z65="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z65,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z65,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AF65" s="5"/>
+        <x:v>Да</x:v>
+      </x:c>
+      <x:c r="AF65" s="5" t="str">
+        <x:v>https://www.live-result.com/football/matches/match1800494_TJ_Druzstevnik_Velke_Ludince-Lokomotiva_Zvolen-live-online | Первый тайм 0:0 по статистике периода и хронологии; голы 46 и 76 минут во втором тайме. Согласуется со срезом BetsAPI на перерыве 16:25:03. | Проверено 14.10.2026 17:14:56 МСК</x:v>
+      </x:c>
       <x:c r="AG65" s="5" t="str">
         <x:v>Два контура v2</x:v>
       </x:c>
@@ -7028,14 +7080,19 @@
       <x:c r="S66" s="80" t="str">
         <x:v>BetsAPI / Bet365 full markets; Взрослый мужской; run 38538525336 attempt 2</x:v>
       </x:c>
-      <x:c r="T66" s="80"/>
-      <x:c r="U66" s="80"/>
-      <x:c r="V66" s="89" t="str">
+      <x:c r="T66" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="U66" s="80" t="str">
+        <x:v>Поражение</x:v>
+      </x:c>
+      <x:c r="V66" s="89" t="n">
         <x:f>IF(A66="","",IF(U66="","",IF(U66="Выигрыш",J66-1,IF(U66="Полувыигрыш",(J66-1)/2,IF(U66="Возврат",0,IF(U66="Полупроигрыш",-0.5,IF(U66="Поражение",-1,"Проверить результат")))))))</x:f>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="W66" s="80" t="str">
         <x:f>IF(A66="","",IF(U66="","Открыт",IF(ISNUMBER(V66),"Рассчитан","Проверить результат")))</x:f>
-        <x:v>Открыт</x:v>
+        <x:v>Рассчитан</x:v>
       </x:c>
       <x:c r="X66" s="98" t="str">
         <x:v>1 гол до перерыва - полувыигрыш; 2 - полный; исходные условия первичного ответа</x:v>
@@ -7060,9 +7117,11 @@
       </x:c>
       <x:c r="AE66" s="5" t="str">
         <x:f>IF(A66="","",IF(Z66="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z66,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z66,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="AF66" s="5"/>
+        <x:v>Да</x:v>
+      </x:c>
+      <x:c r="AF66" s="5" t="str">
+        <x:v>https://www.live-result.com/football/matches/match1800494_TJ_Druzstevnik_Velke_Ludince-Lokomotiva_Zvolen-live-online | Первый тайм 0:0 по статистике периода и хронологии; голы 46 и 76 минут во втором тайме. Согласуется со срезом BetsAPI на перерыве 16:25:03. | Проверено 14.10.2026 17:14:56 МСК</x:v>
+      </x:c>
       <x:c r="AG66" s="5" t="str">
         <x:v>Два контура v2</x:v>
       </x:c>
@@ -7650,25 +7709,63 @@
       </x:c>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="80"/>
-      <x:c r="B73" s="80"/>
-      <x:c r="C73" s="83"/>
-      <x:c r="D73" s="80"/>
-      <x:c r="E73" s="80"/>
-      <x:c r="F73" s="86"/>
-      <x:c r="G73" s="80"/>
-      <x:c r="H73" s="95"/>
-      <x:c r="I73" s="95"/>
-      <x:c r="J73" s="96"/>
-      <x:c r="K73" s="97"/>
-      <x:c r="L73" s="98"/>
-      <x:c r="M73" s="98"/>
-      <x:c r="N73" s="98"/>
-      <x:c r="O73" s="98"/>
-      <x:c r="P73" s="98"/>
-      <x:c r="Q73" s="80"/>
-      <x:c r="R73" s="80"/>
-      <x:c r="S73" s="80"/>
+      <x:c r="A73" s="80" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B73" s="80" t="str">
+        <x:v>11168551</x:v>
+      </x:c>
+      <x:c r="C73" s="83" t="str">
+        <x:v>14.10.2026 17:11:23</x:v>
+      </x:c>
+      <x:c r="D73" s="80" t="str">
+        <x:v>Норвегия — 1-й дивизион</x:v>
+      </x:c>
+      <x:c r="E73" s="80" t="str">
+        <x:v>Стрёммен - Осане</x:v>
+      </x:c>
+      <x:c r="F73" s="86" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G73" s="80" t="str">
+        <x:v>2:0</x:v>
+      </x:c>
+      <x:c r="H73" s="95" t="str">
+        <x:v>Высокий объём ударов при преимуществе хозяев; возможны голы через давление хозяев и попытки гостей отыграться.</x:v>
+      </x:c>
+      <x:c r="I73" s="95" t="str">
+        <x:v>ТБ 3.25 матча</x:v>
+      </x:c>
+      <x:c r="J73" s="96" t="n">
+        <x:v>1.55</x:v>
+      </x:c>
+      <x:c r="K73" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L73" s="98" t="str">
+        <x:v>Взрослый мужской. В створ 6:1; мимо 5:9; опасные атаки 50:35; угловые 7:3; xG отсутствует.</x:v>
+      </x:c>
+      <x:c r="M73" s="98" t="str">
+        <x:v>2893.5 с между срезами; минута 22 → 53; с перерывом; не окно 10–15 минут. Прирост в створ 5:1, мимо 4:3, угловые 5:1, опасные атаки 30:25.</x:v>
+      </x:c>
+      <x:c r="N73" s="98" t="str">
+        <x:v>21 удар, в створ 6:1, угловые 7:3. Хозяева способны создавать голы сами, гости отвечают объёмом ударов.</x:v>
+      </x:c>
+      <x:c r="O73" s="98" t="str">
+        <x:v>При 2:0 хозяева могут снижать темп; у гостей лишь 1 удар в створ. Нет xG и короткого интервала динамики.</x:v>
+      </x:c>
+      <x:c r="P73" s="98" t="str">
+        <x:v>Есть счёт, минута, статистика и активные линии; нет xG и динамики за 10–15 минут.</x:v>
+      </x:c>
+      <x:c r="Q73" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R73" s="80" t="str">
+        <x:v>Канон 14.10.2026; быстрый отбор + сохранение срезов</x:v>
+      </x:c>
+      <x:c r="S73" s="80" t="str">
+        <x:v>BetsAPI Events board + Bet365 full markets; run 38578271681</x:v>
+      </x:c>
       <x:c r="T73" s="80"/>
       <x:c r="U73" s="80"/>
       <x:c r="V73" s="89" t="str">
@@ -7676,40 +7773,96 @@
       </x:c>
       <x:c r="W73" s="80" t="str">
         <x:f>IF(A73="","",IF(U73="","Открыт",IF(ISNUMBER(V73),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X73" s="98"/>
-      <x:c r="Y73" s="5"/>
-      <x:c r="Z73" s="5"/>
-      <x:c r="AA73" s="5"/>
-      <x:c r="AB73" s="118"/>
-      <x:c r="AC73" s="119"/>
-      <x:c r="AD73" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X73" s="98" t="str">
+        <x:v>Ещё 2 гола: полный выигрыш; 1: полупроигрыш; 0: проигрыш. 1 условная единица. Внешнее обогащение не применялось: нет конкретного уточнения, способного изменить отбор.</x:v>
+      </x:c>
+      <x:c r="Y73" s="5" t="str">
+        <x:v>Оптимальный</x:v>
+      </x:c>
+      <x:c r="Z73" s="5" t="str">
+        <x:v>20261014T171124-11168551</x:v>
+      </x:c>
+      <x:c r="AA73" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB73" s="118" t="n">
+        <x:v>3.25</x:v>
+      </x:c>
+      <x:c r="AC73" s="119" t="str">
+        <x:v>14.10.2026 17:11:23</x:v>
+      </x:c>
+      <x:c r="AD73" s="119" t="str">
+        <x:v>14.10.2026 17:12:32</x:v>
+      </x:c>
       <x:c r="AE73" s="5" t="str">
         <x:f>IF(A73="","",IF(Z73="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z73,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z73,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF73" s="5"/>
-      <x:c r="AG73" s="5"/>
+      <x:c r="AG73" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="80"/>
-      <x:c r="B74" s="80"/>
-      <x:c r="C74" s="83"/>
-      <x:c r="D74" s="80"/>
-      <x:c r="E74" s="80"/>
-      <x:c r="F74" s="86"/>
-      <x:c r="G74" s="80"/>
-      <x:c r="H74" s="95"/>
-      <x:c r="I74" s="95"/>
-      <x:c r="J74" s="96"/>
-      <x:c r="K74" s="97"/>
-      <x:c r="L74" s="98"/>
-      <x:c r="M74" s="98"/>
-      <x:c r="N74" s="98"/>
-      <x:c r="O74" s="98"/>
-      <x:c r="P74" s="98"/>
-      <x:c r="Q74" s="80"/>
-      <x:c r="R74" s="80"/>
-      <x:c r="S74" s="80"/>
+      <x:c r="A74" s="80" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B74" s="80" t="str">
+        <x:v>11168551</x:v>
+      </x:c>
+      <x:c r="C74" s="83" t="str">
+        <x:v>14.10.2026 17:11:23</x:v>
+      </x:c>
+      <x:c r="D74" s="80" t="str">
+        <x:v>Норвегия — 1-й дивизион</x:v>
+      </x:c>
+      <x:c r="E74" s="80" t="str">
+        <x:v>Стрёммен - Осане</x:v>
+      </x:c>
+      <x:c r="F74" s="86" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G74" s="80" t="str">
+        <x:v>2:0</x:v>
+      </x:c>
+      <x:c r="H74" s="95" t="str">
+        <x:v>Высокий объём ударов при преимуществе хозяев; возможны голы через давление хозяев и попытки гостей отыграться.</x:v>
+      </x:c>
+      <x:c r="I74" s="95" t="str">
+        <x:v>ТБ 3.75 матча</x:v>
+      </x:c>
+      <x:c r="J74" s="96" t="n">
+        <x:v>2.075</x:v>
+      </x:c>
+      <x:c r="K74" s="97" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L74" s="98" t="str">
+        <x:v>Взрослый мужской. В створ 6:1; мимо 5:9; опасные атаки 50:35; угловые 7:3; xG отсутствует.</x:v>
+      </x:c>
+      <x:c r="M74" s="98" t="str">
+        <x:v>2893.5 с между срезами; минута 22 → 53; с перерывом; не окно 10–15 минут. Прирост в створ 5:1, мимо 4:3, угловые 5:1, опасные атаки 30:25.</x:v>
+      </x:c>
+      <x:c r="N74" s="98" t="str">
+        <x:v>21 удар, в створ 6:1, угловые 7:3. Хозяева способны создавать голы сами, гости отвечают объёмом ударов.</x:v>
+      </x:c>
+      <x:c r="O74" s="98" t="str">
+        <x:v>При 2:0 хозяева могут снижать темп; у гостей лишь 1 удар в створ. Нет xG и короткого интервала динамики.</x:v>
+      </x:c>
+      <x:c r="P74" s="98" t="str">
+        <x:v>Есть счёт, минута, статистика и активные линии; нет xG и динамики за 10–15 минут.</x:v>
+      </x:c>
+      <x:c r="Q74" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R74" s="80" t="str">
+        <x:v>Канон 14.10.2026; быстрый отбор + сохранение срезов</x:v>
+      </x:c>
+      <x:c r="S74" s="80" t="str">
+        <x:v>BetsAPI Events board + Bet365 full markets; run 38578271681</x:v>
+      </x:c>
       <x:c r="T74" s="80"/>
       <x:c r="U74" s="80"/>
       <x:c r="V74" s="89" t="str">
@@ -7717,40 +7870,96 @@
       </x:c>
       <x:c r="W74" s="80" t="str">
         <x:f>IF(A74="","",IF(U74="","Открыт",IF(ISNUMBER(V74),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X74" s="98"/>
-      <x:c r="Y74" s="5"/>
-      <x:c r="Z74" s="5"/>
-      <x:c r="AA74" s="5"/>
-      <x:c r="AB74" s="118"/>
-      <x:c r="AC74" s="119"/>
-      <x:c r="AD74" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X74" s="98" t="str">
+        <x:v>Ещё 3 гола: полный выигрыш; 2: полувыигрыш; 0–1: проигрыш. 1 условная единица. Внешнее обогащение не применялось: нет конкретного уточнения, способного изменить отбор.</x:v>
+      </x:c>
+      <x:c r="Y74" s="5" t="str">
+        <x:v>Агрессивный</x:v>
+      </x:c>
+      <x:c r="Z74" s="5" t="str">
+        <x:v>20261014T171124-11168551</x:v>
+      </x:c>
+      <x:c r="AA74" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB74" s="118" t="n">
+        <x:v>3.75</x:v>
+      </x:c>
+      <x:c r="AC74" s="119" t="str">
+        <x:v>14.10.2026 17:11:23</x:v>
+      </x:c>
+      <x:c r="AD74" s="119" t="str">
+        <x:v>14.10.2026 17:12:32</x:v>
+      </x:c>
       <x:c r="AE74" s="5" t="str">
         <x:f>IF(A74="","",IF(Z74="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z74,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z74,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF74" s="5"/>
-      <x:c r="AG74" s="5"/>
+      <x:c r="AG74" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="80"/>
-      <x:c r="B75" s="80"/>
-      <x:c r="C75" s="83"/>
-      <x:c r="D75" s="80"/>
-      <x:c r="E75" s="80"/>
-      <x:c r="F75" s="86"/>
-      <x:c r="G75" s="80"/>
-      <x:c r="H75" s="95"/>
-      <x:c r="I75" s="95"/>
-      <x:c r="J75" s="96"/>
-      <x:c r="K75" s="97"/>
-      <x:c r="L75" s="98"/>
-      <x:c r="M75" s="98"/>
-      <x:c r="N75" s="98"/>
-      <x:c r="O75" s="98"/>
-      <x:c r="P75" s="98"/>
-      <x:c r="Q75" s="80"/>
-      <x:c r="R75" s="80"/>
-      <x:c r="S75" s="80"/>
+      <x:c r="A75" s="80" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B75" s="80" t="str">
+        <x:v>13293139</x:v>
+      </x:c>
+      <x:c r="C75" s="83" t="str">
+        <x:v>14.10.2026 17:11:23</x:v>
+      </x:c>
+      <x:c r="D75" s="80" t="str">
+        <x:v>Египет — второй дивизион B</x:v>
+      </x:c>
+      <x:c r="E75" s="80" t="str">
+        <x:v>Каскада - Джи ФК</x:v>
+      </x:c>
+      <x:c r="F75" s="86" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G75" s="80" t="str">
+        <x:v>0:2</x:v>
+      </x:c>
+      <x:c r="H75" s="95" t="str">
+        <x:v>Взаимная угроза и попытки хозяев вернуться в матч создают условия для следующих голов.</x:v>
+      </x:c>
+      <x:c r="I75" s="95" t="str">
+        <x:v>ТБ 3 матча</x:v>
+      </x:c>
+      <x:c r="J75" s="96" t="n">
+        <x:v>1.825</x:v>
+      </x:c>
+      <x:c r="K75" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L75" s="98" t="str">
+        <x:v>Взрослый мужской. В створ 3:5; мимо 7:4; опасные атаки 51:41; угловые 2:3; xG отсутствует.</x:v>
+      </x:c>
+      <x:c r="M75" s="98" t="str">
+        <x:v>2893.5 с между срезами; минута 39 → 55; с перерывом; не окно 10–15 минут. Прирост в створ 1:2, мимо 2:2, угловые 2:1, опасные атаки 19:13.</x:v>
+      </x:c>
+      <x:c r="N75" s="98" t="str">
+        <x:v>В створ 3:5, мимо 7:4, опасные атаки 51:41. Угроза с обеих сторон при необходимости хозяев отыгрываться.</x:v>
+      </x:c>
+      <x:c r="O75" s="98" t="str">
+        <x:v>Гости ведут 0:2 и могут перейти к удержанию. Нет xG и короткого интервала динамики.</x:v>
+      </x:c>
+      <x:c r="P75" s="98" t="str">
+        <x:v>Есть счёт, минута, статистика и активные линии; нет xG и динамики за 10–15 минут.</x:v>
+      </x:c>
+      <x:c r="Q75" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R75" s="80" t="str">
+        <x:v>Канон 14.10.2026; быстрый отбор + сохранение срезов</x:v>
+      </x:c>
+      <x:c r="S75" s="80" t="str">
+        <x:v>BetsAPI Events board + Bet365 full markets; run 38578271681</x:v>
+      </x:c>
       <x:c r="T75" s="80"/>
       <x:c r="U75" s="80"/>
       <x:c r="V75" s="89" t="str">
@@ -7758,40 +7967,96 @@
       </x:c>
       <x:c r="W75" s="80" t="str">
         <x:f>IF(A75="","",IF(U75="","Открыт",IF(ISNUMBER(V75),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X75" s="98"/>
-      <x:c r="Y75" s="5"/>
-      <x:c r="Z75" s="5"/>
-      <x:c r="AA75" s="5"/>
-      <x:c r="AB75" s="118"/>
-      <x:c r="AC75" s="119"/>
-      <x:c r="AD75" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X75" s="98" t="str">
+        <x:v>Ещё 2 гола: выигрыш; 1: возврат; 0: проигрыш. 1 условная единица. Внешнее обогащение не применялось: нет конкретного уточнения, способного изменить отбор.</x:v>
+      </x:c>
+      <x:c r="Y75" s="5" t="str">
+        <x:v>Оптимальный</x:v>
+      </x:c>
+      <x:c r="Z75" s="5" t="str">
+        <x:v>20261014T171124-13293139</x:v>
+      </x:c>
+      <x:c r="AA75" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB75" s="118" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AC75" s="119" t="str">
+        <x:v>14.10.2026 17:11:23</x:v>
+      </x:c>
+      <x:c r="AD75" s="119" t="str">
+        <x:v>14.10.2026 17:12:32</x:v>
+      </x:c>
       <x:c r="AE75" s="5" t="str">
         <x:f>IF(A75="","",IF(Z75="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z75,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z75,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF75" s="5"/>
-      <x:c r="AG75" s="5"/>
+      <x:c r="AG75" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="80"/>
-      <x:c r="B76" s="80"/>
-      <x:c r="C76" s="83"/>
-      <x:c r="D76" s="80"/>
-      <x:c r="E76" s="80"/>
-      <x:c r="F76" s="86"/>
-      <x:c r="G76" s="80"/>
-      <x:c r="H76" s="95"/>
-      <x:c r="I76" s="95"/>
-      <x:c r="J76" s="96"/>
-      <x:c r="K76" s="97"/>
-      <x:c r="L76" s="98"/>
-      <x:c r="M76" s="98"/>
-      <x:c r="N76" s="98"/>
-      <x:c r="O76" s="98"/>
-      <x:c r="P76" s="98"/>
-      <x:c r="Q76" s="80"/>
-      <x:c r="R76" s="80"/>
-      <x:c r="S76" s="80"/>
+      <x:c r="A76" s="80" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B76" s="80" t="str">
+        <x:v>13293139</x:v>
+      </x:c>
+      <x:c r="C76" s="83" t="str">
+        <x:v>14.10.2026 17:11:23</x:v>
+      </x:c>
+      <x:c r="D76" s="80" t="str">
+        <x:v>Египет — второй дивизион B</x:v>
+      </x:c>
+      <x:c r="E76" s="80" t="str">
+        <x:v>Каскада - Джи ФК</x:v>
+      </x:c>
+      <x:c r="F76" s="86" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G76" s="80" t="str">
+        <x:v>0:2</x:v>
+      </x:c>
+      <x:c r="H76" s="95" t="str">
+        <x:v>Взаимная угроза и попытки хозяев вернуться в матч создают условия для следующих голов.</x:v>
+      </x:c>
+      <x:c r="I76" s="95" t="str">
+        <x:v>ТБ 3.5 матча</x:v>
+      </x:c>
+      <x:c r="J76" s="96" t="n">
+        <x:v>2.75</x:v>
+      </x:c>
+      <x:c r="K76" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L76" s="98" t="str">
+        <x:v>Взрослый мужской. В створ 3:5; мимо 7:4; опасные атаки 51:41; угловые 2:3; xG отсутствует.</x:v>
+      </x:c>
+      <x:c r="M76" s="98" t="str">
+        <x:v>2893.5 с между срезами; минута 39 → 55; с перерывом; не окно 10–15 минут. Прирост в створ 1:2, мимо 2:2, угловые 2:1, опасные атаки 19:13.</x:v>
+      </x:c>
+      <x:c r="N76" s="98" t="str">
+        <x:v>В створ 3:5, мимо 7:4, опасные атаки 51:41. Угроза с обеих сторон при необходимости хозяев отыгрываться.</x:v>
+      </x:c>
+      <x:c r="O76" s="98" t="str">
+        <x:v>Гости ведут 0:2 и могут перейти к удержанию. Нет xG и короткого интервала динамики.</x:v>
+      </x:c>
+      <x:c r="P76" s="98" t="str">
+        <x:v>Есть счёт, минута, статистика и активные линии; нет xG и динамики за 10–15 минут.</x:v>
+      </x:c>
+      <x:c r="Q76" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R76" s="80" t="str">
+        <x:v>Канон 14.10.2026; быстрый отбор + сохранение срезов</x:v>
+      </x:c>
+      <x:c r="S76" s="80" t="str">
+        <x:v>BetsAPI Events board + Bet365 full markets; run 38578271681</x:v>
+      </x:c>
       <x:c r="T76" s="80"/>
       <x:c r="U76" s="80"/>
       <x:c r="V76" s="89" t="str">
@@ -7799,40 +8064,96 @@
       </x:c>
       <x:c r="W76" s="80" t="str">
         <x:f>IF(A76="","",IF(U76="","Открыт",IF(ISNUMBER(V76),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X76" s="98"/>
-      <x:c r="Y76" s="5"/>
-      <x:c r="Z76" s="5"/>
-      <x:c r="AA76" s="5"/>
-      <x:c r="AB76" s="118"/>
-      <x:c r="AC76" s="119"/>
-      <x:c r="AD76" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X76" s="98" t="str">
+        <x:v>Ещё 2 гола: выигрыш; 0–1: проигрыш. 1 условная единица. Внешнее обогащение не применялось: нет конкретного уточнения, способного изменить отбор.</x:v>
+      </x:c>
+      <x:c r="Y76" s="5" t="str">
+        <x:v>Агрессивный</x:v>
+      </x:c>
+      <x:c r="Z76" s="5" t="str">
+        <x:v>20261014T171124-13293139</x:v>
+      </x:c>
+      <x:c r="AA76" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB76" s="118" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="AC76" s="119" t="str">
+        <x:v>14.10.2026 17:11:23</x:v>
+      </x:c>
+      <x:c r="AD76" s="119" t="str">
+        <x:v>14.10.2026 17:12:32</x:v>
+      </x:c>
       <x:c r="AE76" s="5" t="str">
         <x:f>IF(A76="","",IF(Z76="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z76,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z76,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF76" s="5"/>
-      <x:c r="AG76" s="5"/>
+      <x:c r="AG76" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="80"/>
-      <x:c r="B77" s="80"/>
-      <x:c r="C77" s="83"/>
-      <x:c r="D77" s="80"/>
-      <x:c r="E77" s="80"/>
-      <x:c r="F77" s="86"/>
-      <x:c r="G77" s="80"/>
-      <x:c r="H77" s="95"/>
-      <x:c r="I77" s="95"/>
-      <x:c r="J77" s="96"/>
-      <x:c r="K77" s="97"/>
-      <x:c r="L77" s="98"/>
-      <x:c r="M77" s="98"/>
-      <x:c r="N77" s="98"/>
-      <x:c r="O77" s="98"/>
-      <x:c r="P77" s="98"/>
-      <x:c r="Q77" s="80"/>
-      <x:c r="R77" s="80"/>
-      <x:c r="S77" s="80"/>
+      <x:c r="A77" s="80" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B77" s="80" t="str">
+        <x:v>11560445</x:v>
+      </x:c>
+      <x:c r="C77" s="83" t="str">
+        <x:v>14.10.2026 17:11:23</x:v>
+      </x:c>
+      <x:c r="D77" s="80" t="str">
+        <x:v>Эстония — Мейстрилига</x:v>
+      </x:c>
+      <x:c r="E77" s="80" t="str">
+        <x:v>Нарва Транс - Курессааре</x:v>
+      </x:c>
+      <x:c r="F77" s="86" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G77" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H77" s="95" t="str">
+        <x:v>Один или два гола во втором тайме при взаимной угрозе и равном счёте.</x:v>
+      </x:c>
+      <x:c r="I77" s="95" t="str">
+        <x:v>ТБ 1 матча</x:v>
+      </x:c>
+      <x:c r="J77" s="96" t="n">
+        <x:v>1.575</x:v>
+      </x:c>
+      <x:c r="K77" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L77" s="98" t="str">
+        <x:v>Взрослый мужской. В створ 2:4; мимо 0:2; опасные атаки 32:27; угловые 2:2; xG отсутствует.</x:v>
+      </x:c>
+      <x:c r="M77" s="98" t="str">
+        <x:v>2893.5 с между срезами; минута 21 → 53; с перерывом; не окно 10–15 минут. Прирост в створ 1:2, мимо 0:0, угловые 1:1, опасные атаки 22:15.</x:v>
+      </x:c>
+      <x:c r="N77" s="98" t="str">
+        <x:v>В створ 2:4, опасные атаки 32:27. Угроза обеих сторон сочетается с низкой линией.</x:v>
+      </x:c>
+      <x:c r="O77" s="98" t="str">
+        <x:v>Всего 8 ударов, общий темп умеренный. Нет xG и короткого интервала динамики.</x:v>
+      </x:c>
+      <x:c r="P77" s="98" t="str">
+        <x:v>Есть счёт, минута, статистика и активные линии; нет xG и динамики за 10–15 минут.</x:v>
+      </x:c>
+      <x:c r="Q77" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R77" s="80" t="str">
+        <x:v>Канон 14.10.2026; быстрый отбор + сохранение срезов</x:v>
+      </x:c>
+      <x:c r="S77" s="80" t="str">
+        <x:v>BetsAPI Events board + Bet365 full markets; run 38578271681</x:v>
+      </x:c>
       <x:c r="T77" s="80"/>
       <x:c r="U77" s="80"/>
       <x:c r="V77" s="89" t="str">
@@ -7840,40 +8161,96 @@
       </x:c>
       <x:c r="W77" s="80" t="str">
         <x:f>IF(A77="","",IF(U77="","Открыт",IF(ISNUMBER(V77),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X77" s="98"/>
-      <x:c r="Y77" s="5"/>
-      <x:c r="Z77" s="5"/>
-      <x:c r="AA77" s="5"/>
-      <x:c r="AB77" s="118"/>
-      <x:c r="AC77" s="119"/>
-      <x:c r="AD77" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X77" s="98" t="str">
+        <x:v>Ещё 2 гола: выигрыш; 1: возврат; 0: проигрыш. 1 условная единица. Внешнее обогащение не применялось: нет конкретного уточнения, способного изменить отбор.</x:v>
+      </x:c>
+      <x:c r="Y77" s="5" t="str">
+        <x:v>Оптимальный</x:v>
+      </x:c>
+      <x:c r="Z77" s="5" t="str">
+        <x:v>20261014T171124-11560445</x:v>
+      </x:c>
+      <x:c r="AA77" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB77" s="118" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC77" s="119" t="str">
+        <x:v>14.10.2026 17:11:23</x:v>
+      </x:c>
+      <x:c r="AD77" s="119" t="str">
+        <x:v>14.10.2026 17:12:32</x:v>
+      </x:c>
       <x:c r="AE77" s="5" t="str">
         <x:f>IF(A77="","",IF(Z77="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z77,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z77,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF77" s="5"/>
-      <x:c r="AG77" s="5"/>
+      <x:c r="AG77" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="80"/>
-      <x:c r="B78" s="80"/>
-      <x:c r="C78" s="83"/>
-      <x:c r="D78" s="80"/>
-      <x:c r="E78" s="80"/>
-      <x:c r="F78" s="86"/>
-      <x:c r="G78" s="80"/>
-      <x:c r="H78" s="95"/>
-      <x:c r="I78" s="95"/>
-      <x:c r="J78" s="96"/>
-      <x:c r="K78" s="97"/>
-      <x:c r="L78" s="98"/>
-      <x:c r="M78" s="98"/>
-      <x:c r="N78" s="98"/>
-      <x:c r="O78" s="98"/>
-      <x:c r="P78" s="98"/>
-      <x:c r="Q78" s="80"/>
-      <x:c r="R78" s="80"/>
-      <x:c r="S78" s="80"/>
+      <x:c r="A78" s="80" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B78" s="80" t="str">
+        <x:v>11560445</x:v>
+      </x:c>
+      <x:c r="C78" s="83" t="str">
+        <x:v>14.10.2026 17:11:23</x:v>
+      </x:c>
+      <x:c r="D78" s="80" t="str">
+        <x:v>Эстония — Мейстрилига</x:v>
+      </x:c>
+      <x:c r="E78" s="80" t="str">
+        <x:v>Нарва Транс - Курессааре</x:v>
+      </x:c>
+      <x:c r="F78" s="86" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G78" s="80" t="str">
+        <x:v>0:0</x:v>
+      </x:c>
+      <x:c r="H78" s="95" t="str">
+        <x:v>Один или два гола во втором тайме при взаимной угрозе и равном счёте.</x:v>
+      </x:c>
+      <x:c r="I78" s="95" t="str">
+        <x:v>ТБ 1.25 матча</x:v>
+      </x:c>
+      <x:c r="J78" s="96" t="n">
+        <x:v>1.975</x:v>
+      </x:c>
+      <x:c r="K78" s="97" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L78" s="98" t="str">
+        <x:v>Взрослый мужской. В створ 2:4; мимо 0:2; опасные атаки 32:27; угловые 2:2; xG отсутствует.</x:v>
+      </x:c>
+      <x:c r="M78" s="98" t="str">
+        <x:v>2893.5 с между срезами; минута 21 → 53; с перерывом; не окно 10–15 минут. Прирост в створ 1:2, мимо 0:0, угловые 1:1, опасные атаки 22:15.</x:v>
+      </x:c>
+      <x:c r="N78" s="98" t="str">
+        <x:v>В створ 2:4, опасные атаки 32:27. Угроза обеих сторон сочетается с низкой линией.</x:v>
+      </x:c>
+      <x:c r="O78" s="98" t="str">
+        <x:v>Всего 8 ударов, общий темп умеренный. Нет xG и короткого интервала динамики.</x:v>
+      </x:c>
+      <x:c r="P78" s="98" t="str">
+        <x:v>Есть счёт, минута, статистика и активные линии; нет xG и динамики за 10–15 минут.</x:v>
+      </x:c>
+      <x:c r="Q78" s="80" t="str">
+        <x:v>ПОДХОДИТ В LIVE</x:v>
+      </x:c>
+      <x:c r="R78" s="80" t="str">
+        <x:v>Канон 14.10.2026; быстрый отбор + сохранение срезов</x:v>
+      </x:c>
+      <x:c r="S78" s="80" t="str">
+        <x:v>BetsAPI Events board + Bet365 full markets; run 38578271681</x:v>
+      </x:c>
       <x:c r="T78" s="80"/>
       <x:c r="U78" s="80"/>
       <x:c r="V78" s="89" t="str">
@@ -7881,19 +8258,37 @@
       </x:c>
       <x:c r="W78" s="80" t="str">
         <x:f>IF(A78="","",IF(U78="","Открыт",IF(ISNUMBER(V78),"Рассчитан","Проверить результат")))</x:f>
-      </x:c>
-      <x:c r="X78" s="98"/>
-      <x:c r="Y78" s="5"/>
-      <x:c r="Z78" s="5"/>
-      <x:c r="AA78" s="5"/>
-      <x:c r="AB78" s="118"/>
-      <x:c r="AC78" s="119"/>
-      <x:c r="AD78" s="119"/>
+        <x:v>Открыт</x:v>
+      </x:c>
+      <x:c r="X78" s="98" t="str">
+        <x:v>Ещё 2 гола: выигрыш; 1: полупроигрыш; 0: проигрыш. 1 условная единица. Внешнее обогащение не применялось: нет конкретного уточнения, способного изменить отбор.</x:v>
+      </x:c>
+      <x:c r="Y78" s="5" t="str">
+        <x:v>Агрессивный</x:v>
+      </x:c>
+      <x:c r="Z78" s="5" t="str">
+        <x:v>20261014T171124-11560445</x:v>
+      </x:c>
+      <x:c r="AA78" s="5" t="str">
+        <x:v>Матч</x:v>
+      </x:c>
+      <x:c r="AB78" s="118" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="AC78" s="119" t="str">
+        <x:v>14.10.2026 17:11:23</x:v>
+      </x:c>
+      <x:c r="AD78" s="119" t="str">
+        <x:v>14.10.2026 17:12:32</x:v>
+      </x:c>
       <x:c r="AE78" s="5" t="str">
         <x:f>IF(A78="","",IF(Z78="","Нет ID пары",IF(AND(COUNTIFS($Z$59:$Z$505,Z78,$Y$59:$Y$505,"Оптимальный",$W$59:$W$505,"Рассчитан")=1,COUNTIFS($Z$59:$Z$505,Z78,$Y$59:$Y$505,"Агрессивный",$W$59:$W$505,"Рассчитан")=1),"Да","Нет")))</x:f>
+        <x:v>Нет</x:v>
       </x:c>
       <x:c r="AF78" s="5"/>
-      <x:c r="AG78" s="5"/>
+      <x:c r="AG78" s="5" t="str">
+        <x:v>Два контура v2</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="80"/>
